--- a/youzi/申港广东分/index.xlsx
+++ b/youzi/申港广东分/index.xlsx
@@ -39,18 +39,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3616D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -63,12 +105,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -81,12 +117,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -111,19 +219,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,13 +405,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,49 +441,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,7 +597,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0303F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,7 +615,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,19 +729,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,13 +753,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,37 +771,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,7 +879,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
+        <fgColor rgb="FFDD3C4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,7 +927,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -363,13 +1053,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -381,31 +1251,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -441,13 +1311,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -459,13 +1395,1177 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -477,67 +2577,403 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF98D4A6"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC22938"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -549,49 +2985,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -603,2545 +3117,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8698,7 +8698,7 @@
       <c r="C2" t="str">
         <v>603110</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="10" t="str">
         <v>净买: 1763.82万</v>
       </c>
       <c r="E2">
@@ -8713,40 +8713,40 @@
       <c r="H2">
         <v>9.98</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="12">
         <v>9.98</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="2">
         <v>3.91</v>
       </c>
       <c r="L2" s="5">
         <v>1.47</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="13">
         <v>11.62</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="7">
         <v>22.79</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="3">
         <v>15.02</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="8">
         <v>26.53</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="4">
         <v>32.65</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="1">
         <v>28.74</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="9">
         <v>21.77</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="14" t="str">
         <v>净买: 486.49万</v>
       </c>
       <c r="E3">
@@ -8775,40 +8775,40 @@
       <c r="H3">
         <v>6.6</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="15">
         <v>-11.36</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="24">
         <v>-13.44</v>
       </c>
       <c r="K3" s="20">
         <v>-4.79</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="16">
         <v>4.74</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="17">
         <v>-1.89</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="25">
         <v>7.93</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="18">
         <v>13.15</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="19">
         <v>9.82</v>
       </c>
       <c r="Q3" s="26">
         <v>3.87</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="21">
         <v>6.53</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="22">
         <v>-4.11</v>
       </c>
-      <c r="T3" s="16">
+      <c r="T3" s="23">
         <v>-14.7</v>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
       <c r="C4" t="str">
         <v>603881</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 7242.53万</v>
       </c>
       <c r="E4">
@@ -8837,40 +8837,40 @@
       <c r="H4">
         <v>8.87</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="33">
         <v>1.04</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="30">
         <v>11.14</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="39">
         <v>0.03</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="31">
         <v>7.5</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="34">
         <v>8.74</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="28">
         <v>19.61</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="27">
         <v>25.9</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="35">
         <v>21.45</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="36">
         <v>15.56</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="37">
         <v>9.81</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="38">
         <v>-0.74</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="29">
         <v>21.21</v>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       <c r="C5" t="str">
         <v>603881</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -9194.30万</v>
       </c>
       <c r="E5">
@@ -8899,40 +8899,40 @@
       <c r="H5">
         <v>-4.56</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="40">
         <v>-5.7</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="46">
         <v>1.34</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="41">
         <v>2.51</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="49">
         <v>12.77</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="47">
         <v>18.69</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="42">
         <v>14.5</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="48">
         <v>8.94</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="50">
         <v>3.52</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="43">
         <v>-6.42</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="44">
         <v>-4.83</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="51">
         <v>-3.18</v>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="52">
         <v>14.27</v>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       <c r="C6" t="str">
         <v>000818</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="59" t="str">
         <v>净买: 5099.54万</v>
       </c>
       <c r="E6">
@@ -8961,40 +8961,40 @@
       <c r="H6">
         <v>5.63</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="63">
         <v>4.13</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="55">
         <v>14.56</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="64">
         <v>7.97</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="65">
         <v>-2.83</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="53">
         <v>-12.53</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="58">
         <v>-15.63</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="60">
         <v>-12.8</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="61">
         <v>-16.13</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="54">
         <v>-19.84</v>
       </c>
-      <c r="R6" s="63">
+      <c r="R6" s="56">
         <v>-20.37</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="57">
         <v>-19.6</v>
       </c>
-      <c r="T6" s="65">
+      <c r="T6" s="62">
         <v>-60.19</v>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       <c r="C7" t="str">
         <v>600590</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="78" t="str">
         <v>净买: 1013.84万</v>
       </c>
       <c r="E7">
@@ -9023,40 +9023,40 @@
       <c r="H7">
         <v>10.05</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="69">
         <v>0</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="76">
         <v>-2.39</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="70">
         <v>7.39</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="77">
         <v>1.85</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="73">
         <v>1.63</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="66">
         <v>-5.76</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="71">
         <v>-3.48</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="74">
         <v>6.2</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="75">
         <v>16.85</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="67">
         <v>26.41</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="72">
         <v>21.74</v>
       </c>
-      <c r="T7" s="71">
+      <c r="T7" s="68">
         <v>72.17</v>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       <c r="C8" t="str">
         <v>000818</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="82" t="str">
         <v>净卖: -5301.29万</v>
       </c>
       <c r="E8">
@@ -9091,34 +9091,34 @@
       <c r="J8" s="83">
         <v>-9.99</v>
       </c>
-      <c r="K8" s="86">
+      <c r="K8" s="80">
         <v>-13.17</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="89">
         <v>-10.26</v>
       </c>
       <c r="M8" s="81">
         <v>-13.69</v>
       </c>
-      <c r="N8" s="88">
+      <c r="N8" s="84">
         <v>-17.51</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="90">
         <v>-18.06</v>
       </c>
-      <c r="P8" s="90">
+      <c r="P8" s="85">
         <v>-17.26</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="91">
         <v>-14.79</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="86">
         <v>-16.85</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="88">
         <v>-14.02</v>
       </c>
-      <c r="T8" s="84">
+      <c r="T8" s="87">
         <v>-59.03</v>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
       <c r="C9" t="str">
         <v>002290</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="103" t="str">
         <v>净卖: -2168.44万</v>
       </c>
       <c r="E9">
@@ -9147,40 +9147,40 @@
       <c r="H9">
         <v>-9.5</v>
       </c>
-      <c r="I9" s="97">
+      <c r="I9" s="100">
         <v>-0.54</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="104">
         <v>0</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="94">
         <v>0.33</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="97">
         <v>3.33</v>
       </c>
-      <c r="M9" s="100">
+      <c r="M9" s="92">
         <v>-7</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="101">
         <v>-1.67</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="95">
         <v>6.04</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="102">
         <v>7.58</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="98">
         <v>12.71</v>
       </c>
-      <c r="R9" s="103">
+      <c r="R9" s="93">
         <v>16.92</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="99">
         <v>12.79</v>
       </c>
-      <c r="T9" s="95">
+      <c r="T9" s="96">
         <v>210.42</v>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       <c r="C10" t="str">
         <v>605300</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="115" t="str">
         <v>净买: 1145.88万</v>
       </c>
       <c r="E10">
@@ -9209,40 +9209,40 @@
       <c r="H10">
         <v>1.49</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="116">
         <v>8.41</v>
       </c>
-      <c r="J10" s="117">
+      <c r="J10" s="112">
         <v>-2.41</v>
       </c>
-      <c r="K10" s="109">
+      <c r="K10" s="110">
         <v>-12.18</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="106">
         <v>-15</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="111">
         <v>-12.88</v>
       </c>
-      <c r="N10" s="111">
+      <c r="N10" s="117">
         <v>-14.71</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="105">
         <v>-15.65</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="107">
         <v>-16.18</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="108">
         <v>-16.82</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="113">
         <v>-18.35</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="109">
         <v>-15.18</v>
       </c>
-      <c r="T10" s="106">
+      <c r="T10" s="114">
         <v>-35.76</v>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       <c r="C11" t="str">
         <v>605100</v>
       </c>
-      <c r="D11" s="121" t="str">
+      <c r="D11" s="129" t="str">
         <v>净买: 1795.46万</v>
       </c>
       <c r="E11">
@@ -9271,40 +9271,40 @@
       <c r="H11">
         <v>9.99</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="125">
         <v>0</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="130">
         <v>-9.16</v>
       </c>
-      <c r="K11" s="124">
+      <c r="K11" s="120">
         <v>-0.08</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="126">
         <v>0</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="118">
         <v>9.99</v>
       </c>
-      <c r="N11" s="130">
+      <c r="N11" s="127">
         <v>-0.99</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="121">
         <v>8.93</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="123">
         <v>19.83</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="122">
         <v>12.16</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="124">
         <v>23.38</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="119">
         <v>13.07</v>
       </c>
-      <c r="T11" s="127">
+      <c r="T11" s="128">
         <v>89.81</v>
       </c>
     </row>
@@ -9318,7 +9318,7 @@
       <c r="C12" t="str">
         <v>605300</v>
       </c>
-      <c r="D12" s="132" t="str">
+      <c r="D12" s="140" t="str">
         <v>净卖: -1034.72万</v>
       </c>
       <c r="E12">
@@ -9333,16 +9333,16 @@
       <c r="H12">
         <v>-5.36</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="138">
         <v>2.26</v>
       </c>
-      <c r="J12" s="142">
+      <c r="J12" s="141">
         <v>4.81</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="142">
         <v>2.62</v>
       </c>
-      <c r="L12" s="131">
+      <c r="L12" s="143">
         <v>1.49</v>
       </c>
       <c r="M12" s="133">
@@ -9351,22 +9351,22 @@
       <c r="N12" s="134">
         <v>0.07</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="135">
         <v>-1.77</v>
       </c>
-      <c r="P12" s="135">
+      <c r="P12" s="136">
         <v>2.05</v>
       </c>
-      <c r="Q12" s="136">
+      <c r="Q12" s="131">
         <v>0.85</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="139">
         <v>0.21</v>
       </c>
       <c r="S12" s="137">
         <v>-0.92</v>
       </c>
-      <c r="T12" s="143">
+      <c r="T12" s="132">
         <v>-22.72</v>
       </c>
     </row>
@@ -9395,40 +9395,40 @@
       <c r="H13">
         <v>9.83</v>
       </c>
-      <c r="I13" s="148">
+      <c r="I13" s="153">
         <v>0.13</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="154">
         <v>-1.41</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="146">
         <v>-4.6</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="149">
         <v>-6.65</v>
       </c>
       <c r="M13" s="144">
         <v>-6.01</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="150">
         <v>-6.52</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="155">
         <v>-5.5</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="151">
         <v>-10.1</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="152">
         <v>-9.59</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="145">
         <v>-10.87</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="147">
         <v>-11.76</v>
       </c>
-      <c r="T13" s="153">
+      <c r="T13" s="148">
         <v>13.94</v>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       <c r="C14" t="str">
         <v>605303</v>
       </c>
-      <c r="D14" s="169" t="str">
+      <c r="D14" s="161" t="str">
         <v>净买: 1578.26万</v>
       </c>
       <c r="E14">
@@ -9457,40 +9457,40 @@
       <c r="H14">
         <v>10.03</v>
       </c>
-      <c r="I14" s="159">
+      <c r="I14" s="163">
         <v>0</v>
       </c>
-      <c r="J14" s="160">
+      <c r="J14" s="157">
         <v>-7.6</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="164">
         <v>-13.68</v>
       </c>
       <c r="L14" s="158">
         <v>-20.06</v>
       </c>
-      <c r="M14" s="165">
+      <c r="M14" s="162">
         <v>-20.21</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="165">
         <v>-21.58</v>
       </c>
-      <c r="O14" s="167">
+      <c r="O14" s="166">
         <v>-22.87</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="167">
         <v>-23.86</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="159">
         <v>-24.62</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="160">
         <v>-27.13</v>
       </c>
       <c r="S14" s="168">
         <v>-26.6</v>
       </c>
-      <c r="T14" s="161">
+      <c r="T14" s="169">
         <v>85.71</v>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       <c r="C15" t="str">
         <v>605303</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="173" t="str">
         <v>净卖: -1462.35万</v>
       </c>
       <c r="E15">
@@ -9519,40 +9519,40 @@
       <c r="H15">
         <v>-2.55</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="170">
         <v>-4.97</v>
       </c>
       <c r="J15" s="175">
         <v>-5.15</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="176">
         <v>-6.78</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="177">
         <v>-8.31</v>
       </c>
-      <c r="M15" s="177">
+      <c r="M15" s="179">
         <v>-9.49</v>
       </c>
-      <c r="N15" s="173">
+      <c r="N15" s="180">
         <v>-10.39</v>
       </c>
-      <c r="O15" s="182">
+      <c r="O15" s="171">
         <v>-13.37</v>
       </c>
-      <c r="P15" s="178">
+      <c r="P15" s="181">
         <v>-12.74</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="172">
         <v>-14.27</v>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="178">
         <v>-15.54</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="182">
         <v>-16.71</v>
       </c>
-      <c r="T15" s="171">
+      <c r="T15" s="174">
         <v>120.78</v>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       <c r="C16" t="str">
         <v>600301</v>
       </c>
-      <c r="D16" s="183" t="str">
+      <c r="D16" s="194" t="str">
         <v>净卖: -3080.81万</v>
       </c>
       <c r="E16">
@@ -9581,40 +9581,40 @@
       <c r="H16">
         <v>-2.8</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="195">
         <v>-4.62</v>
       </c>
-      <c r="J16" s="184">
+      <c r="J16" s="190">
         <v>-5.96</v>
       </c>
-      <c r="K16" s="185">
+      <c r="K16" s="183">
         <v>-4.88</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="184">
         <v>-5.27</v>
       </c>
-      <c r="M16" s="194">
+      <c r="M16" s="185">
         <v>-3.31</v>
       </c>
-      <c r="N16" s="189">
+      <c r="N16" s="191">
         <v>-7.19</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="189">
         <v>-7.88</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="186">
         <v>-7.88</v>
       </c>
-      <c r="Q16" s="190">
+      <c r="Q16" s="187">
         <v>-10.35</v>
       </c>
-      <c r="R16" s="191">
+      <c r="R16" s="188">
         <v>-11.15</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="192">
         <v>-14.38</v>
       </c>
-      <c r="T16" s="192">
+      <c r="T16" s="193">
         <v>94.27</v>
       </c>
     </row>
@@ -9628,7 +9628,7 @@
       <c r="C17" t="str">
         <v>000815</v>
       </c>
-      <c r="D17" s="204" t="str">
+      <c r="D17" s="202" t="str">
         <v>净买: 5327.66万</v>
       </c>
       <c r="E17">
@@ -9643,40 +9643,40 @@
       <c r="H17">
         <v>2.39</v>
       </c>
-      <c r="I17" s="197">
+      <c r="I17" s="203">
         <v>2.95</v>
       </c>
       <c r="J17" s="205">
         <v>-3.14</v>
       </c>
-      <c r="K17" s="198">
+      <c r="K17" s="207">
         <v>-4.8</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="197">
         <v>-6.52</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="198">
         <v>-12.98</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="208">
         <v>-17.22</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="206">
         <v>-16.91</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="204">
         <v>-20.79</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="199">
         <v>-20.3</v>
       </c>
-      <c r="R17" s="208">
+      <c r="R17" s="196">
         <v>-19.74</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="200">
         <v>-20.85</v>
       </c>
-      <c r="T17" s="196">
+      <c r="T17" s="201">
         <v>32.84</v>
       </c>
     </row>
@@ -9708,37 +9708,37 @@
       <c r="I18" s="216">
         <v>0</v>
       </c>
-      <c r="J18" s="212">
+      <c r="J18" s="211">
         <v>9.99</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="212">
         <v>20.99</v>
       </c>
       <c r="L18" s="213">
         <v>8.87</v>
       </c>
-      <c r="M18" s="214">
+      <c r="M18" s="217">
         <v>-2</v>
       </c>
       <c r="N18" s="220">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="221">
+      <c r="O18" s="218">
         <v>-12.8</v>
       </c>
-      <c r="P18" s="209">
+      <c r="P18" s="214">
         <v>-17.49</v>
       </c>
-      <c r="Q18" s="217">
+      <c r="Q18" s="221">
         <v>-18.11</v>
       </c>
-      <c r="R18" s="210">
+      <c r="R18" s="209">
         <v>-16.36</v>
       </c>
-      <c r="S18" s="215">
+      <c r="S18" s="210">
         <v>-16.55</v>
       </c>
-      <c r="T18" s="211">
+      <c r="T18" s="215">
         <v>15.68</v>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       <c r="C19" t="str">
         <v>603315</v>
       </c>
-      <c r="D19" s="230" t="str">
+      <c r="D19" s="233" t="str">
         <v>净卖: -2227.67万</v>
       </c>
       <c r="E19">
@@ -9767,40 +9767,40 @@
       <c r="H19">
         <v>-4.2</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="226">
         <v>14.82</v>
       </c>
-      <c r="J19" s="225">
+      <c r="J19" s="223">
         <v>3.32</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="234">
         <v>-6.99</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="224">
         <v>-16.3</v>
       </c>
       <c r="M19" s="227">
         <v>-17.25</v>
       </c>
-      <c r="N19" s="223">
+      <c r="N19" s="228">
         <v>-21.7</v>
       </c>
-      <c r="O19" s="228">
+      <c r="O19" s="222">
         <v>-22.29</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="225">
         <v>-20.63</v>
       </c>
-      <c r="Q19" s="232">
+      <c r="Q19" s="229">
         <v>-20.81</v>
       </c>
-      <c r="R19" s="233">
+      <c r="R19" s="231">
         <v>-20.09</v>
       </c>
-      <c r="S19" s="234">
+      <c r="S19" s="232">
         <v>-22.05</v>
       </c>
-      <c r="T19" s="222">
+      <c r="T19" s="230">
         <v>9.78</v>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       <c r="C20" t="str">
         <v>000737</v>
       </c>
-      <c r="D20" s="237" t="str">
+      <c r="D20" s="240" t="str">
         <v>净买: 2607.05万</v>
       </c>
       <c r="E20">
@@ -9829,40 +9829,40 @@
       <c r="H20">
         <v>0.79</v>
       </c>
-      <c r="I20" s="242">
+      <c r="I20" s="235">
         <v>9.19</v>
       </c>
-      <c r="J20" s="238">
+      <c r="J20" s="245">
         <v>15.54</v>
       </c>
-      <c r="K20" s="239">
+      <c r="K20" s="236">
         <v>20.43</v>
       </c>
-      <c r="L20" s="243">
+      <c r="L20" s="246">
         <v>11.93</v>
       </c>
-      <c r="M20" s="240">
+      <c r="M20" s="241">
         <v>4.79</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="242">
         <v>2.64</v>
       </c>
-      <c r="O20" s="245">
+      <c r="O20" s="238">
         <v>2.83</v>
       </c>
-      <c r="P20" s="247">
+      <c r="P20" s="243">
         <v>1.08</v>
       </c>
-      <c r="Q20" s="241">
+      <c r="Q20" s="244">
         <v>-2.15</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="237">
         <v>-11.93</v>
       </c>
-      <c r="S20" s="235">
+      <c r="S20" s="247">
         <v>-19.65</v>
       </c>
-      <c r="T20" s="236">
+      <c r="T20" s="239">
         <v>38.03</v>
       </c>
     </row>
@@ -9891,40 +9891,40 @@
       <c r="H21">
         <v>9.36</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="250">
         <v>-14.36</v>
       </c>
-      <c r="J21" s="259">
+      <c r="J21" s="254">
         <v>-22.92</v>
       </c>
-      <c r="K21" s="260">
+      <c r="K21" s="258">
         <v>-25.67</v>
       </c>
-      <c r="L21" s="254">
+      <c r="L21" s="256">
         <v>-28.8</v>
       </c>
-      <c r="M21" s="250">
+      <c r="M21" s="251">
         <v>-29.11</v>
       </c>
-      <c r="N21" s="248">
+      <c r="N21" s="259">
         <v>-26.05</v>
       </c>
-      <c r="O21" s="255">
+      <c r="O21" s="257">
         <v>-28.27</v>
       </c>
-      <c r="P21" s="256">
+      <c r="P21" s="260">
         <v>-29.03</v>
       </c>
-      <c r="Q21" s="251">
+      <c r="Q21" s="248">
         <v>-29.95</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="255">
         <v>-36.97</v>
       </c>
       <c r="S21" s="249">
         <v>-35.91</v>
       </c>
-      <c r="T21" s="257">
+      <c r="T21" s="252">
         <v>-33.16</v>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       <c r="C22" t="str">
         <v>600727</v>
       </c>
-      <c r="D22" s="265" t="str">
+      <c r="D22" s="262" t="str">
         <v>净卖: -2220.75万</v>
       </c>
       <c r="E22">
@@ -9953,40 +9953,40 @@
       <c r="H22">
         <v>4.31</v>
       </c>
-      <c r="I22" s="269">
+      <c r="I22" s="267">
         <v>-1.31</v>
       </c>
-      <c r="J22" s="266">
+      <c r="J22" s="272">
         <v>0.76</v>
       </c>
-      <c r="K22" s="272">
+      <c r="K22" s="273">
         <v>-9.36</v>
       </c>
-      <c r="L22" s="270">
+      <c r="L22" s="269">
         <v>-13.71</v>
       </c>
-      <c r="M22" s="273">
+      <c r="M22" s="263">
         <v>-11.32</v>
       </c>
-      <c r="N22" s="271">
+      <c r="N22" s="264">
         <v>-12.08</v>
       </c>
-      <c r="O22" s="262">
+      <c r="O22" s="265">
         <v>-7.51</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="270">
         <v>-16.76</v>
       </c>
-      <c r="Q22" s="263">
+      <c r="Q22" s="271">
         <v>-15.13</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="268">
         <v>-16.76</v>
       </c>
-      <c r="S22" s="267">
+      <c r="S22" s="266">
         <v>-15.67</v>
       </c>
-      <c r="T22" s="268">
+      <c r="T22" s="261">
         <v>-16.32</v>
       </c>
     </row>
@@ -10000,7 +10000,7 @@
       <c r="C23" t="str">
         <v>001217</v>
       </c>
-      <c r="D23" s="283" t="str">
+      <c r="D23" s="286" t="str">
         <v>净买: 3127.44万</v>
       </c>
       <c r="E23">
@@ -10015,37 +10015,37 @@
       <c r="H23">
         <v>9.99</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="278">
         <v>0</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="279">
         <v>-8.55</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="280">
         <v>-13.73</v>
       </c>
-      <c r="L23" s="276">
+      <c r="L23" s="281">
         <v>-17.5</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="275">
         <v>-20.66</v>
       </c>
-      <c r="N23" s="285">
+      <c r="N23" s="282">
         <v>-28.6</v>
       </c>
-      <c r="O23" s="278">
+      <c r="O23" s="283">
         <v>-31.02</v>
       </c>
-      <c r="P23" s="279">
+      <c r="P23" s="285">
         <v>-31.09</v>
       </c>
-      <c r="Q23" s="280">
+      <c r="Q23" s="274">
         <v>-29.48</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="276">
         <v>-28.33</v>
       </c>
-      <c r="S23" s="282">
+      <c r="S23" s="284">
         <v>-26.72</v>
       </c>
       <c r="T23" s="277">
@@ -10077,40 +10077,40 @@
       <c r="H24">
         <v>-3.3</v>
       </c>
-      <c r="I24" s="295">
+      <c r="I24" s="287">
         <v>-6.9</v>
       </c>
-      <c r="J24" s="296">
+      <c r="J24" s="295">
         <v>-8.84</v>
       </c>
-      <c r="K24" s="290">
+      <c r="K24" s="296">
         <v>-7.5</v>
       </c>
-      <c r="L24" s="297">
+      <c r="L24" s="292">
         <v>-7.64</v>
       </c>
-      <c r="M24" s="287">
+      <c r="M24" s="298">
         <v>-12.93</v>
       </c>
-      <c r="N24" s="291">
+      <c r="N24" s="288">
         <v>-21.63</v>
       </c>
-      <c r="O24" s="292">
+      <c r="O24" s="289">
         <v>-20.23</v>
       </c>
-      <c r="P24" s="298">
+      <c r="P24" s="299">
         <v>-21.57</v>
       </c>
-      <c r="Q24" s="288">
+      <c r="Q24" s="290">
         <v>-20.09</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="297">
         <v>-20.03</v>
       </c>
-      <c r="S24" s="293">
+      <c r="S24" s="291">
         <v>-17.62</v>
       </c>
-      <c r="T24" s="299">
+      <c r="T24" s="293">
         <v>6.03</v>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       <c r="C25" t="str">
         <v>001333</v>
       </c>
-      <c r="D25" s="302" t="str">
+      <c r="D25" s="306" t="str">
         <v>净买: 1650.82万</v>
       </c>
       <c r="E25">
@@ -10139,40 +10139,40 @@
       <c r="H25">
         <v>-1.88</v>
       </c>
-      <c r="I25" s="306">
+      <c r="I25" s="303">
         <v>12.11</v>
       </c>
-      <c r="J25" s="308">
+      <c r="J25" s="307">
         <v>23.33</v>
       </c>
       <c r="K25" s="311">
         <v>11.01</v>
       </c>
-      <c r="L25" s="309">
+      <c r="L25" s="304">
         <v>-0.08</v>
       </c>
-      <c r="M25" s="303">
+      <c r="M25" s="310">
         <v>-10.07</v>
       </c>
-      <c r="N25" s="310">
+      <c r="N25" s="312">
         <v>-18.1</v>
       </c>
-      <c r="O25" s="312">
+      <c r="O25" s="308">
         <v>-17.47</v>
       </c>
-      <c r="P25" s="304">
+      <c r="P25" s="300">
         <v>-15.81</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="301">
         <v>-10.96</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="305">
         <v>-8.75</v>
       </c>
-      <c r="S25" s="301">
+      <c r="S25" s="302">
         <v>-10.28</v>
       </c>
-      <c r="T25" s="305">
+      <c r="T25" s="309">
         <v>5.65</v>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
       <c r="C26" t="str">
         <v>002365</v>
       </c>
-      <c r="D26" s="314" t="str">
+      <c r="D26" s="319" t="str">
         <v>净卖: -918.91万</v>
       </c>
       <c r="E26">
@@ -10201,40 +10201,40 @@
       <c r="H26">
         <v>-8.32</v>
       </c>
-      <c r="I26" s="316">
+      <c r="I26" s="320">
         <v>20.02</v>
       </c>
-      <c r="J26" s="320">
+      <c r="J26" s="314">
         <v>15.9</v>
       </c>
       <c r="K26" s="321">
         <v>22.97</v>
       </c>
-      <c r="L26" s="317">
+      <c r="L26" s="315">
         <v>19.43</v>
       </c>
-      <c r="M26" s="318">
+      <c r="M26" s="316">
         <v>16.02</v>
       </c>
-      <c r="N26" s="324">
+      <c r="N26" s="322">
         <v>10.37</v>
       </c>
-      <c r="O26" s="319">
+      <c r="O26" s="317">
         <v>9.42</v>
       </c>
-      <c r="P26" s="325">
+      <c r="P26" s="323">
         <v>11.66</v>
       </c>
-      <c r="Q26" s="313">
+      <c r="Q26" s="318">
         <v>6.24</v>
       </c>
-      <c r="R26" s="322">
+      <c r="R26" s="325">
         <v>16.84</v>
       </c>
-      <c r="S26" s="315">
+      <c r="S26" s="313">
         <v>20.49</v>
       </c>
-      <c r="T26" s="323">
+      <c r="T26" s="324">
         <v>60.66</v>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       <c r="C27" t="str">
         <v>600180</v>
       </c>
-      <c r="D27" s="336" t="str">
+      <c r="D27" s="327" t="str">
         <v>净卖: -1973.71万</v>
       </c>
       <c r="E27">
@@ -10263,40 +10263,40 @@
       <c r="H27">
         <v>-4.9</v>
       </c>
-      <c r="I27" s="337">
+      <c r="I27" s="333">
         <v>0.21</v>
       </c>
-      <c r="J27" s="332">
+      <c r="J27" s="334">
         <v>-1.93</v>
       </c>
-      <c r="K27" s="338">
+      <c r="K27" s="328">
         <v>-3.86</v>
       </c>
-      <c r="L27" s="333">
+      <c r="L27" s="329">
         <v>-2.58</v>
       </c>
-      <c r="M27" s="335">
+      <c r="M27" s="337">
         <v>-1.5</v>
       </c>
-      <c r="N27" s="329">
+      <c r="N27" s="330">
         <v>-3.43</v>
       </c>
-      <c r="O27" s="334">
+      <c r="O27" s="331">
         <v>-5.79</v>
       </c>
-      <c r="P27" s="326">
+      <c r="P27" s="332">
         <v>-4.94</v>
       </c>
-      <c r="Q27" s="327">
+      <c r="Q27" s="338">
         <v>-8.58</v>
       </c>
-      <c r="R27" s="328">
+      <c r="R27" s="335">
         <v>-7.73</v>
       </c>
-      <c r="S27" s="330">
+      <c r="S27" s="336">
         <v>-8.37</v>
       </c>
-      <c r="T27" s="331">
+      <c r="T27" s="326">
         <v>-30.9</v>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       <c r="C28" t="str">
         <v>002743</v>
       </c>
-      <c r="D28" s="340" t="str">
+      <c r="D28" s="348" t="str">
         <v>净卖: -345.80万</v>
       </c>
       <c r="E28">
@@ -10325,40 +10325,40 @@
       <c r="H28">
         <v>-9.98</v>
       </c>
-      <c r="I28" s="346">
+      <c r="I28" s="343">
         <v>0</v>
       </c>
-      <c r="J28" s="341">
+      <c r="J28" s="349">
         <v>-5.83</v>
       </c>
-      <c r="K28" s="342">
+      <c r="K28" s="344">
         <v>-3.38</v>
       </c>
-      <c r="L28" s="349">
+      <c r="L28" s="350">
         <v>0.75</v>
       </c>
-      <c r="M28" s="343">
+      <c r="M28" s="345">
         <v>1.88</v>
       </c>
-      <c r="N28" s="347">
+      <c r="N28" s="346">
         <v>3.01</v>
       </c>
-      <c r="O28" s="348">
+      <c r="O28" s="339">
         <v>3.95</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="347">
         <v>0.75</v>
       </c>
-      <c r="Q28" s="345">
+      <c r="Q28" s="340">
         <v>-0.19</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="341">
         <v>1.5</v>
       </c>
-      <c r="S28" s="350">
+      <c r="S28" s="342">
         <v>5.83</v>
       </c>
-      <c r="T28" s="339">
+      <c r="T28" s="351">
         <v>0</v>
       </c>
     </row>
@@ -10372,7 +10372,7 @@
       <c r="C29" t="str">
         <v>600173</v>
       </c>
-      <c r="D29" s="353" t="str">
+      <c r="D29" s="358" t="str">
         <v>净卖: -1818.07万</v>
       </c>
       <c r="E29">
@@ -10387,37 +10387,37 @@
       <c r="H29">
         <v>-1.2</v>
       </c>
-      <c r="I29" s="360">
+      <c r="I29" s="361">
         <v>-8.91</v>
       </c>
-      <c r="J29" s="357">
+      <c r="J29" s="362">
         <v>0.2</v>
       </c>
-      <c r="K29" s="352">
+      <c r="K29" s="353">
         <v>4.45</v>
       </c>
       <c r="L29" s="354">
         <v>-2.94</v>
       </c>
-      <c r="M29" s="355">
+      <c r="M29" s="363">
         <v>-7.89</v>
       </c>
-      <c r="N29" s="361">
+      <c r="N29" s="355">
         <v>-12.45</v>
       </c>
-      <c r="O29" s="362">
+      <c r="O29" s="356">
         <v>-11.84</v>
       </c>
-      <c r="P29" s="363">
+      <c r="P29" s="360">
         <v>-8.1</v>
       </c>
-      <c r="Q29" s="356">
+      <c r="Q29" s="357">
         <v>-5.36</v>
       </c>
       <c r="R29" s="364">
         <v>-2.53</v>
       </c>
-      <c r="S29" s="358">
+      <c r="S29" s="352">
         <v>-3.54</v>
       </c>
       <c r="T29" s="359">
@@ -10434,7 +10434,7 @@
       <c r="C30" t="str">
         <v>000637</v>
       </c>
-      <c r="D30" s="377" t="str">
+      <c r="D30" s="374" t="str">
         <v>净卖: -692.69万</v>
       </c>
       <c r="E30">
@@ -10449,40 +10449,40 @@
       <c r="H30">
         <v>-4.62</v>
       </c>
-      <c r="I30" s="371">
+      <c r="I30" s="367">
         <v>-5.65</v>
       </c>
-      <c r="J30" s="365">
+      <c r="J30" s="368">
         <v>3.83</v>
       </c>
-      <c r="K30" s="372">
+      <c r="K30" s="371">
         <v>-0.81</v>
       </c>
-      <c r="L30" s="366">
+      <c r="L30" s="369">
         <v>0.6</v>
       </c>
-      <c r="M30" s="373">
+      <c r="M30" s="375">
         <v>-2.02</v>
       </c>
-      <c r="N30" s="375">
+      <c r="N30" s="376">
         <v>-6.25</v>
       </c>
-      <c r="O30" s="367">
+      <c r="O30" s="372">
         <v>-4.84</v>
       </c>
-      <c r="P30" s="368">
+      <c r="P30" s="373">
         <v>-4.23</v>
       </c>
-      <c r="Q30" s="374">
+      <c r="Q30" s="366">
         <v>-3.43</v>
       </c>
-      <c r="R30" s="376">
+      <c r="R30" s="377">
         <v>-0.81</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="370">
         <v>-1.01</v>
       </c>
-      <c r="T30" s="370">
+      <c r="T30" s="365">
         <v>-12.3</v>
       </c>
     </row>
@@ -10496,7 +10496,7 @@
       <c r="C31" t="str">
         <v>003038</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="381" t="str">
         <v>净买: 1673.87万</v>
       </c>
       <c r="E31">
@@ -10511,40 +10511,40 @@
       <c r="H31">
         <v>-3.7</v>
       </c>
-      <c r="I31" s="378">
+      <c r="I31" s="386">
         <v>-1.79</v>
       </c>
-      <c r="J31" s="379">
+      <c r="J31" s="382">
         <v>-1.79</v>
       </c>
-      <c r="K31" s="380">
+      <c r="K31" s="383">
         <v>-7.21</v>
       </c>
-      <c r="L31" s="386">
+      <c r="L31" s="387">
         <v>-9</v>
       </c>
-      <c r="M31" s="383">
+      <c r="M31" s="388">
         <v>-11.53</v>
       </c>
-      <c r="N31" s="381">
+      <c r="N31" s="389">
         <v>-10.42</v>
       </c>
-      <c r="O31" s="387">
+      <c r="O31" s="390">
         <v>-9.79</v>
       </c>
-      <c r="P31" s="388">
+      <c r="P31" s="378">
         <v>-11.32</v>
       </c>
-      <c r="Q31" s="384">
+      <c r="Q31" s="379">
         <v>-11.26</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="384">
         <v>-9.89</v>
       </c>
-      <c r="S31" s="389">
+      <c r="S31" s="380">
         <v>-11.89</v>
       </c>
-      <c r="T31" s="390">
+      <c r="T31" s="385">
         <v>-20.47</v>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       <c r="C32" t="str">
         <v>300390</v>
       </c>
-      <c r="D32" s="402" t="str">
+      <c r="D32" s="398" t="str">
         <v>净卖: -2712.20万</v>
       </c>
       <c r="E32">
@@ -10573,40 +10573,40 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="399">
         <v>15.32</v>
       </c>
-      <c r="J32" s="393">
+      <c r="J32" s="394">
         <v>19.24</v>
       </c>
-      <c r="K32" s="396">
+      <c r="K32" s="391">
         <v>21.18</v>
       </c>
-      <c r="L32" s="397">
+      <c r="L32" s="392">
         <v>17.01</v>
       </c>
-      <c r="M32" s="403">
+      <c r="M32" s="395">
         <v>39.41</v>
       </c>
-      <c r="N32" s="391">
+      <c r="N32" s="400">
         <v>44.54</v>
       </c>
-      <c r="O32" s="400">
+      <c r="O32" s="401">
         <v>73.45</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="393">
         <v>64.28</v>
       </c>
-      <c r="Q32" s="398">
+      <c r="Q32" s="403">
         <v>66.69</v>
       </c>
-      <c r="R32" s="399">
+      <c r="R32" s="402">
         <v>76.84</v>
       </c>
-      <c r="S32" s="394">
+      <c r="S32" s="396">
         <v>41.99</v>
       </c>
-      <c r="T32" s="401">
+      <c r="T32" s="397">
         <v>154.76</v>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       <c r="C33" t="str">
         <v>603829</v>
       </c>
-      <c r="D33" s="410" t="str">
+      <c r="D33" s="404" t="str">
         <v>净卖: -2484.77万</v>
       </c>
       <c r="E33">
@@ -10635,40 +10635,40 @@
       <c r="H33">
         <v>0.16</v>
       </c>
-      <c r="I33" s="414">
+      <c r="I33" s="410">
         <v>-10.16</v>
       </c>
-      <c r="J33" s="415">
+      <c r="J33" s="407">
         <v>-9.96</v>
       </c>
-      <c r="K33" s="412">
+      <c r="K33" s="411">
         <v>-18.94</v>
       </c>
-      <c r="L33" s="413">
+      <c r="L33" s="412">
         <v>-22.65</v>
       </c>
       <c r="M33" s="408">
         <v>-22.75</v>
       </c>
-      <c r="N33" s="416">
+      <c r="N33" s="409">
         <v>-25.3</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="414">
         <v>-26.94</v>
       </c>
-      <c r="P33" s="405">
+      <c r="P33" s="415">
         <v>-27.14</v>
       </c>
-      <c r="Q33" s="409">
+      <c r="Q33" s="405">
         <v>-26.97</v>
       </c>
-      <c r="R33" s="411">
+      <c r="R33" s="416">
         <v>-27.01</v>
       </c>
       <c r="S33" s="406">
         <v>-25.4</v>
       </c>
-      <c r="T33" s="407">
+      <c r="T33" s="413">
         <v>-4.23</v>
       </c>
     </row>
@@ -10682,7 +10682,7 @@
       <c r="C34" t="str">
         <v>603829</v>
       </c>
-      <c r="D34" s="426" t="str">
+      <c r="D34" s="427" t="str">
         <v>净卖: -2802.75万</v>
       </c>
       <c r="E34">
@@ -10697,25 +10697,25 @@
       <c r="H34">
         <v>0.15</v>
       </c>
-      <c r="I34" s="427">
+      <c r="I34" s="420">
         <v>-10.11</v>
       </c>
-      <c r="J34" s="428">
+      <c r="J34" s="421">
         <v>-14.21</v>
       </c>
-      <c r="K34" s="422">
+      <c r="K34" s="428">
         <v>-14.32</v>
       </c>
-      <c r="L34" s="429">
+      <c r="L34" s="424">
         <v>-17.16</v>
       </c>
-      <c r="M34" s="419">
+      <c r="M34" s="425">
         <v>-18.97</v>
       </c>
-      <c r="N34" s="420">
+      <c r="N34" s="426">
         <v>-19.19</v>
       </c>
-      <c r="O34" s="423">
+      <c r="O34" s="429">
         <v>-19.01</v>
       </c>
       <c r="P34" s="417">
@@ -10724,13 +10724,13 @@
       <c r="Q34" s="418">
         <v>-17.27</v>
       </c>
-      <c r="R34" s="424">
+      <c r="R34" s="422">
         <v>-15.92</v>
       </c>
-      <c r="S34" s="425">
+      <c r="S34" s="419">
         <v>-14.76</v>
       </c>
-      <c r="T34" s="421">
+      <c r="T34" s="423">
         <v>6.22</v>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       <c r="C35" t="str">
         <v>920427</v>
       </c>
-      <c r="D35" s="439" t="str">
+      <c r="D35" s="440" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E35">
@@ -10759,40 +10759,40 @@
       <c r="H35">
         <v>-8.89</v>
       </c>
-      <c r="I35" s="433">
+      <c r="I35" s="441">
         <v>-21.22</v>
       </c>
-      <c r="J35" s="435">
+      <c r="J35" s="442">
         <v>-19.61</v>
       </c>
-      <c r="K35" s="436">
+      <c r="K35" s="435">
         <v>-23.32</v>
       </c>
-      <c r="L35" s="440">
+      <c r="L35" s="430">
         <v>-23.12</v>
       </c>
-      <c r="M35" s="437">
+      <c r="M35" s="431">
         <v>-27.46</v>
       </c>
-      <c r="N35" s="441">
+      <c r="N35" s="436">
         <v>-27.71</v>
       </c>
-      <c r="O35" s="434">
+      <c r="O35" s="437">
         <v>-26.34</v>
       </c>
       <c r="P35" s="438">
         <v>-23.22</v>
       </c>
-      <c r="Q35" s="430">
+      <c r="Q35" s="432">
         <v>-26.44</v>
       </c>
-      <c r="R35" s="431">
+      <c r="R35" s="433">
         <v>-27.12</v>
       </c>
-      <c r="S35" s="442">
+      <c r="S35" s="434">
         <v>-26.68</v>
       </c>
-      <c r="T35" s="432">
+      <c r="T35" s="439">
         <v>-38.39</v>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       <c r="C36" t="str">
         <v>920427</v>
       </c>
-      <c r="D36" s="447" t="str">
+      <c r="D36" s="451" t="str">
         <v>净卖: -130.63万</v>
       </c>
       <c r="E36">
@@ -10824,37 +10824,37 @@
       <c r="I36" s="448">
         <v>6.67</v>
       </c>
-      <c r="J36" s="445">
+      <c r="J36" s="450">
         <v>1.75</v>
       </c>
-      <c r="K36" s="443">
+      <c r="K36" s="452">
         <v>2.01</v>
       </c>
-      <c r="L36" s="449">
+      <c r="L36" s="453">
         <v>-3.75</v>
       </c>
-      <c r="M36" s="453">
+      <c r="M36" s="454">
         <v>-4.08</v>
       </c>
-      <c r="N36" s="444">
+      <c r="N36" s="449">
         <v>-2.27</v>
       </c>
-      <c r="O36" s="450">
+      <c r="O36" s="445">
         <v>1.88</v>
       </c>
-      <c r="P36" s="451">
+      <c r="P36" s="455">
         <v>-2.39</v>
       </c>
-      <c r="Q36" s="454">
+      <c r="Q36" s="443">
         <v>-3.3</v>
       </c>
-      <c r="R36" s="446">
+      <c r="R36" s="444">
         <v>-2.72</v>
       </c>
-      <c r="S36" s="452">
+      <c r="S36" s="446">
         <v>-6.54</v>
       </c>
-      <c r="T36" s="455">
+      <c r="T36" s="447">
         <v>-18.25</v>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       <c r="C37" t="str">
         <v>603798</v>
       </c>
-      <c r="D37" s="466" t="str">
+      <c r="D37" s="467" t="str">
         <v>净卖: -286.39万</v>
       </c>
       <c r="E37">
@@ -10883,40 +10883,40 @@
       <c r="H37">
         <v>-9.99</v>
       </c>
-      <c r="I37" s="467">
+      <c r="I37" s="456">
         <v>0</v>
       </c>
-      <c r="J37" s="460">
+      <c r="J37" s="458">
         <v>-5.52</v>
       </c>
-      <c r="K37" s="461">
+      <c r="K37" s="459">
         <v>-0.12</v>
       </c>
-      <c r="L37" s="462">
+      <c r="L37" s="460">
         <v>-0.72</v>
       </c>
-      <c r="M37" s="457">
+      <c r="M37" s="463">
         <v>-6.3</v>
       </c>
-      <c r="N37" s="463">
+      <c r="N37" s="468">
         <v>-2.82</v>
       </c>
-      <c r="O37" s="465">
+      <c r="O37" s="461">
         <v>-3.3</v>
       </c>
-      <c r="P37" s="458">
+      <c r="P37" s="457">
         <v>-5.34</v>
       </c>
-      <c r="Q37" s="468">
+      <c r="Q37" s="464">
         <v>-4.92</v>
       </c>
-      <c r="R37" s="456">
+      <c r="R37" s="465">
         <v>0.72</v>
       </c>
-      <c r="S37" s="464">
+      <c r="S37" s="462">
         <v>-4.08</v>
       </c>
-      <c r="T37" s="459">
+      <c r="T37" s="466">
         <v>0.54</v>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       <c r="C38" t="str">
         <v>603291</v>
       </c>
-      <c r="D38" s="475" t="str">
+      <c r="D38" s="478" t="str">
         <v>净买: 465.04万</v>
       </c>
       <c r="E38">
@@ -10945,40 +10945,40 @@
       <c r="H38">
         <v>1.97</v>
       </c>
-      <c r="I38" s="469">
+      <c r="I38" s="472">
         <v>-11.73</v>
       </c>
-      <c r="J38" s="480">
+      <c r="J38" s="479">
         <v>-11.73</v>
       </c>
-      <c r="K38" s="481">
+      <c r="K38" s="476">
         <v>-15.59</v>
       </c>
-      <c r="L38" s="476">
+      <c r="L38" s="473">
         <v>-15.51</v>
       </c>
-      <c r="M38" s="471">
+      <c r="M38" s="480">
         <v>-14.97</v>
       </c>
-      <c r="N38" s="472">
+      <c r="N38" s="477">
         <v>-15.66</v>
       </c>
-      <c r="O38" s="470">
+      <c r="O38" s="474">
         <v>-15.82</v>
       </c>
-      <c r="P38" s="477">
+      <c r="P38" s="475">
         <v>-16.05</v>
       </c>
-      <c r="Q38" s="473">
+      <c r="Q38" s="470">
         <v>-15.97</v>
       </c>
-      <c r="R38" s="478">
+      <c r="R38" s="481">
         <v>-15.51</v>
       </c>
-      <c r="S38" s="474">
+      <c r="S38" s="471">
         <v>-15.59</v>
       </c>
-      <c r="T38" s="479">
+      <c r="T38" s="469">
         <v>-9.34</v>
       </c>
     </row>
@@ -11007,32 +11007,32 @@
       <c r="H39">
         <v>-0.79</v>
       </c>
-      <c r="I39" s="484">
+      <c r="I39" s="486">
         <v>4.15</v>
       </c>
-      <c r="J39" s="485">
+      <c r="J39" s="489">
         <v>7.16</v>
       </c>
-      <c r="K39" s="489">
+      <c r="K39" s="484">
         <v>7.16</v>
       </c>
-      <c r="L39" s="486">
+      <c r="L39" s="487">
         <v>7.39</v>
       </c>
-      <c r="M39" s="487">
+      <c r="M39" s="485">
         <v>7.45</v>
       </c>
-      <c r="N39" s="490">
+      <c r="N39" s="482">
         <v>8.48</v>
       </c>
-      <c r="O39" s="482">
+      <c r="O39" s="488">
         <v>6.71</v>
       </c>
       <c r="P39" t="str"/>
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="488">
+      <c r="T39" s="490">
         <v>6.71</v>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       <c r="C40" t="str">
         <v>600605</v>
       </c>
-      <c r="D40" s="493" t="str">
+      <c r="D40" s="491" t="str">
         <v>净卖: -789.04万</v>
       </c>
       <c r="E40">
@@ -11061,13 +11061,13 @@
       <c r="H40">
         <v>6.5</v>
       </c>
-      <c r="I40" s="494">
+      <c r="I40" s="492">
         <v>3.29</v>
       </c>
-      <c r="J40" s="495">
+      <c r="J40" s="493">
         <v>-0.16</v>
       </c>
-      <c r="K40" s="491">
+      <c r="K40" s="494">
         <v>-1.47</v>
       </c>
       <c r="L40" t="str"/>
@@ -11078,7 +11078,7 @@
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="492">
+      <c r="T40" s="495">
         <v>-1.47</v>
       </c>
     </row>
@@ -11141,40 +11141,40 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="507">
+      <c r="I42" s="501">
         <v>38.46</v>
       </c>
-      <c r="J42" s="505">
+      <c r="J42" s="504">
         <v>41.03</v>
       </c>
-      <c r="K42" s="502">
+      <c r="K42" s="507">
         <v>38.46</v>
       </c>
-      <c r="L42" s="498">
+      <c r="L42" s="502">
         <v>36.84</v>
       </c>
-      <c r="M42" s="503">
+      <c r="M42" s="496">
         <v>28.95</v>
       </c>
-      <c r="N42" s="499">
+      <c r="N42" s="497">
         <v>26.32</v>
       </c>
-      <c r="O42" s="496">
+      <c r="O42" s="498">
         <v>31.58</v>
       </c>
-      <c r="P42" s="500">
+      <c r="P42" s="499">
         <v>32.43</v>
       </c>
-      <c r="Q42" s="506">
+      <c r="Q42" s="505">
         <v>24.32</v>
       </c>
-      <c r="R42" s="497">
+      <c r="R42" s="506">
         <v>29.73</v>
       </c>
-      <c r="S42" s="501">
+      <c r="S42" s="503">
         <v>18.92</v>
       </c>
-      <c r="T42" s="504">
+      <c r="T42" s="500">
         <v>51.28</v>
       </c>
     </row>
@@ -11192,34 +11192,34 @@
       <c r="I43" s="517">
         <v>-0.38</v>
       </c>
-      <c r="J43" s="514">
+      <c r="J43" s="511">
         <v>-0.74</v>
       </c>
-      <c r="K43" s="515">
+      <c r="K43" s="518">
         <v>-2.11</v>
       </c>
-      <c r="L43" s="509">
+      <c r="L43" s="519">
         <v>-4.14</v>
       </c>
-      <c r="M43" s="518">
+      <c r="M43" s="508">
         <v>-5.26</v>
       </c>
-      <c r="N43" s="510">
+      <c r="N43" s="514">
         <v>-6.6</v>
       </c>
-      <c r="O43" s="511">
+      <c r="O43" s="515">
         <v>-5.4</v>
       </c>
-      <c r="P43" s="516">
+      <c r="P43" s="512">
         <v>-6.06</v>
       </c>
-      <c r="Q43" s="519">
+      <c r="Q43" s="509">
         <v>-6.48</v>
       </c>
-      <c r="R43" s="512">
+      <c r="R43" s="510">
         <v>-5.55</v>
       </c>
-      <c r="S43" s="508">
+      <c r="S43" s="516">
         <v>-7.91</v>
       </c>
       <c r="T43" s="513">

--- a/youzi/申港广东分/index.xlsx
+++ b/youzi/申港广东分/index.xlsx
@@ -39,12 +39,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3616D"/>
         <bgColor/>
       </patternFill>
@@ -63,7 +81,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,18 +111,342 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -117,25 +459,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,49 +603,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,6 +615,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -213,13 +651,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,73 +771,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,7 +891,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,7 +963,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,13 +1017,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,7 +1059,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -369,7 +1185,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -411,30 +1281,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -447,19 +1293,1843 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC22938"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -471,2677 +3141,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8698,7 +8698,7 @@
       <c r="C2" t="str">
         <v>603110</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="8" t="str">
         <v>净买: 1763.82万</v>
       </c>
       <c r="E2">
@@ -8713,40 +8713,40 @@
       <c r="H2">
         <v>9.98</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
       <c r="J2" s="12">
         <v>9.98</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="5">
         <v>3.91</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="1">
         <v>1.47</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="2">
         <v>11.62</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="10">
         <v>22.79</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="11">
         <v>15.02</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="3">
         <v>26.53</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="6">
         <v>32.65</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="13">
         <v>28.74</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="7">
         <v>21.77</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="4">
         <v>0</v>
       </c>
     </row>
@@ -8760,7 +8760,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="22" t="str">
         <v>净买: 486.49万</v>
       </c>
       <c r="E3">
@@ -8775,40 +8775,40 @@
       <c r="H3">
         <v>6.6</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="14">
         <v>-11.36</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="17">
         <v>-13.44</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="18">
         <v>-4.79</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="19">
         <v>4.74</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="23">
         <v>-1.89</v>
       </c>
       <c r="N3" s="25">
         <v>7.93</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="26">
         <v>13.15</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="15">
         <v>9.82</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="24">
         <v>3.87</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="16">
         <v>6.53</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="20">
         <v>-4.11</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="21">
         <v>-14.7</v>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
       <c r="C4" t="str">
         <v>603881</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="36" t="str">
         <v>净买: 7242.53万</v>
       </c>
       <c r="E4">
@@ -8837,40 +8837,40 @@
       <c r="H4">
         <v>8.87</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="37">
         <v>1.04</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="34">
         <v>11.14</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="38">
         <v>0.03</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="39">
         <v>7.5</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="30">
         <v>8.74</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="27">
         <v>19.61</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="28">
         <v>25.9</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="31">
         <v>21.45</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="29">
         <v>15.56</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="32">
         <v>9.81</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="33">
         <v>-0.74</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="35">
         <v>21.21</v>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       <c r="C5" t="str">
         <v>603881</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="50" t="str">
         <v>净卖: -9194.30万</v>
       </c>
       <c r="E5">
@@ -8899,40 +8899,40 @@
       <c r="H5">
         <v>-4.56</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="51">
         <v>-5.7</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="40">
         <v>1.34</v>
       </c>
       <c r="K5" s="41">
         <v>2.51</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="42">
         <v>12.77</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="44">
         <v>18.69</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="43">
         <v>14.5</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="47">
         <v>8.94</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="48">
         <v>3.52</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="52">
         <v>-6.42</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="45">
         <v>-4.83</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="46">
         <v>-3.18</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="49">
         <v>14.27</v>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       <c r="C6" t="str">
         <v>000818</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 5099.54万</v>
       </c>
       <c r="E6">
@@ -8961,40 +8961,40 @@
       <c r="H6">
         <v>5.63</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="61">
         <v>4.13</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="53">
         <v>14.56</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="54">
         <v>7.97</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="57">
         <v>-2.83</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="58">
         <v>-12.53</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="59">
         <v>-15.63</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="56">
         <v>-12.8</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="62">
         <v>-16.13</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="55">
         <v>-19.84</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="63">
         <v>-20.37</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="60">
         <v>-19.6</v>
       </c>
-      <c r="T6" s="62">
+      <c r="T6" s="64">
         <v>-60.19</v>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       <c r="C7" t="str">
         <v>600590</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="77" t="str">
         <v>净买: 1013.84万</v>
       </c>
       <c r="E7">
@@ -9023,40 +9023,40 @@
       <c r="H7">
         <v>10.05</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="67">
         <v>0</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="68">
         <v>-2.39</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="78">
         <v>7.39</v>
       </c>
-      <c r="L7" s="77">
+      <c r="L7" s="71">
         <v>1.85</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="72">
         <v>1.63</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="73">
         <v>-5.76</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="76">
         <v>-3.48</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="66">
         <v>6.2</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="74">
         <v>16.85</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="75">
         <v>26.41</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="69">
         <v>21.74</v>
       </c>
-      <c r="T7" s="68">
+      <c r="T7" s="70">
         <v>72.17</v>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       <c r="C8" t="str">
         <v>000818</v>
       </c>
-      <c r="D8" s="82" t="str">
+      <c r="D8" s="81" t="str">
         <v>净卖: -5301.29万</v>
       </c>
       <c r="E8">
@@ -9085,40 +9085,40 @@
       <c r="H8">
         <v>-10</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="88">
         <v>0</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="84">
         <v>-9.99</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="85">
         <v>-13.17</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="91">
         <v>-10.26</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="82">
         <v>-13.69</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="79">
         <v>-17.51</v>
       </c>
-      <c r="O8" s="90">
+      <c r="O8" s="86">
         <v>-18.06</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="87">
         <v>-17.26</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="80">
         <v>-14.79</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="83">
         <v>-16.85</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="89">
         <v>-14.02</v>
       </c>
-      <c r="T8" s="87">
+      <c r="T8" s="90">
         <v>-59.03</v>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
       <c r="C9" t="str">
         <v>002290</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="95" t="str">
         <v>净卖: -2168.44万</v>
       </c>
       <c r="E9">
@@ -9147,40 +9147,40 @@
       <c r="H9">
         <v>-9.5</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="103">
         <v>-0.54</v>
       </c>
       <c r="J9" s="104">
         <v>0</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="98">
         <v>0.33</v>
       </c>
-      <c r="L9" s="97">
+      <c r="L9" s="99">
         <v>3.33</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="97">
         <v>-7</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="100">
         <v>-1.67</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="92">
         <v>6.04</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="93">
         <v>7.58</v>
       </c>
-      <c r="Q9" s="98">
+      <c r="Q9" s="96">
         <v>12.71</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="101">
         <v>16.92</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="94">
         <v>12.79</v>
       </c>
-      <c r="T9" s="96">
+      <c r="T9" s="102">
         <v>210.42</v>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       <c r="C10" t="str">
         <v>605300</v>
       </c>
-      <c r="D10" s="115" t="str">
+      <c r="D10" s="107" t="str">
         <v>净买: 1145.88万</v>
       </c>
       <c r="E10">
@@ -9209,40 +9209,40 @@
       <c r="H10">
         <v>1.49</v>
       </c>
-      <c r="I10" s="116">
+      <c r="I10" s="110">
         <v>8.41</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="115">
         <v>-2.41</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="116">
         <v>-12.18</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="111">
         <v>-15</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="108">
         <v>-12.88</v>
       </c>
       <c r="N10" s="117">
         <v>-14.71</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="112">
         <v>-15.65</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="113">
         <v>-16.18</v>
       </c>
-      <c r="Q10" s="108">
+      <c r="Q10" s="114">
         <v>-16.82</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="109">
         <v>-18.35</v>
       </c>
-      <c r="S10" s="109">
+      <c r="S10" s="105">
         <v>-15.18</v>
       </c>
-      <c r="T10" s="114">
+      <c r="T10" s="106">
         <v>-35.76</v>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       <c r="C11" t="str">
         <v>605100</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="122" t="str">
         <v>净买: 1795.46万</v>
       </c>
       <c r="E11">
@@ -9271,40 +9271,40 @@
       <c r="H11">
         <v>9.99</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="128">
         <v>0</v>
       </c>
-      <c r="J11" s="130">
+      <c r="J11" s="127">
         <v>-9.16</v>
       </c>
-      <c r="K11" s="120">
+      <c r="K11" s="129">
         <v>-0.08</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="130">
         <v>0</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="123">
         <v>9.99</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="124">
         <v>-0.99</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="118">
         <v>8.93</v>
       </c>
-      <c r="P11" s="123">
+      <c r="P11" s="119">
         <v>19.83</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="125">
         <v>12.16</v>
       </c>
-      <c r="R11" s="124">
+      <c r="R11" s="120">
         <v>23.38</v>
       </c>
-      <c r="S11" s="119">
+      <c r="S11" s="126">
         <v>13.07</v>
       </c>
-      <c r="T11" s="128">
+      <c r="T11" s="121">
         <v>89.81</v>
       </c>
     </row>
@@ -9318,7 +9318,7 @@
       <c r="C12" t="str">
         <v>605300</v>
       </c>
-      <c r="D12" s="140" t="str">
+      <c r="D12" s="142" t="str">
         <v>净卖: -1034.72万</v>
       </c>
       <c r="E12">
@@ -9333,16 +9333,16 @@
       <c r="H12">
         <v>-5.36</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="143">
         <v>2.26</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="131">
         <v>4.81</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="139">
         <v>2.62</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="132">
         <v>1.49</v>
       </c>
       <c r="M12" s="133">
@@ -9351,22 +9351,22 @@
       <c r="N12" s="134">
         <v>0.07</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="140">
         <v>-1.77</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="135">
         <v>2.05</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="138">
         <v>0.85</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="136">
         <v>0.21</v>
       </c>
       <c r="S12" s="137">
         <v>-0.92</v>
       </c>
-      <c r="T12" s="132">
+      <c r="T12" s="141">
         <v>-22.72</v>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       <c r="C13" t="str">
         <v>002114</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="155" t="str">
         <v>净买: 1554.85万</v>
       </c>
       <c r="E13">
@@ -9395,40 +9395,40 @@
       <c r="H13">
         <v>9.83</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="156">
         <v>0.13</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="152">
         <v>-1.41</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="153">
         <v>-4.6</v>
       </c>
       <c r="L13" s="149">
         <v>-6.65</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="151">
         <v>-6.01</v>
       </c>
       <c r="N13" s="150">
         <v>-6.52</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="144">
         <v>-5.5</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="145">
         <v>-10.1</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="146">
         <v>-9.59</v>
       </c>
-      <c r="R13" s="145">
+      <c r="R13" s="147">
         <v>-10.87</v>
       </c>
-      <c r="S13" s="147">
+      <c r="S13" s="148">
         <v>-11.76</v>
       </c>
-      <c r="T13" s="148">
+      <c r="T13" s="154">
         <v>13.94</v>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       <c r="C14" t="str">
         <v>605303</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="158" t="str">
         <v>净买: 1578.26万</v>
       </c>
       <c r="E14">
@@ -9457,40 +9457,40 @@
       <c r="H14">
         <v>10.03</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="168">
         <v>0</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="164">
         <v>-7.6</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="160">
         <v>-13.68</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="169">
         <v>-20.06</v>
       </c>
-      <c r="M14" s="162">
+      <c r="M14" s="165">
         <v>-20.21</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="161">
         <v>-21.58</v>
       </c>
-      <c r="O14" s="166">
+      <c r="O14" s="162">
         <v>-22.87</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="166">
         <v>-23.86</v>
       </c>
-      <c r="Q14" s="159">
+      <c r="Q14" s="167">
         <v>-24.62</v>
       </c>
-      <c r="R14" s="160">
+      <c r="R14" s="159">
         <v>-27.13</v>
       </c>
-      <c r="S14" s="168">
+      <c r="S14" s="157">
         <v>-26.6</v>
       </c>
-      <c r="T14" s="169">
+      <c r="T14" s="163">
         <v>85.71</v>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       <c r="C15" t="str">
         <v>605303</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="179" t="str">
         <v>净卖: -1462.35万</v>
       </c>
       <c r="E15">
@@ -9519,40 +9519,40 @@
       <c r="H15">
         <v>-2.55</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="180">
         <v>-4.97</v>
       </c>
-      <c r="J15" s="175">
+      <c r="J15" s="174">
         <v>-5.15</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="177">
         <v>-6.78</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="171">
         <v>-8.31</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="175">
         <v>-9.49</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="172">
         <v>-10.39</v>
       </c>
-      <c r="O15" s="171">
+      <c r="O15" s="181">
         <v>-13.37</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="178">
         <v>-12.74</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="182">
         <v>-14.27</v>
       </c>
-      <c r="R15" s="178">
+      <c r="R15" s="176">
         <v>-15.54</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="173">
         <v>-16.71</v>
       </c>
-      <c r="T15" s="174">
+      <c r="T15" s="170">
         <v>120.78</v>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       <c r="C16" t="str">
         <v>600301</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="186" t="str">
         <v>净卖: -3080.81万</v>
       </c>
       <c r="E16">
@@ -9581,10 +9581,10 @@
       <c r="H16">
         <v>-2.8</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="187">
         <v>-4.62</v>
       </c>
-      <c r="J16" s="190">
+      <c r="J16" s="192">
         <v>-5.96</v>
       </c>
       <c r="K16" s="183">
@@ -9593,28 +9593,28 @@
       <c r="L16" s="184">
         <v>-5.27</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="189">
         <v>-3.31</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="193">
         <v>-7.19</v>
       </c>
-      <c r="O16" s="189">
+      <c r="O16" s="188">
         <v>-7.88</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="194">
         <v>-7.88</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="185">
         <v>-10.35</v>
       </c>
-      <c r="R16" s="188">
+      <c r="R16" s="190">
         <v>-11.15</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="195">
         <v>-14.38</v>
       </c>
-      <c r="T16" s="193">
+      <c r="T16" s="191">
         <v>94.27</v>
       </c>
     </row>
@@ -9628,7 +9628,7 @@
       <c r="C17" t="str">
         <v>000815</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="204" t="str">
         <v>净买: 5327.66万</v>
       </c>
       <c r="E17">
@@ -9643,13 +9643,13 @@
       <c r="H17">
         <v>2.39</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="200">
         <v>2.95</v>
       </c>
-      <c r="J17" s="205">
+      <c r="J17" s="201">
         <v>-3.14</v>
       </c>
-      <c r="K17" s="207">
+      <c r="K17" s="196">
         <v>-4.8</v>
       </c>
       <c r="L17" s="197">
@@ -9658,25 +9658,25 @@
       <c r="M17" s="198">
         <v>-12.98</v>
       </c>
-      <c r="N17" s="208">
+      <c r="N17" s="205">
         <v>-17.22</v>
       </c>
-      <c r="O17" s="206">
+      <c r="O17" s="199">
         <v>-16.91</v>
       </c>
-      <c r="P17" s="204">
+      <c r="P17" s="206">
         <v>-20.79</v>
       </c>
-      <c r="Q17" s="199">
+      <c r="Q17" s="202">
         <v>-20.3</v>
       </c>
-      <c r="R17" s="196">
+      <c r="R17" s="203">
         <v>-19.74</v>
       </c>
-      <c r="S17" s="200">
+      <c r="S17" s="207">
         <v>-20.85</v>
       </c>
-      <c r="T17" s="201">
+      <c r="T17" s="208">
         <v>32.84</v>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       <c r="C18" t="str">
         <v>603315</v>
       </c>
-      <c r="D18" s="219" t="str">
+      <c r="D18" s="218" t="str">
         <v>净买: 2006.31万</v>
       </c>
       <c r="E18">
@@ -9705,40 +9705,40 @@
       <c r="H18">
         <v>10.03</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="217">
         <v>0</v>
       </c>
-      <c r="J18" s="211">
+      <c r="J18" s="219">
         <v>9.99</v>
       </c>
-      <c r="K18" s="212">
+      <c r="K18" s="220">
         <v>20.99</v>
       </c>
-      <c r="L18" s="213">
+      <c r="L18" s="210">
         <v>8.87</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="213">
         <v>-2</v>
       </c>
-      <c r="N18" s="220">
+      <c r="N18" s="214">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="218">
+      <c r="O18" s="211">
         <v>-12.8</v>
       </c>
-      <c r="P18" s="214">
+      <c r="P18" s="212">
         <v>-17.49</v>
       </c>
       <c r="Q18" s="221">
         <v>-18.11</v>
       </c>
-      <c r="R18" s="209">
+      <c r="R18" s="215">
         <v>-16.36</v>
       </c>
-      <c r="S18" s="210">
+      <c r="S18" s="216">
         <v>-16.55</v>
       </c>
-      <c r="T18" s="215">
+      <c r="T18" s="209">
         <v>15.68</v>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       <c r="C19" t="str">
         <v>603315</v>
       </c>
-      <c r="D19" s="233" t="str">
+      <c r="D19" s="222" t="str">
         <v>净卖: -2227.67万</v>
       </c>
       <c r="E19">
@@ -9767,40 +9767,40 @@
       <c r="H19">
         <v>-4.2</v>
       </c>
-      <c r="I19" s="226">
+      <c r="I19" s="223">
         <v>14.82</v>
       </c>
-      <c r="J19" s="223">
+      <c r="J19" s="229">
         <v>3.32</v>
       </c>
-      <c r="K19" s="234">
+      <c r="K19" s="230">
         <v>-6.99</v>
       </c>
-      <c r="L19" s="224">
+      <c r="L19" s="226">
         <v>-16.3</v>
       </c>
       <c r="M19" s="227">
         <v>-17.25</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="224">
         <v>-21.7</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="231">
         <v>-22.29</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="228">
         <v>-20.63</v>
       </c>
-      <c r="Q19" s="229">
+      <c r="Q19" s="225">
         <v>-20.81</v>
       </c>
-      <c r="R19" s="231">
+      <c r="R19" s="232">
         <v>-20.09</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="234">
         <v>-22.05</v>
       </c>
-      <c r="T19" s="230">
+      <c r="T19" s="233">
         <v>9.78</v>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       <c r="C20" t="str">
         <v>000737</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 2607.05万</v>
       </c>
       <c r="E20">
@@ -9829,40 +9829,40 @@
       <c r="H20">
         <v>0.79</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="244">
         <v>9.19</v>
       </c>
-      <c r="J20" s="245">
+      <c r="J20" s="239">
         <v>15.54</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="235">
         <v>20.43</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="245">
         <v>11.93</v>
       </c>
-      <c r="M20" s="241">
+      <c r="M20" s="237">
         <v>4.79</v>
       </c>
-      <c r="N20" s="242">
+      <c r="N20" s="240">
         <v>2.64</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="241">
         <v>2.83</v>
       </c>
-      <c r="P20" s="243">
+      <c r="P20" s="246">
         <v>1.08</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="242">
         <v>-2.15</v>
       </c>
-      <c r="R20" s="237">
+      <c r="R20" s="243">
         <v>-11.93</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="236">
         <v>-19.65</v>
       </c>
-      <c r="T20" s="239">
+      <c r="T20" s="238">
         <v>38.03</v>
       </c>
     </row>
@@ -9876,7 +9876,7 @@
       <c r="C21" t="str">
         <v>000779</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="252" t="str">
         <v>净买: 1464.90万</v>
       </c>
       <c r="E21">
@@ -9891,40 +9891,40 @@
       <c r="H21">
         <v>9.36</v>
       </c>
-      <c r="I21" s="250">
+      <c r="I21" s="259">
         <v>-14.36</v>
       </c>
-      <c r="J21" s="254">
+      <c r="J21" s="253">
         <v>-22.92</v>
       </c>
-      <c r="K21" s="258">
+      <c r="K21" s="254">
         <v>-25.67</v>
       </c>
-      <c r="L21" s="256">
+      <c r="L21" s="260">
         <v>-28.8</v>
       </c>
-      <c r="M21" s="251">
+      <c r="M21" s="248">
         <v>-29.11</v>
       </c>
-      <c r="N21" s="259">
+      <c r="N21" s="255">
         <v>-26.05</v>
       </c>
-      <c r="O21" s="257">
+      <c r="O21" s="256">
         <v>-28.27</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="257">
         <v>-29.03</v>
       </c>
-      <c r="Q21" s="248">
+      <c r="Q21" s="258">
         <v>-29.95</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="249">
         <v>-36.97</v>
       </c>
-      <c r="S21" s="249">
+      <c r="S21" s="250">
         <v>-35.91</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="251">
         <v>-33.16</v>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       <c r="C22" t="str">
         <v>600727</v>
       </c>
-      <c r="D22" s="262" t="str">
+      <c r="D22" s="273" t="str">
         <v>净卖: -2220.75万</v>
       </c>
       <c r="E22">
@@ -9953,40 +9953,40 @@
       <c r="H22">
         <v>4.31</v>
       </c>
-      <c r="I22" s="267">
+      <c r="I22" s="261">
         <v>-1.31</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="262">
         <v>0.76</v>
       </c>
-      <c r="K22" s="273">
+      <c r="K22" s="266">
         <v>-9.36</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="263">
         <v>-13.71</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="264">
         <v>-11.32</v>
       </c>
-      <c r="N22" s="264">
+      <c r="N22" s="265">
         <v>-12.08</v>
       </c>
-      <c r="O22" s="265">
+      <c r="O22" s="271">
         <v>-7.51</v>
       </c>
-      <c r="P22" s="270">
+      <c r="P22" s="267">
         <v>-16.76</v>
       </c>
-      <c r="Q22" s="271">
+      <c r="Q22" s="268">
         <v>-15.13</v>
       </c>
-      <c r="R22" s="268">
+      <c r="R22" s="269">
         <v>-16.76</v>
       </c>
-      <c r="S22" s="266">
+      <c r="S22" s="272">
         <v>-15.67</v>
       </c>
-      <c r="T22" s="261">
+      <c r="T22" s="270">
         <v>-16.32</v>
       </c>
     </row>
@@ -10000,7 +10000,7 @@
       <c r="C23" t="str">
         <v>001217</v>
       </c>
-      <c r="D23" s="286" t="str">
+      <c r="D23" s="283" t="str">
         <v>净买: 3127.44万</v>
       </c>
       <c r="E23">
@@ -10015,40 +10015,40 @@
       <c r="H23">
         <v>9.99</v>
       </c>
-      <c r="I23" s="278">
+      <c r="I23" s="284">
         <v>0</v>
       </c>
-      <c r="J23" s="279">
+      <c r="J23" s="285">
         <v>-8.55</v>
       </c>
-      <c r="K23" s="280">
+      <c r="K23" s="286">
         <v>-13.73</v>
       </c>
-      <c r="L23" s="281">
+      <c r="L23" s="274">
         <v>-17.5</v>
       </c>
       <c r="M23" s="275">
         <v>-20.66</v>
       </c>
-      <c r="N23" s="282">
+      <c r="N23" s="276">
         <v>-28.6</v>
       </c>
-      <c r="O23" s="283">
+      <c r="O23" s="279">
         <v>-31.02</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="281">
         <v>-31.09</v>
       </c>
-      <c r="Q23" s="274">
+      <c r="Q23" s="277">
         <v>-29.48</v>
       </c>
-      <c r="R23" s="276">
+      <c r="R23" s="278">
         <v>-28.33</v>
       </c>
-      <c r="S23" s="284">
+      <c r="S23" s="280">
         <v>-26.72</v>
       </c>
-      <c r="T23" s="277">
+      <c r="T23" s="282">
         <v>-21.13</v>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       <c r="C24" t="str">
         <v>000422</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="291" t="str">
         <v>净卖: -6435.12万</v>
       </c>
       <c r="E24">
@@ -10077,40 +10077,40 @@
       <c r="H24">
         <v>-3.3</v>
       </c>
-      <c r="I24" s="287">
+      <c r="I24" s="297">
         <v>-6.9</v>
       </c>
-      <c r="J24" s="295">
+      <c r="J24" s="298">
         <v>-8.84</v>
       </c>
-      <c r="K24" s="296">
+      <c r="K24" s="293">
         <v>-7.5</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="288">
         <v>-7.64</v>
       </c>
-      <c r="M24" s="298">
+      <c r="M24" s="289">
         <v>-12.93</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="294">
         <v>-21.63</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="295">
         <v>-20.23</v>
       </c>
-      <c r="P24" s="299">
+      <c r="P24" s="290">
         <v>-21.57</v>
       </c>
-      <c r="Q24" s="290">
+      <c r="Q24" s="299">
         <v>-20.09</v>
       </c>
-      <c r="R24" s="297">
+      <c r="R24" s="292">
         <v>-20.03</v>
       </c>
-      <c r="S24" s="291">
+      <c r="S24" s="287">
         <v>-17.62</v>
       </c>
-      <c r="T24" s="293">
+      <c r="T24" s="296">
         <v>6.03</v>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       <c r="C25" t="str">
         <v>001333</v>
       </c>
-      <c r="D25" s="306" t="str">
+      <c r="D25" s="305" t="str">
         <v>净买: 1650.82万</v>
       </c>
       <c r="E25">
@@ -10139,40 +10139,40 @@
       <c r="H25">
         <v>-1.88</v>
       </c>
-      <c r="I25" s="303">
+      <c r="I25" s="306">
         <v>12.11</v>
       </c>
-      <c r="J25" s="307">
+      <c r="J25" s="300">
         <v>23.33</v>
       </c>
-      <c r="K25" s="311">
+      <c r="K25" s="301">
         <v>11.01</v>
       </c>
-      <c r="L25" s="304">
+      <c r="L25" s="303">
         <v>-0.08</v>
       </c>
-      <c r="M25" s="310">
+      <c r="M25" s="307">
         <v>-10.07</v>
       </c>
-      <c r="N25" s="312">
+      <c r="N25" s="302">
         <v>-18.1</v>
       </c>
       <c r="O25" s="308">
         <v>-17.47</v>
       </c>
-      <c r="P25" s="300">
+      <c r="P25" s="309">
         <v>-15.81</v>
       </c>
-      <c r="Q25" s="301">
+      <c r="Q25" s="304">
         <v>-10.96</v>
       </c>
-      <c r="R25" s="305">
+      <c r="R25" s="310">
         <v>-8.75</v>
       </c>
-      <c r="S25" s="302">
+      <c r="S25" s="311">
         <v>-10.28</v>
       </c>
-      <c r="T25" s="309">
+      <c r="T25" s="312">
         <v>5.65</v>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
       <c r="C26" t="str">
         <v>002365</v>
       </c>
-      <c r="D26" s="319" t="str">
+      <c r="D26" s="314" t="str">
         <v>净卖: -918.91万</v>
       </c>
       <c r="E26">
@@ -10201,13 +10201,13 @@
       <c r="H26">
         <v>-8.32</v>
       </c>
-      <c r="I26" s="320">
+      <c r="I26" s="321">
         <v>20.02</v>
       </c>
-      <c r="J26" s="314">
+      <c r="J26" s="322">
         <v>15.9</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="318">
         <v>22.97</v>
       </c>
       <c r="L26" s="315">
@@ -10216,25 +10216,25 @@
       <c r="M26" s="316">
         <v>16.02</v>
       </c>
-      <c r="N26" s="322">
+      <c r="N26" s="323">
         <v>10.37</v>
       </c>
-      <c r="O26" s="317">
+      <c r="O26" s="324">
         <v>9.42</v>
       </c>
-      <c r="P26" s="323">
+      <c r="P26" s="317">
         <v>11.66</v>
       </c>
-      <c r="Q26" s="318">
+      <c r="Q26" s="325">
         <v>6.24</v>
       </c>
-      <c r="R26" s="325">
+      <c r="R26" s="313">
         <v>16.84</v>
       </c>
-      <c r="S26" s="313">
+      <c r="S26" s="319">
         <v>20.49</v>
       </c>
-      <c r="T26" s="324">
+      <c r="T26" s="320">
         <v>60.66</v>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       <c r="C27" t="str">
         <v>600180</v>
       </c>
-      <c r="D27" s="327" t="str">
+      <c r="D27" s="334" t="str">
         <v>净卖: -1973.71万</v>
       </c>
       <c r="E27">
@@ -10263,40 +10263,40 @@
       <c r="H27">
         <v>-4.9</v>
       </c>
-      <c r="I27" s="333">
+      <c r="I27" s="332">
         <v>0.21</v>
       </c>
-      <c r="J27" s="334">
+      <c r="J27" s="335">
         <v>-1.93</v>
       </c>
-      <c r="K27" s="328">
+      <c r="K27" s="337">
         <v>-3.86</v>
       </c>
-      <c r="L27" s="329">
+      <c r="L27" s="328">
         <v>-2.58</v>
       </c>
-      <c r="M27" s="337">
+      <c r="M27" s="329">
         <v>-1.5</v>
       </c>
-      <c r="N27" s="330">
+      <c r="N27" s="336">
         <v>-3.43</v>
       </c>
-      <c r="O27" s="331">
+      <c r="O27" s="333">
         <v>-5.79</v>
       </c>
-      <c r="P27" s="332">
+      <c r="P27" s="338">
         <v>-4.94</v>
       </c>
-      <c r="Q27" s="338">
+      <c r="Q27" s="326">
         <v>-8.58</v>
       </c>
-      <c r="R27" s="335">
+      <c r="R27" s="327">
         <v>-7.73</v>
       </c>
-      <c r="S27" s="336">
+      <c r="S27" s="330">
         <v>-8.37</v>
       </c>
-      <c r="T27" s="326">
+      <c r="T27" s="331">
         <v>-30.9</v>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       <c r="C28" t="str">
         <v>002743</v>
       </c>
-      <c r="D28" s="348" t="str">
+      <c r="D28" s="343" t="str">
         <v>净卖: -345.80万</v>
       </c>
       <c r="E28">
@@ -10325,40 +10325,40 @@
       <c r="H28">
         <v>-9.98</v>
       </c>
-      <c r="I28" s="343">
+      <c r="I28" s="339">
         <v>0</v>
       </c>
-      <c r="J28" s="349">
+      <c r="J28" s="344">
         <v>-5.83</v>
       </c>
-      <c r="K28" s="344">
+      <c r="K28" s="347">
         <v>-3.38</v>
       </c>
-      <c r="L28" s="350">
+      <c r="L28" s="348">
         <v>0.75</v>
       </c>
       <c r="M28" s="345">
         <v>1.88</v>
       </c>
-      <c r="N28" s="346">
+      <c r="N28" s="349">
         <v>3.01</v>
       </c>
-      <c r="O28" s="339">
+      <c r="O28" s="350">
         <v>3.95</v>
       </c>
-      <c r="P28" s="347">
+      <c r="P28" s="341">
         <v>0.75</v>
       </c>
-      <c r="Q28" s="340">
+      <c r="Q28" s="342">
         <v>-0.19</v>
       </c>
-      <c r="R28" s="341">
+      <c r="R28" s="340">
         <v>1.5</v>
       </c>
-      <c r="S28" s="342">
+      <c r="S28" s="351">
         <v>5.83</v>
       </c>
-      <c r="T28" s="351">
+      <c r="T28" s="346">
         <v>0</v>
       </c>
     </row>
@@ -10372,7 +10372,7 @@
       <c r="C29" t="str">
         <v>600173</v>
       </c>
-      <c r="D29" s="358" t="str">
+      <c r="D29" s="354" t="str">
         <v>净卖: -1818.07万</v>
       </c>
       <c r="E29">
@@ -10393,34 +10393,34 @@
       <c r="J29" s="362">
         <v>0.2</v>
       </c>
-      <c r="K29" s="353">
+      <c r="K29" s="363">
         <v>4.45</v>
       </c>
-      <c r="L29" s="354">
+      <c r="L29" s="359">
         <v>-2.94</v>
       </c>
-      <c r="M29" s="363">
+      <c r="M29" s="355">
         <v>-7.89</v>
       </c>
-      <c r="N29" s="355">
+      <c r="N29" s="356">
         <v>-12.45</v>
       </c>
-      <c r="O29" s="356">
+      <c r="O29" s="352">
         <v>-11.84</v>
       </c>
-      <c r="P29" s="360">
+      <c r="P29" s="353">
         <v>-8.1</v>
       </c>
-      <c r="Q29" s="357">
+      <c r="Q29" s="360">
         <v>-5.36</v>
       </c>
-      <c r="R29" s="364">
+      <c r="R29" s="357">
         <v>-2.53</v>
       </c>
-      <c r="S29" s="352">
+      <c r="S29" s="358">
         <v>-3.54</v>
       </c>
-      <c r="T29" s="359">
+      <c r="T29" s="364">
         <v>-19.13</v>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       <c r="C30" t="str">
         <v>000637</v>
       </c>
-      <c r="D30" s="374" t="str">
+      <c r="D30" s="368" t="str">
         <v>净卖: -692.69万</v>
       </c>
       <c r="E30">
@@ -10449,22 +10449,22 @@
       <c r="H30">
         <v>-4.62</v>
       </c>
-      <c r="I30" s="367">
+      <c r="I30" s="369">
         <v>-5.65</v>
       </c>
-      <c r="J30" s="368">
+      <c r="J30" s="374">
         <v>3.83</v>
       </c>
-      <c r="K30" s="371">
+      <c r="K30" s="370">
         <v>-0.81</v>
       </c>
-      <c r="L30" s="369">
+      <c r="L30" s="376">
         <v>0.6</v>
       </c>
-      <c r="M30" s="375">
+      <c r="M30" s="377">
         <v>-2.02</v>
       </c>
-      <c r="N30" s="376">
+      <c r="N30" s="371">
         <v>-6.25</v>
       </c>
       <c r="O30" s="372">
@@ -10473,16 +10473,16 @@
       <c r="P30" s="373">
         <v>-4.23</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="375">
         <v>-3.43</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="365">
         <v>-0.81</v>
       </c>
-      <c r="S30" s="370">
+      <c r="S30" s="366">
         <v>-1.01</v>
       </c>
-      <c r="T30" s="365">
+      <c r="T30" s="367">
         <v>-12.3</v>
       </c>
     </row>
@@ -10496,7 +10496,7 @@
       <c r="C31" t="str">
         <v>003038</v>
       </c>
-      <c r="D31" s="381" t="str">
+      <c r="D31" s="383" t="str">
         <v>净买: 1673.87万</v>
       </c>
       <c r="E31">
@@ -10511,40 +10511,40 @@
       <c r="H31">
         <v>-3.7</v>
       </c>
-      <c r="I31" s="386">
+      <c r="I31" s="384">
         <v>-1.79</v>
       </c>
-      <c r="J31" s="382">
+      <c r="J31" s="390">
         <v>-1.79</v>
       </c>
-      <c r="K31" s="383">
+      <c r="K31" s="378">
         <v>-7.21</v>
       </c>
-      <c r="L31" s="387">
+      <c r="L31" s="388">
         <v>-9</v>
       </c>
-      <c r="M31" s="388">
+      <c r="M31" s="389">
         <v>-11.53</v>
       </c>
-      <c r="N31" s="389">
+      <c r="N31" s="385">
         <v>-10.42</v>
       </c>
-      <c r="O31" s="390">
+      <c r="O31" s="379">
         <v>-9.79</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="381">
         <v>-11.32</v>
       </c>
-      <c r="Q31" s="379">
+      <c r="Q31" s="382">
         <v>-11.26</v>
       </c>
-      <c r="R31" s="384">
+      <c r="R31" s="386">
         <v>-9.89</v>
       </c>
       <c r="S31" s="380">
         <v>-11.89</v>
       </c>
-      <c r="T31" s="385">
+      <c r="T31" s="387">
         <v>-20.47</v>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       <c r="C32" t="str">
         <v>300390</v>
       </c>
-      <c r="D32" s="398" t="str">
+      <c r="D32" s="393" t="str">
         <v>净卖: -2712.20万</v>
       </c>
       <c r="E32">
@@ -10573,40 +10573,40 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="399">
+      <c r="I32" s="397">
         <v>15.32</v>
       </c>
-      <c r="J32" s="394">
+      <c r="J32" s="403">
         <v>19.24</v>
       </c>
-      <c r="K32" s="391">
+      <c r="K32" s="398">
         <v>21.18</v>
       </c>
-      <c r="L32" s="392">
+      <c r="L32" s="399">
         <v>17.01</v>
       </c>
-      <c r="M32" s="395">
+      <c r="M32" s="400">
         <v>39.41</v>
       </c>
-      <c r="N32" s="400">
+      <c r="N32" s="401">
         <v>44.54</v>
       </c>
-      <c r="O32" s="401">
+      <c r="O32" s="394">
         <v>73.45</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="391">
         <v>64.28</v>
       </c>
-      <c r="Q32" s="403">
+      <c r="Q32" s="402">
         <v>66.69</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="395">
         <v>76.84</v>
       </c>
       <c r="S32" s="396">
         <v>41.99</v>
       </c>
-      <c r="T32" s="397">
+      <c r="T32" s="392">
         <v>154.76</v>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       <c r="C33" t="str">
         <v>603829</v>
       </c>
-      <c r="D33" s="404" t="str">
+      <c r="D33" s="405" t="str">
         <v>净卖: -2484.77万</v>
       </c>
       <c r="E33">
@@ -10635,40 +10635,40 @@
       <c r="H33">
         <v>0.16</v>
       </c>
-      <c r="I33" s="410">
+      <c r="I33" s="412">
         <v>-10.16</v>
       </c>
-      <c r="J33" s="407">
+      <c r="J33" s="408">
         <v>-9.96</v>
       </c>
-      <c r="K33" s="411">
+      <c r="K33" s="413">
         <v>-18.94</v>
       </c>
-      <c r="L33" s="412">
+      <c r="L33" s="404">
         <v>-22.65</v>
       </c>
-      <c r="M33" s="408">
+      <c r="M33" s="409">
         <v>-22.75</v>
       </c>
-      <c r="N33" s="409">
+      <c r="N33" s="414">
         <v>-25.3</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="406">
         <v>-26.94</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="410">
         <v>-27.14</v>
       </c>
-      <c r="Q33" s="405">
+      <c r="Q33" s="415">
         <v>-26.97</v>
       </c>
-      <c r="R33" s="416">
+      <c r="R33" s="407">
         <v>-27.01</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="411">
         <v>-25.4</v>
       </c>
-      <c r="T33" s="413">
+      <c r="T33" s="416">
         <v>-4.23</v>
       </c>
     </row>
@@ -10682,7 +10682,7 @@
       <c r="C34" t="str">
         <v>603829</v>
       </c>
-      <c r="D34" s="427" t="str">
+      <c r="D34" s="429" t="str">
         <v>净卖: -2802.75万</v>
       </c>
       <c r="E34">
@@ -10697,40 +10697,40 @@
       <c r="H34">
         <v>0.15</v>
       </c>
-      <c r="I34" s="420">
+      <c r="I34" s="417">
         <v>-10.11</v>
       </c>
-      <c r="J34" s="421">
+      <c r="J34" s="426">
         <v>-14.21</v>
       </c>
-      <c r="K34" s="428">
+      <c r="K34" s="427">
         <v>-14.32</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="422">
         <v>-17.16</v>
       </c>
-      <c r="M34" s="425">
+      <c r="M34" s="424">
         <v>-18.97</v>
       </c>
-      <c r="N34" s="426">
+      <c r="N34" s="418">
         <v>-19.19</v>
       </c>
-      <c r="O34" s="429">
+      <c r="O34" s="419">
         <v>-19.01</v>
       </c>
-      <c r="P34" s="417">
+      <c r="P34" s="423">
         <v>-19.05</v>
       </c>
-      <c r="Q34" s="418">
+      <c r="Q34" s="420">
         <v>-17.27</v>
       </c>
-      <c r="R34" s="422">
+      <c r="R34" s="425">
         <v>-15.92</v>
       </c>
-      <c r="S34" s="419">
+      <c r="S34" s="421">
         <v>-14.76</v>
       </c>
-      <c r="T34" s="423">
+      <c r="T34" s="428">
         <v>6.22</v>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       <c r="C35" t="str">
         <v>920427</v>
       </c>
-      <c r="D35" s="440" t="str">
+      <c r="D35" s="433" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E35">
@@ -10759,40 +10759,40 @@
       <c r="H35">
         <v>-8.89</v>
       </c>
-      <c r="I35" s="441">
+      <c r="I35" s="434">
         <v>-21.22</v>
       </c>
-      <c r="J35" s="442">
+      <c r="J35" s="435">
         <v>-19.61</v>
       </c>
-      <c r="K35" s="435">
+      <c r="K35" s="440">
         <v>-23.32</v>
       </c>
-      <c r="L35" s="430">
+      <c r="L35" s="441">
         <v>-23.12</v>
       </c>
-      <c r="M35" s="431">
+      <c r="M35" s="438">
         <v>-27.46</v>
       </c>
-      <c r="N35" s="436">
+      <c r="N35" s="431">
         <v>-27.71</v>
       </c>
-      <c r="O35" s="437">
+      <c r="O35" s="436">
         <v>-26.34</v>
       </c>
-      <c r="P35" s="438">
+      <c r="P35" s="439">
         <v>-23.22</v>
       </c>
-      <c r="Q35" s="432">
+      <c r="Q35" s="437">
         <v>-26.44</v>
       </c>
-      <c r="R35" s="433">
+      <c r="R35" s="442">
         <v>-27.12</v>
       </c>
-      <c r="S35" s="434">
+      <c r="S35" s="430">
         <v>-26.68</v>
       </c>
-      <c r="T35" s="439">
+      <c r="T35" s="432">
         <v>-38.39</v>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       <c r="C36" t="str">
         <v>920427</v>
       </c>
-      <c r="D36" s="451" t="str">
+      <c r="D36" s="452" t="str">
         <v>净卖: -130.63万</v>
       </c>
       <c r="E36">
@@ -10821,40 +10821,40 @@
       <c r="H36">
         <v>-4.33</v>
       </c>
-      <c r="I36" s="448">
+      <c r="I36" s="453">
         <v>6.67</v>
       </c>
-      <c r="J36" s="450">
+      <c r="J36" s="454">
         <v>1.75</v>
       </c>
-      <c r="K36" s="452">
+      <c r="K36" s="450">
         <v>2.01</v>
       </c>
-      <c r="L36" s="453">
+      <c r="L36" s="447">
         <v>-3.75</v>
       </c>
-      <c r="M36" s="454">
+      <c r="M36" s="455">
         <v>-4.08</v>
       </c>
-      <c r="N36" s="449">
+      <c r="N36" s="443">
         <v>-2.27</v>
       </c>
-      <c r="O36" s="445">
+      <c r="O36" s="444">
         <v>1.88</v>
       </c>
-      <c r="P36" s="455">
+      <c r="P36" s="445">
         <v>-2.39</v>
       </c>
-      <c r="Q36" s="443">
+      <c r="Q36" s="451">
         <v>-3.3</v>
       </c>
-      <c r="R36" s="444">
+      <c r="R36" s="449">
         <v>-2.72</v>
       </c>
-      <c r="S36" s="446">
+      <c r="S36" s="448">
         <v>-6.54</v>
       </c>
-      <c r="T36" s="447">
+      <c r="T36" s="446">
         <v>-18.25</v>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       <c r="C37" t="str">
         <v>603798</v>
       </c>
-      <c r="D37" s="467" t="str">
+      <c r="D37" s="468" t="str">
         <v>净卖: -286.39万</v>
       </c>
       <c r="E37">
@@ -10883,40 +10883,40 @@
       <c r="H37">
         <v>-9.99</v>
       </c>
-      <c r="I37" s="456">
+      <c r="I37" s="464">
         <v>0</v>
       </c>
-      <c r="J37" s="458">
+      <c r="J37" s="465">
         <v>-5.52</v>
       </c>
-      <c r="K37" s="459">
+      <c r="K37" s="466">
         <v>-0.12</v>
       </c>
-      <c r="L37" s="460">
+      <c r="L37" s="456">
         <v>-0.72</v>
       </c>
-      <c r="M37" s="463">
+      <c r="M37" s="459">
         <v>-6.3</v>
       </c>
-      <c r="N37" s="468">
+      <c r="N37" s="457">
         <v>-2.82</v>
       </c>
-      <c r="O37" s="461">
+      <c r="O37" s="460">
         <v>-3.3</v>
       </c>
-      <c r="P37" s="457">
+      <c r="P37" s="461">
         <v>-5.34</v>
       </c>
-      <c r="Q37" s="464">
+      <c r="Q37" s="467">
         <v>-4.92</v>
       </c>
-      <c r="R37" s="465">
+      <c r="R37" s="462">
         <v>0.72</v>
       </c>
-      <c r="S37" s="462">
+      <c r="S37" s="458">
         <v>-4.08</v>
       </c>
-      <c r="T37" s="466">
+      <c r="T37" s="463">
         <v>0.54</v>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       <c r="C38" t="str">
         <v>603291</v>
       </c>
-      <c r="D38" s="478" t="str">
+      <c r="D38" s="476" t="str">
         <v>净买: 465.04万</v>
       </c>
       <c r="E38">
@@ -10945,40 +10945,40 @@
       <c r="H38">
         <v>1.97</v>
       </c>
-      <c r="I38" s="472">
+      <c r="I38" s="477">
         <v>-11.73</v>
       </c>
-      <c r="J38" s="479">
+      <c r="J38" s="471">
         <v>-11.73</v>
       </c>
-      <c r="K38" s="476">
+      <c r="K38" s="474">
         <v>-15.59</v>
       </c>
-      <c r="L38" s="473">
+      <c r="L38" s="478">
         <v>-15.51</v>
       </c>
-      <c r="M38" s="480">
+      <c r="M38" s="472">
         <v>-14.97</v>
       </c>
-      <c r="N38" s="477">
+      <c r="N38" s="469">
         <v>-15.66</v>
       </c>
-      <c r="O38" s="474">
+      <c r="O38" s="479">
         <v>-15.82</v>
       </c>
-      <c r="P38" s="475">
+      <c r="P38" s="473">
         <v>-16.05</v>
       </c>
-      <c r="Q38" s="470">
+      <c r="Q38" s="475">
         <v>-15.97</v>
       </c>
-      <c r="R38" s="481">
+      <c r="R38" s="470">
         <v>-15.51</v>
       </c>
-      <c r="S38" s="471">
+      <c r="S38" s="480">
         <v>-15.59</v>
       </c>
-      <c r="T38" s="469">
+      <c r="T38" s="481">
         <v>-9.34</v>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       <c r="C39" t="str">
         <v>603284</v>
       </c>
-      <c r="D39" s="483" t="str">
+      <c r="D39" s="489" t="str">
         <v>净买: 1322.73万</v>
       </c>
       <c r="E39">
@@ -11007,32 +11007,32 @@
       <c r="H39">
         <v>-0.79</v>
       </c>
-      <c r="I39" s="486">
+      <c r="I39" s="487">
         <v>4.15</v>
       </c>
-      <c r="J39" s="489">
+      <c r="J39" s="482">
         <v>7.16</v>
       </c>
-      <c r="K39" s="484">
+      <c r="K39" s="486">
         <v>7.16</v>
       </c>
-      <c r="L39" s="487">
+      <c r="L39" s="488">
         <v>7.39</v>
       </c>
-      <c r="M39" s="485">
+      <c r="M39" s="483">
         <v>7.45</v>
       </c>
-      <c r="N39" s="482">
+      <c r="N39" s="484">
         <v>8.48</v>
       </c>
-      <c r="O39" s="488">
+      <c r="O39" s="490">
         <v>6.71</v>
       </c>
       <c r="P39" t="str"/>
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="490">
+      <c r="T39" s="485">
         <v>6.71</v>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       <c r="C40" t="str">
         <v>600605</v>
       </c>
-      <c r="D40" s="491" t="str">
+      <c r="D40" s="495" t="str">
         <v>净卖: -789.04万</v>
       </c>
       <c r="E40">
@@ -11061,13 +11061,13 @@
       <c r="H40">
         <v>6.5</v>
       </c>
-      <c r="I40" s="492">
+      <c r="I40" s="491">
         <v>3.29</v>
       </c>
-      <c r="J40" s="493">
+      <c r="J40" s="492">
         <v>-0.16</v>
       </c>
-      <c r="K40" s="494">
+      <c r="K40" s="493">
         <v>-1.47</v>
       </c>
       <c r="L40" t="str"/>
@@ -11078,7 +11078,7 @@
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="495">
+      <c r="T40" s="494">
         <v>-1.47</v>
       </c>
     </row>
@@ -11141,40 +11141,40 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="501">
+      <c r="I42" s="499">
         <v>38.46</v>
       </c>
       <c r="J42" s="504">
         <v>41.03</v>
       </c>
-      <c r="K42" s="507">
+      <c r="K42" s="506">
         <v>38.46</v>
       </c>
-      <c r="L42" s="502">
+      <c r="L42" s="500">
         <v>36.84</v>
       </c>
-      <c r="M42" s="496">
+      <c r="M42" s="507">
         <v>28.95</v>
       </c>
-      <c r="N42" s="497">
+      <c r="N42" s="505">
         <v>26.32</v>
       </c>
-      <c r="O42" s="498">
+      <c r="O42" s="496">
         <v>31.58</v>
       </c>
-      <c r="P42" s="499">
+      <c r="P42" s="497">
         <v>32.43</v>
       </c>
-      <c r="Q42" s="505">
+      <c r="Q42" s="501">
         <v>24.32</v>
       </c>
-      <c r="R42" s="506">
+      <c r="R42" s="498">
         <v>29.73</v>
       </c>
-      <c r="S42" s="503">
+      <c r="S42" s="502">
         <v>18.92</v>
       </c>
-      <c r="T42" s="500">
+      <c r="T42" s="503">
         <v>51.28</v>
       </c>
     </row>
@@ -11189,40 +11189,40 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="517">
+      <c r="I43" s="513">
         <v>-0.38</v>
       </c>
-      <c r="J43" s="511">
+      <c r="J43" s="509">
         <v>-0.74</v>
       </c>
-      <c r="K43" s="518">
+      <c r="K43" s="510">
         <v>-2.11</v>
       </c>
-      <c r="L43" s="519">
+      <c r="L43" s="511">
         <v>-4.14</v>
       </c>
       <c r="M43" s="508">
         <v>-5.26</v>
       </c>
-      <c r="N43" s="514">
+      <c r="N43" s="518">
         <v>-6.6</v>
       </c>
-      <c r="O43" s="515">
+      <c r="O43" s="514">
         <v>-5.4</v>
       </c>
-      <c r="P43" s="512">
+      <c r="P43" s="519">
         <v>-6.06</v>
       </c>
-      <c r="Q43" s="509">
+      <c r="Q43" s="515">
         <v>-6.48</v>
       </c>
-      <c r="R43" s="510">
+      <c r="R43" s="516">
         <v>-5.55</v>
       </c>
-      <c r="S43" s="516">
+      <c r="S43" s="512">
         <v>-7.91</v>
       </c>
-      <c r="T43" s="513">
+      <c r="T43" s="517">
         <v>16.46</v>
       </c>
     </row>

--- a/youzi/申港广东分/index.xlsx
+++ b/youzi/申港广东分/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="521">
+  <fills count="523">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF4C3C8"/>
         <bgColor/>
       </patternFill>
@@ -57,13 +111,379 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,18 +495,294 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -99,91 +795,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,25 +987,307 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,13 +1299,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,43 +1323,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -291,61 +1473,391 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,61 +1869,499 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -429,7 +2379,421 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -441,7 +2805,355 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -451,2708 +3163,22 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="520">
+  <borders count="522">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6797,7 +6823,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="520">
+  <cellXfs count="522">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8354,6 +8380,12 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="519" fillId="520" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="520" fillId="521" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="521" fillId="522" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8698,7 +8730,7 @@
       <c r="C2" t="str">
         <v>603110</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="13" t="str">
         <v>净买: 1763.82万</v>
       </c>
       <c r="E2">
@@ -8713,41 +8745,41 @@
       <c r="H2">
         <v>9.98</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="4">
         <v>0</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="9">
         <v>9.98</v>
       </c>
       <c r="K2" s="5">
         <v>3.91</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="10">
         <v>1.47</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="6">
         <v>11.62</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="1">
         <v>22.79</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="7">
         <v>15.02</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="11">
         <v>26.53</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="2">
         <v>32.65</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="3">
         <v>28.74</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="12">
         <v>21.77</v>
       </c>
-      <c r="T2" s="4">
-        <v>0</v>
+      <c r="T2" s="8">
+        <v>2.15</v>
       </c>
     </row>
     <row r="3">
@@ -8760,7 +8792,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="20" t="str">
         <v>净买: 486.49万</v>
       </c>
       <c r="E3">
@@ -8775,41 +8807,41 @@
       <c r="H3">
         <v>6.6</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="22">
         <v>-11.36</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="14">
         <v>-13.44</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="21">
         <v>-4.79</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="15">
         <v>4.74</v>
       </c>
       <c r="M3" s="23">
         <v>-1.89</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="24">
         <v>7.93</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="16">
         <v>13.15</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="17">
         <v>9.82</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="18">
         <v>3.87</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="19">
         <v>6.53</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="25">
         <v>-4.11</v>
       </c>
-      <c r="T3" s="21">
-        <v>-14.7</v>
+      <c r="T3" s="26">
+        <v>-12.86</v>
       </c>
     </row>
     <row r="4">
@@ -8822,7 +8854,7 @@
       <c r="C4" t="str">
         <v>603881</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="35" t="str">
         <v>净买: 7242.53万</v>
       </c>
       <c r="E4">
@@ -8837,41 +8869,41 @@
       <c r="H4">
         <v>8.87</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="36">
         <v>1.04</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="31">
         <v>11.14</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="32">
         <v>0.03</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="33">
         <v>7.5</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="29">
         <v>8.74</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="30">
         <v>19.61</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="34">
         <v>25.9</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="39">
         <v>21.45</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="37">
         <v>15.56</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="27">
         <v>9.81</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="38">
         <v>-0.74</v>
       </c>
-      <c r="T4" s="35">
-        <v>21.21</v>
+      <c r="T4" s="28">
+        <v>16.95</v>
       </c>
     </row>
     <row r="5">
@@ -8884,7 +8916,7 @@
       <c r="C5" t="str">
         <v>603881</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="40" t="str">
         <v>净卖: -9194.30万</v>
       </c>
       <c r="E5">
@@ -8899,41 +8931,41 @@
       <c r="H5">
         <v>-4.56</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="46">
         <v>-5.7</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="49">
         <v>1.34</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="47">
         <v>2.51</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="41">
         <v>12.77</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="48">
         <v>18.69</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="42">
         <v>14.5</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="43">
         <v>8.94</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="44">
         <v>3.52</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="50">
         <v>-6.42</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="52">
         <v>-4.83</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="45">
         <v>-3.18</v>
       </c>
-      <c r="T5" s="49">
-        <v>14.27</v>
+      <c r="T5" s="51">
+        <v>10.25</v>
       </c>
     </row>
     <row r="6">
@@ -8961,41 +8993,41 @@
       <c r="H6">
         <v>5.63</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="53">
         <v>4.13</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="54">
         <v>14.56</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="60">
         <v>7.97</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="58">
         <v>-2.83</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="61">
         <v>-12.53</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="62">
         <v>-15.63</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="55">
         <v>-12.8</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="63">
         <v>-16.13</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="59">
         <v>-19.84</v>
       </c>
-      <c r="R6" s="63">
+      <c r="R6" s="56">
         <v>-20.37</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="57">
         <v>-19.6</v>
       </c>
       <c r="T6" s="64">
-        <v>-60.19</v>
+        <v>-60.05</v>
       </c>
     </row>
     <row r="7">
@@ -9008,7 +9040,7 @@
       <c r="C7" t="str">
         <v>600590</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="70" t="str">
         <v>净买: 1013.84万</v>
       </c>
       <c r="E7">
@@ -9023,41 +9055,41 @@
       <c r="H7">
         <v>10.05</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="73">
         <v>0</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="77">
         <v>-2.39</v>
       </c>
       <c r="K7" s="78">
         <v>7.39</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="67">
         <v>1.85</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="74">
         <v>1.63</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="66">
         <v>-5.76</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="68">
         <v>-3.48</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="75">
         <v>6.2</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="71">
         <v>16.85</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="72">
         <v>26.41</v>
       </c>
       <c r="S7" s="69">
         <v>21.74</v>
       </c>
-      <c r="T7" s="70">
-        <v>72.17</v>
+      <c r="T7" s="76">
+        <v>89.35</v>
       </c>
     </row>
     <row r="8">
@@ -9070,7 +9102,7 @@
       <c r="C8" t="str">
         <v>000818</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="85" t="str">
         <v>净卖: -5301.29万</v>
       </c>
       <c r="E8">
@@ -9085,41 +9117,41 @@
       <c r="H8">
         <v>-10</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="84">
         <v>0</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="88">
         <v>-9.99</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="79">
         <v>-13.17</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="89">
         <v>-10.26</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="80">
         <v>-13.69</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="90">
         <v>-17.51</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="81">
         <v>-18.06</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="82">
         <v>-17.26</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="86">
         <v>-14.79</v>
       </c>
       <c r="R8" s="83">
         <v>-16.85</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="91">
         <v>-14.02</v>
       </c>
-      <c r="T8" s="90">
-        <v>-59.03</v>
+      <c r="T8" s="87">
+        <v>-58.89</v>
       </c>
     </row>
     <row r="9">
@@ -9147,41 +9179,41 @@
       <c r="H9">
         <v>-9.5</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="101">
         <v>-0.54</v>
       </c>
-      <c r="J9" s="104">
+      <c r="J9" s="102">
         <v>0</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="92">
         <v>0.33</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="96">
         <v>3.33</v>
       </c>
       <c r="M9" s="97">
         <v>-7</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="98">
         <v>-1.67</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="103">
         <v>6.04</v>
       </c>
-      <c r="P9" s="93">
+      <c r="P9" s="99">
         <v>7.58</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="104">
         <v>12.71</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="93">
         <v>16.92</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="100">
         <v>12.79</v>
       </c>
-      <c r="T9" s="102">
-        <v>210.42</v>
+      <c r="T9" s="94">
+        <v>209.79</v>
       </c>
     </row>
     <row r="10">
@@ -9194,7 +9226,7 @@
       <c r="C10" t="str">
         <v>605300</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="109" t="str">
         <v>净买: 1145.88万</v>
       </c>
       <c r="E10">
@@ -9212,38 +9244,38 @@
       <c r="I10" s="110">
         <v>8.41</v>
       </c>
-      <c r="J10" s="115">
+      <c r="J10" s="105">
         <v>-2.41</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="106">
         <v>-12.18</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="115">
         <v>-15</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="111">
         <v>-12.88</v>
       </c>
-      <c r="N10" s="117">
+      <c r="N10" s="113">
         <v>-14.71</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="116">
         <v>-15.65</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="112">
         <v>-16.18</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="117">
         <v>-16.82</v>
       </c>
-      <c r="R10" s="109">
+      <c r="R10" s="107">
         <v>-18.35</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="114">
         <v>-15.18</v>
       </c>
-      <c r="T10" s="106">
-        <v>-35.76</v>
+      <c r="T10" s="108">
+        <v>-36</v>
       </c>
     </row>
     <row r="11">
@@ -9271,41 +9303,41 @@
       <c r="H11">
         <v>9.99</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="125">
         <v>0</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="123">
         <v>-9.16</v>
       </c>
-      <c r="K11" s="129">
+      <c r="K11" s="119">
         <v>-0.08</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="127">
         <v>0</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="128">
         <v>9.99</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="120">
         <v>-0.99</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="129">
         <v>8.93</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="130">
         <v>19.83</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="118">
         <v>12.16</v>
       </c>
-      <c r="R11" s="120">
+      <c r="R11" s="126">
         <v>23.38</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="124">
         <v>13.07</v>
       </c>
       <c r="T11" s="121">
-        <v>89.81</v>
+        <v>93.44</v>
       </c>
     </row>
     <row r="12">
@@ -9336,38 +9368,38 @@
       <c r="I12" s="143">
         <v>2.26</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="135">
         <v>4.81</v>
       </c>
-      <c r="K12" s="139">
+      <c r="K12" s="141">
         <v>2.62</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="136">
         <v>1.49</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="131">
         <v>0.85</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="138">
         <v>0.07</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="139">
         <v>-1.77</v>
       </c>
-      <c r="P12" s="135">
+      <c r="P12" s="132">
         <v>2.05</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="133">
         <v>0.85</v>
       </c>
-      <c r="R12" s="136">
+      <c r="R12" s="134">
         <v>0.21</v>
       </c>
       <c r="S12" s="137">
         <v>-0.92</v>
       </c>
-      <c r="T12" s="141">
-        <v>-22.72</v>
+      <c r="T12" s="140">
+        <v>-23</v>
       </c>
     </row>
     <row r="13">
@@ -9380,7 +9412,7 @@
       <c r="C13" t="str">
         <v>002114</v>
       </c>
-      <c r="D13" s="155" t="str">
+      <c r="D13" s="145" t="str">
         <v>净买: 1554.85万</v>
       </c>
       <c r="E13">
@@ -9395,41 +9427,41 @@
       <c r="H13">
         <v>9.83</v>
       </c>
-      <c r="I13" s="156">
+      <c r="I13" s="152">
         <v>0.13</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="153">
         <v>-1.41</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="146">
         <v>-4.6</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="147">
         <v>-6.65</v>
       </c>
-      <c r="M13" s="151">
+      <c r="M13" s="150">
         <v>-6.01</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="154">
         <v>-6.52</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="156">
         <v>-5.5</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="155">
         <v>-10.1</v>
       </c>
-      <c r="Q13" s="146">
+      <c r="Q13" s="151">
         <v>-9.59</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="148">
         <v>-10.87</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="149">
         <v>-11.76</v>
       </c>
-      <c r="T13" s="154">
-        <v>13.94</v>
+      <c r="T13" s="144">
+        <v>17.39</v>
       </c>
     </row>
     <row r="14">
@@ -9442,7 +9474,7 @@
       <c r="C14" t="str">
         <v>605303</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="161" t="str">
         <v>净买: 1578.26万</v>
       </c>
       <c r="E14">
@@ -9460,38 +9492,38 @@
       <c r="I14" s="168">
         <v>0</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="162">
         <v>-7.6</v>
       </c>
-      <c r="K14" s="160">
+      <c r="K14" s="169">
         <v>-13.68</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="159">
         <v>-20.06</v>
       </c>
-      <c r="M14" s="165">
+      <c r="M14" s="163">
         <v>-20.21</v>
       </c>
-      <c r="N14" s="161">
+      <c r="N14" s="164">
         <v>-21.58</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="165">
         <v>-22.87</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="157">
         <v>-23.86</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="166">
         <v>-24.62</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="167">
         <v>-27.13</v>
       </c>
-      <c r="S14" s="157">
+      <c r="S14" s="160">
         <v>-26.6</v>
       </c>
-      <c r="T14" s="163">
-        <v>85.71</v>
+      <c r="T14" s="158">
+        <v>72.95</v>
       </c>
     </row>
     <row r="15">
@@ -9504,7 +9536,7 @@
       <c r="C15" t="str">
         <v>605303</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="180" t="str">
         <v>净卖: -1462.35万</v>
       </c>
       <c r="E15">
@@ -9519,41 +9551,41 @@
       <c r="H15">
         <v>-2.55</v>
       </c>
-      <c r="I15" s="180">
+      <c r="I15" s="173">
         <v>-4.97</v>
       </c>
       <c r="J15" s="174">
         <v>-5.15</v>
       </c>
-      <c r="K15" s="177">
+      <c r="K15" s="181">
         <v>-6.78</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="182">
         <v>-8.31</v>
       </c>
       <c r="M15" s="175">
         <v>-9.49</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="170">
         <v>-10.39</v>
       </c>
-      <c r="O15" s="181">
+      <c r="O15" s="171">
         <v>-13.37</v>
       </c>
       <c r="P15" s="178">
         <v>-12.74</v>
       </c>
-      <c r="Q15" s="182">
+      <c r="Q15" s="176">
         <v>-14.27</v>
       </c>
-      <c r="R15" s="176">
+      <c r="R15" s="177">
         <v>-15.54</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="172">
         <v>-16.71</v>
       </c>
-      <c r="T15" s="170">
-        <v>120.78</v>
+      <c r="T15" s="179">
+        <v>105.6</v>
       </c>
     </row>
     <row r="16">
@@ -9566,7 +9598,7 @@
       <c r="C16" t="str">
         <v>600301</v>
       </c>
-      <c r="D16" s="186" t="str">
+      <c r="D16" s="189" t="str">
         <v>净卖: -3080.81万</v>
       </c>
       <c r="E16">
@@ -9581,41 +9613,41 @@
       <c r="H16">
         <v>-2.8</v>
       </c>
-      <c r="I16" s="187">
+      <c r="I16" s="190">
         <v>-4.62</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="185">
         <v>-5.96</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="192">
         <v>-4.88</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="193">
         <v>-5.27</v>
       </c>
-      <c r="M16" s="189">
+      <c r="M16" s="186">
         <v>-3.31</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="194">
         <v>-7.19</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="195">
         <v>-7.88</v>
       </c>
-      <c r="P16" s="194">
+      <c r="P16" s="183">
         <v>-7.88</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="187">
         <v>-10.35</v>
       </c>
-      <c r="R16" s="190">
+      <c r="R16" s="184">
         <v>-11.15</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="188">
         <v>-14.38</v>
       </c>
       <c r="T16" s="191">
-        <v>94.27</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="17">
@@ -9628,7 +9660,7 @@
       <c r="C17" t="str">
         <v>000815</v>
       </c>
-      <c r="D17" s="204" t="str">
+      <c r="D17" s="198" t="str">
         <v>净买: 5327.66万</v>
       </c>
       <c r="E17">
@@ -9643,41 +9675,41 @@
       <c r="H17">
         <v>2.39</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="201">
         <v>2.95</v>
       </c>
-      <c r="J17" s="201">
+      <c r="J17" s="199">
         <v>-3.14</v>
       </c>
-      <c r="K17" s="196">
+      <c r="K17" s="206">
         <v>-4.8</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="203">
         <v>-6.52</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="200">
         <v>-12.98</v>
       </c>
-      <c r="N17" s="205">
+      <c r="N17" s="204">
         <v>-17.22</v>
       </c>
-      <c r="O17" s="199">
+      <c r="O17" s="207">
         <v>-16.91</v>
       </c>
-      <c r="P17" s="206">
+      <c r="P17" s="208">
         <v>-20.79</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="196">
         <v>-20.3</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="205">
         <v>-19.74</v>
       </c>
-      <c r="S17" s="207">
+      <c r="S17" s="197">
         <v>-20.85</v>
       </c>
-      <c r="T17" s="208">
-        <v>32.84</v>
+      <c r="T17" s="202">
+        <v>34.99</v>
       </c>
     </row>
     <row r="18">
@@ -9690,7 +9722,7 @@
       <c r="C18" t="str">
         <v>603315</v>
       </c>
-      <c r="D18" s="218" t="str">
+      <c r="D18" s="209" t="str">
         <v>净买: 2006.31万</v>
       </c>
       <c r="E18">
@@ -9705,41 +9737,41 @@
       <c r="H18">
         <v>10.03</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="213">
         <v>0</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="210">
         <v>9.99</v>
       </c>
-      <c r="K18" s="220">
+      <c r="K18" s="214">
         <v>20.99</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="216">
         <v>8.87</v>
       </c>
-      <c r="M18" s="213">
+      <c r="M18" s="211">
         <v>-2</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="219">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="211">
+      <c r="O18" s="215">
         <v>-12.8</v>
       </c>
-      <c r="P18" s="212">
+      <c r="P18" s="217">
         <v>-17.49</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="218">
         <v>-18.11</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="220">
         <v>-16.36</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="212">
         <v>-16.55</v>
       </c>
-      <c r="T18" s="209">
-        <v>15.68</v>
+      <c r="T18" s="221">
+        <v>9.93</v>
       </c>
     </row>
     <row r="19">
@@ -9752,7 +9784,7 @@
       <c r="C19" t="str">
         <v>603315</v>
       </c>
-      <c r="D19" s="222" t="str">
+      <c r="D19" s="234" t="str">
         <v>净卖: -2227.67万</v>
       </c>
       <c r="E19">
@@ -9767,41 +9799,41 @@
       <c r="H19">
         <v>-4.2</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="226">
         <v>14.82</v>
       </c>
-      <c r="J19" s="229">
+      <c r="J19" s="230">
         <v>3.32</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="227">
         <v>-6.99</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="231">
         <v>-16.3</v>
       </c>
-      <c r="M19" s="227">
+      <c r="M19" s="222">
         <v>-17.25</v>
       </c>
-      <c r="N19" s="224">
+      <c r="N19" s="228">
         <v>-21.7</v>
       </c>
-      <c r="O19" s="231">
+      <c r="O19" s="223">
         <v>-22.29</v>
       </c>
-      <c r="P19" s="228">
+      <c r="P19" s="232">
         <v>-20.63</v>
       </c>
-      <c r="Q19" s="225">
+      <c r="Q19" s="224">
         <v>-20.81</v>
       </c>
-      <c r="R19" s="232">
+      <c r="R19" s="233">
         <v>-20.09</v>
       </c>
-      <c r="S19" s="234">
+      <c r="S19" s="225">
         <v>-22.05</v>
       </c>
-      <c r="T19" s="233">
-        <v>9.78</v>
+      <c r="T19" s="229">
+        <v>4.33</v>
       </c>
     </row>
     <row r="20">
@@ -9814,7 +9846,7 @@
       <c r="C20" t="str">
         <v>000737</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="236" t="str">
         <v>净买: 2607.05万</v>
       </c>
       <c r="E20">
@@ -9829,41 +9861,41 @@
       <c r="H20">
         <v>0.79</v>
       </c>
-      <c r="I20" s="244">
+      <c r="I20" s="237">
         <v>9.19</v>
       </c>
-      <c r="J20" s="239">
+      <c r="J20" s="245">
         <v>15.54</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="241">
         <v>20.43</v>
       </c>
-      <c r="L20" s="245">
+      <c r="L20" s="246">
         <v>11.93</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="242">
         <v>4.79</v>
       </c>
-      <c r="N20" s="240">
+      <c r="N20" s="247">
         <v>2.64</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="243">
         <v>2.83</v>
       </c>
-      <c r="P20" s="246">
+      <c r="P20" s="238">
         <v>1.08</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="240">
         <v>-2.15</v>
       </c>
-      <c r="R20" s="243">
+      <c r="R20" s="244">
         <v>-11.93</v>
       </c>
-      <c r="S20" s="236">
+      <c r="S20" s="235">
         <v>-19.65</v>
       </c>
-      <c r="T20" s="238">
-        <v>38.03</v>
+      <c r="T20" s="239">
+        <v>38.51</v>
       </c>
     </row>
     <row r="21">
@@ -9876,7 +9908,7 @@
       <c r="C21" t="str">
         <v>000779</v>
       </c>
-      <c r="D21" s="252" t="str">
+      <c r="D21" s="253" t="str">
         <v>净买: 1464.90万</v>
       </c>
       <c r="E21">
@@ -9891,41 +9923,41 @@
       <c r="H21">
         <v>9.36</v>
       </c>
-      <c r="I21" s="259">
+      <c r="I21" s="254">
         <v>-14.36</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="257">
         <v>-22.92</v>
       </c>
-      <c r="K21" s="254">
+      <c r="K21" s="260">
         <v>-25.67</v>
       </c>
-      <c r="L21" s="260">
+      <c r="L21" s="258">
         <v>-28.8</v>
       </c>
-      <c r="M21" s="248">
+      <c r="M21" s="259">
         <v>-29.11</v>
       </c>
-      <c r="N21" s="255">
+      <c r="N21" s="248">
         <v>-26.05</v>
       </c>
-      <c r="O21" s="256">
+      <c r="O21" s="255">
         <v>-28.27</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="252">
         <v>-29.03</v>
       </c>
-      <c r="Q21" s="258">
+      <c r="Q21" s="249">
         <v>-29.95</v>
       </c>
-      <c r="R21" s="249">
+      <c r="R21" s="250">
         <v>-36.97</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="251">
         <v>-35.91</v>
       </c>
-      <c r="T21" s="251">
-        <v>-33.16</v>
+      <c r="T21" s="256">
+        <v>-32.93</v>
       </c>
     </row>
     <row r="22">
@@ -9938,7 +9970,7 @@
       <c r="C22" t="str">
         <v>600727</v>
       </c>
-      <c r="D22" s="273" t="str">
+      <c r="D22" s="267" t="str">
         <v>净卖: -2220.75万</v>
       </c>
       <c r="E22">
@@ -9953,41 +9985,41 @@
       <c r="H22">
         <v>4.31</v>
       </c>
-      <c r="I22" s="261">
+      <c r="I22" s="262">
         <v>-1.31</v>
       </c>
-      <c r="J22" s="262">
+      <c r="J22" s="271">
         <v>0.76</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="268">
         <v>-9.36</v>
       </c>
-      <c r="L22" s="263">
+      <c r="L22" s="269">
         <v>-13.71</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="270">
         <v>-11.32</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="272">
         <v>-12.08</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="263">
         <v>-7.51</v>
       </c>
-      <c r="P22" s="267">
+      <c r="P22" s="273">
         <v>-16.76</v>
       </c>
-      <c r="Q22" s="268">
+      <c r="Q22" s="264">
         <v>-15.13</v>
       </c>
-      <c r="R22" s="269">
+      <c r="R22" s="265">
         <v>-16.76</v>
       </c>
-      <c r="S22" s="272">
+      <c r="S22" s="266">
         <v>-15.67</v>
       </c>
-      <c r="T22" s="270">
-        <v>-16.32</v>
+      <c r="T22" s="261">
+        <v>-15.13</v>
       </c>
     </row>
     <row r="23">
@@ -10000,7 +10032,7 @@
       <c r="C23" t="str">
         <v>001217</v>
       </c>
-      <c r="D23" s="283" t="str">
+      <c r="D23" s="282" t="str">
         <v>净买: 3127.44万</v>
       </c>
       <c r="E23">
@@ -10015,41 +10047,41 @@
       <c r="H23">
         <v>9.99</v>
       </c>
-      <c r="I23" s="284">
+      <c r="I23" s="278">
         <v>0</v>
       </c>
-      <c r="J23" s="285">
+      <c r="J23" s="279">
         <v>-8.55</v>
       </c>
-      <c r="K23" s="286">
+      <c r="K23" s="283">
         <v>-13.73</v>
       </c>
-      <c r="L23" s="274">
+      <c r="L23" s="286">
         <v>-17.5</v>
       </c>
-      <c r="M23" s="275">
+      <c r="M23" s="276">
         <v>-20.66</v>
       </c>
-      <c r="N23" s="276">
+      <c r="N23" s="284">
         <v>-28.6</v>
       </c>
-      <c r="O23" s="279">
+      <c r="O23" s="274">
         <v>-31.02</v>
       </c>
-      <c r="P23" s="281">
+      <c r="P23" s="280">
         <v>-31.09</v>
       </c>
-      <c r="Q23" s="277">
+      <c r="Q23" s="275">
         <v>-29.48</v>
       </c>
-      <c r="R23" s="278">
+      <c r="R23" s="277">
         <v>-28.33</v>
       </c>
-      <c r="S23" s="280">
+      <c r="S23" s="285">
         <v>-26.72</v>
       </c>
-      <c r="T23" s="282">
-        <v>-21.13</v>
+      <c r="T23" s="281">
+        <v>-20.05</v>
       </c>
     </row>
     <row r="24">
@@ -10077,40 +10109,40 @@
       <c r="H24">
         <v>-3.3</v>
       </c>
-      <c r="I24" s="297">
+      <c r="I24" s="292">
         <v>-6.9</v>
       </c>
-      <c r="J24" s="298">
+      <c r="J24" s="293">
         <v>-8.84</v>
       </c>
-      <c r="K24" s="293">
+      <c r="K24" s="299">
         <v>-7.5</v>
       </c>
-      <c r="L24" s="288">
+      <c r="L24" s="289">
         <v>-7.64</v>
       </c>
-      <c r="M24" s="289">
+      <c r="M24" s="295">
         <v>-12.93</v>
       </c>
-      <c r="N24" s="294">
+      <c r="N24" s="290">
         <v>-21.63</v>
       </c>
-      <c r="O24" s="295">
+      <c r="O24" s="296">
         <v>-20.23</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="294">
         <v>-21.57</v>
       </c>
-      <c r="Q24" s="299">
+      <c r="Q24" s="287">
         <v>-20.09</v>
       </c>
-      <c r="R24" s="292">
+      <c r="R24" s="297">
         <v>-20.03</v>
       </c>
-      <c r="S24" s="287">
+      <c r="S24" s="298">
         <v>-17.62</v>
       </c>
-      <c r="T24" s="296">
+      <c r="T24" s="288">
         <v>6.03</v>
       </c>
     </row>
@@ -10124,7 +10156,7 @@
       <c r="C25" t="str">
         <v>001333</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="301" t="str">
         <v>净买: 1650.82万</v>
       </c>
       <c r="E25">
@@ -10139,41 +10171,41 @@
       <c r="H25">
         <v>-1.88</v>
       </c>
-      <c r="I25" s="306">
+      <c r="I25" s="305">
         <v>12.11</v>
       </c>
-      <c r="J25" s="300">
+      <c r="J25" s="309">
         <v>23.33</v>
       </c>
-      <c r="K25" s="301">
+      <c r="K25" s="310">
         <v>11.01</v>
       </c>
-      <c r="L25" s="303">
+      <c r="L25" s="306">
         <v>-0.08</v>
       </c>
-      <c r="M25" s="307">
+      <c r="M25" s="302">
         <v>-10.07</v>
       </c>
-      <c r="N25" s="302">
+      <c r="N25" s="311">
         <v>-18.1</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="303">
         <v>-17.47</v>
       </c>
-      <c r="P25" s="309">
+      <c r="P25" s="312">
         <v>-15.81</v>
       </c>
       <c r="Q25" s="304">
         <v>-10.96</v>
       </c>
-      <c r="R25" s="310">
+      <c r="R25" s="307">
         <v>-8.75</v>
       </c>
-      <c r="S25" s="311">
+      <c r="S25" s="308">
         <v>-10.28</v>
       </c>
-      <c r="T25" s="312">
-        <v>5.65</v>
+      <c r="T25" s="300">
+        <v>6.16</v>
       </c>
     </row>
     <row r="26">
@@ -10186,7 +10218,7 @@
       <c r="C26" t="str">
         <v>002365</v>
       </c>
-      <c r="D26" s="314" t="str">
+      <c r="D26" s="313" t="str">
         <v>净卖: -918.91万</v>
       </c>
       <c r="E26">
@@ -10201,41 +10233,41 @@
       <c r="H26">
         <v>-8.32</v>
       </c>
-      <c r="I26" s="321">
+      <c r="I26" s="314">
         <v>20.02</v>
       </c>
-      <c r="J26" s="322">
+      <c r="J26" s="316">
         <v>15.9</v>
       </c>
-      <c r="K26" s="318">
+      <c r="K26" s="317">
         <v>22.97</v>
       </c>
-      <c r="L26" s="315">
+      <c r="L26" s="323">
         <v>19.43</v>
       </c>
-      <c r="M26" s="316">
+      <c r="M26" s="318">
         <v>16.02</v>
       </c>
-      <c r="N26" s="323">
+      <c r="N26" s="319">
         <v>10.37</v>
       </c>
-      <c r="O26" s="324">
+      <c r="O26" s="320">
         <v>9.42</v>
       </c>
-      <c r="P26" s="317">
+      <c r="P26" s="324">
         <v>11.66</v>
       </c>
-      <c r="Q26" s="325">
+      <c r="Q26" s="315">
         <v>6.24</v>
       </c>
-      <c r="R26" s="313">
+      <c r="R26" s="325">
         <v>16.84</v>
       </c>
-      <c r="S26" s="319">
+      <c r="S26" s="321">
         <v>20.49</v>
       </c>
-      <c r="T26" s="320">
-        <v>60.66</v>
+      <c r="T26" s="322">
+        <v>61.13</v>
       </c>
     </row>
     <row r="27">
@@ -10248,7 +10280,7 @@
       <c r="C27" t="str">
         <v>600180</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="329" t="str">
         <v>净卖: -1973.71万</v>
       </c>
       <c r="E27">
@@ -10263,41 +10295,41 @@
       <c r="H27">
         <v>-4.9</v>
       </c>
-      <c r="I27" s="332">
+      <c r="I27" s="330">
         <v>0.21</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="331">
         <v>-1.93</v>
       </c>
-      <c r="K27" s="337">
+      <c r="K27" s="332">
         <v>-3.86</v>
       </c>
-      <c r="L27" s="328">
+      <c r="L27" s="337">
         <v>-2.58</v>
       </c>
-      <c r="M27" s="329">
+      <c r="M27" s="333">
         <v>-1.5</v>
       </c>
-      <c r="N27" s="336">
+      <c r="N27" s="338">
         <v>-3.43</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="326">
         <v>-5.79</v>
       </c>
-      <c r="P27" s="338">
+      <c r="P27" s="334">
         <v>-4.94</v>
       </c>
-      <c r="Q27" s="326">
+      <c r="Q27" s="327">
         <v>-8.58</v>
       </c>
-      <c r="R27" s="327">
+      <c r="R27" s="335">
         <v>-7.73</v>
       </c>
-      <c r="S27" s="330">
+      <c r="S27" s="328">
         <v>-8.37</v>
       </c>
-      <c r="T27" s="331">
-        <v>-30.9</v>
+      <c r="T27" s="336">
+        <v>-31.33</v>
       </c>
     </row>
     <row r="28">
@@ -10310,7 +10342,7 @@
       <c r="C28" t="str">
         <v>002743</v>
       </c>
-      <c r="D28" s="343" t="str">
+      <c r="D28" s="350" t="str">
         <v>净卖: -345.80万</v>
       </c>
       <c r="E28">
@@ -10325,41 +10357,41 @@
       <c r="H28">
         <v>-9.98</v>
       </c>
-      <c r="I28" s="339">
+      <c r="I28" s="351">
         <v>0</v>
       </c>
-      <c r="J28" s="344">
+      <c r="J28" s="342">
         <v>-5.83</v>
       </c>
-      <c r="K28" s="347">
+      <c r="K28" s="346">
         <v>-3.38</v>
       </c>
-      <c r="L28" s="348">
+      <c r="L28" s="339">
         <v>0.75</v>
       </c>
-      <c r="M28" s="345">
+      <c r="M28" s="343">
         <v>1.88</v>
       </c>
-      <c r="N28" s="349">
+      <c r="N28" s="340">
         <v>3.01</v>
       </c>
-      <c r="O28" s="350">
+      <c r="O28" s="347">
         <v>3.95</v>
       </c>
-      <c r="P28" s="341">
+      <c r="P28" s="344">
         <v>0.75</v>
       </c>
-      <c r="Q28" s="342">
+      <c r="Q28" s="348">
         <v>-0.19</v>
       </c>
-      <c r="R28" s="340">
+      <c r="R28" s="349">
         <v>1.5</v>
       </c>
-      <c r="S28" s="351">
+      <c r="S28" s="341">
         <v>5.83</v>
       </c>
-      <c r="T28" s="346">
-        <v>0</v>
+      <c r="T28" s="345">
+        <v>0.19</v>
       </c>
     </row>
     <row r="29">
@@ -10372,7 +10404,7 @@
       <c r="C29" t="str">
         <v>600173</v>
       </c>
-      <c r="D29" s="354" t="str">
+      <c r="D29" s="358" t="str">
         <v>净卖: -1818.07万</v>
       </c>
       <c r="E29">
@@ -10387,41 +10419,41 @@
       <c r="H29">
         <v>-1.2</v>
       </c>
-      <c r="I29" s="361">
+      <c r="I29" s="359">
         <v>-8.91</v>
       </c>
-      <c r="J29" s="362">
+      <c r="J29" s="363">
         <v>0.2</v>
       </c>
-      <c r="K29" s="363">
+      <c r="K29" s="360">
         <v>4.45</v>
       </c>
-      <c r="L29" s="359">
+      <c r="L29" s="354">
         <v>-2.94</v>
       </c>
-      <c r="M29" s="355">
+      <c r="M29" s="361">
         <v>-7.89</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="364">
         <v>-12.45</v>
       </c>
       <c r="O29" s="352">
         <v>-11.84</v>
       </c>
-      <c r="P29" s="353">
+      <c r="P29" s="355">
         <v>-8.1</v>
       </c>
-      <c r="Q29" s="360">
+      <c r="Q29" s="356">
         <v>-5.36</v>
       </c>
       <c r="R29" s="357">
         <v>-2.53</v>
       </c>
-      <c r="S29" s="358">
+      <c r="S29" s="362">
         <v>-3.54</v>
       </c>
-      <c r="T29" s="364">
-        <v>-19.13</v>
+      <c r="T29" s="353">
+        <v>-22.27</v>
       </c>
     </row>
     <row r="30">
@@ -10434,7 +10466,7 @@
       <c r="C30" t="str">
         <v>000637</v>
       </c>
-      <c r="D30" s="368" t="str">
+      <c r="D30" s="369" t="str">
         <v>净卖: -692.69万</v>
       </c>
       <c r="E30">
@@ -10449,41 +10481,41 @@
       <c r="H30">
         <v>-4.62</v>
       </c>
-      <c r="I30" s="369">
+      <c r="I30" s="365">
         <v>-5.65</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="370">
         <v>3.83</v>
       </c>
-      <c r="K30" s="370">
+      <c r="K30" s="376">
         <v>-0.81</v>
       </c>
-      <c r="L30" s="376">
+      <c r="L30" s="371">
         <v>0.6</v>
       </c>
-      <c r="M30" s="377">
+      <c r="M30" s="372">
         <v>-2.02</v>
       </c>
-      <c r="N30" s="371">
+      <c r="N30" s="366">
         <v>-6.25</v>
       </c>
-      <c r="O30" s="372">
+      <c r="O30" s="367">
         <v>-4.84</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="374">
         <v>-4.23</v>
       </c>
       <c r="Q30" s="375">
         <v>-3.43</v>
       </c>
-      <c r="R30" s="365">
+      <c r="R30" s="368">
         <v>-0.81</v>
       </c>
-      <c r="S30" s="366">
+      <c r="S30" s="373">
         <v>-1.01</v>
       </c>
-      <c r="T30" s="367">
-        <v>-12.3</v>
+      <c r="T30" s="377">
+        <v>-11.69</v>
       </c>
     </row>
     <row r="31">
@@ -10496,7 +10528,7 @@
       <c r="C31" t="str">
         <v>003038</v>
       </c>
-      <c r="D31" s="383" t="str">
+      <c r="D31" s="390" t="str">
         <v>净买: 1673.87万</v>
       </c>
       <c r="E31">
@@ -10511,41 +10543,41 @@
       <c r="H31">
         <v>-3.7</v>
       </c>
-      <c r="I31" s="384">
+      <c r="I31" s="387">
         <v>-1.79</v>
       </c>
-      <c r="J31" s="390">
+      <c r="J31" s="384">
         <v>-1.79</v>
       </c>
-      <c r="K31" s="378">
+      <c r="K31" s="388">
         <v>-7.21</v>
       </c>
-      <c r="L31" s="388">
+      <c r="L31" s="381">
         <v>-9</v>
       </c>
-      <c r="M31" s="389">
+      <c r="M31" s="378">
         <v>-11.53</v>
       </c>
       <c r="N31" s="385">
         <v>-10.42</v>
       </c>
-      <c r="O31" s="379">
+      <c r="O31" s="386">
         <v>-9.79</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="382">
         <v>-11.32</v>
       </c>
-      <c r="Q31" s="382">
+      <c r="Q31" s="389">
         <v>-11.26</v>
       </c>
-      <c r="R31" s="386">
+      <c r="R31" s="383">
         <v>-9.89</v>
       </c>
-      <c r="S31" s="380">
+      <c r="S31" s="379">
         <v>-11.89</v>
       </c>
-      <c r="T31" s="387">
-        <v>-20.47</v>
+      <c r="T31" s="380">
+        <v>-20.32</v>
       </c>
     </row>
     <row r="32">
@@ -10558,7 +10590,7 @@
       <c r="C32" t="str">
         <v>300390</v>
       </c>
-      <c r="D32" s="393" t="str">
+      <c r="D32" s="397" t="str">
         <v>净卖: -2712.20万</v>
       </c>
       <c r="E32">
@@ -10573,41 +10605,41 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="397">
+      <c r="I32" s="401">
         <v>15.32</v>
       </c>
-      <c r="J32" s="403">
+      <c r="J32" s="400">
         <v>19.24</v>
       </c>
-      <c r="K32" s="398">
+      <c r="K32" s="402">
         <v>21.18</v>
       </c>
-      <c r="L32" s="399">
+      <c r="L32" s="403">
         <v>17.01</v>
       </c>
-      <c r="M32" s="400">
+      <c r="M32" s="394">
         <v>39.41</v>
       </c>
-      <c r="N32" s="401">
+      <c r="N32" s="395">
         <v>44.54</v>
       </c>
-      <c r="O32" s="394">
+      <c r="O32" s="391">
         <v>73.45</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="398">
         <v>64.28</v>
       </c>
-      <c r="Q32" s="402">
+      <c r="Q32" s="392">
         <v>66.69</v>
       </c>
-      <c r="R32" s="395">
+      <c r="R32" s="393">
         <v>76.84</v>
       </c>
       <c r="S32" s="396">
         <v>41.99</v>
       </c>
-      <c r="T32" s="392">
-        <v>154.76</v>
+      <c r="T32" s="399">
+        <v>151.33</v>
       </c>
     </row>
     <row r="33">
@@ -10620,7 +10652,7 @@
       <c r="C33" t="str">
         <v>603829</v>
       </c>
-      <c r="D33" s="405" t="str">
+      <c r="D33" s="413" t="str">
         <v>净卖: -2484.77万</v>
       </c>
       <c r="E33">
@@ -10635,41 +10667,41 @@
       <c r="H33">
         <v>0.16</v>
       </c>
-      <c r="I33" s="412">
+      <c r="I33" s="414">
         <v>-10.16</v>
       </c>
-      <c r="J33" s="408">
+      <c r="J33" s="415">
         <v>-9.96</v>
       </c>
-      <c r="K33" s="413">
+      <c r="K33" s="416">
         <v>-18.94</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="408">
         <v>-22.65</v>
       </c>
       <c r="M33" s="409">
         <v>-22.75</v>
       </c>
-      <c r="N33" s="414">
+      <c r="N33" s="404">
         <v>-25.3</v>
       </c>
-      <c r="O33" s="406">
+      <c r="O33" s="410">
         <v>-26.94</v>
       </c>
-      <c r="P33" s="410">
+      <c r="P33" s="405">
         <v>-27.14</v>
       </c>
-      <c r="Q33" s="415">
+      <c r="Q33" s="412">
         <v>-26.97</v>
       </c>
-      <c r="R33" s="407">
+      <c r="R33" s="406">
         <v>-27.01</v>
       </c>
-      <c r="S33" s="411">
+      <c r="S33" s="407">
         <v>-25.4</v>
       </c>
-      <c r="T33" s="416">
-        <v>-4.23</v>
+      <c r="T33" s="411">
+        <v>-2.92</v>
       </c>
     </row>
     <row r="34">
@@ -10682,7 +10714,7 @@
       <c r="C34" t="str">
         <v>603829</v>
       </c>
-      <c r="D34" s="429" t="str">
+      <c r="D34" s="428" t="str">
         <v>净卖: -2802.75万</v>
       </c>
       <c r="E34">
@@ -10697,41 +10729,41 @@
       <c r="H34">
         <v>0.15</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="418">
         <v>-10.11</v>
       </c>
-      <c r="J34" s="426">
+      <c r="J34" s="419">
         <v>-14.21</v>
       </c>
-      <c r="K34" s="427">
+      <c r="K34" s="422">
         <v>-14.32</v>
       </c>
-      <c r="L34" s="422">
+      <c r="L34" s="423">
         <v>-17.16</v>
       </c>
-      <c r="M34" s="424">
+      <c r="M34" s="429">
         <v>-18.97</v>
       </c>
-      <c r="N34" s="418">
+      <c r="N34" s="425">
         <v>-19.19</v>
       </c>
-      <c r="O34" s="419">
+      <c r="O34" s="426">
         <v>-19.01</v>
       </c>
-      <c r="P34" s="423">
+      <c r="P34" s="417">
         <v>-19.05</v>
       </c>
       <c r="Q34" s="420">
         <v>-17.27</v>
       </c>
-      <c r="R34" s="425">
+      <c r="R34" s="421">
         <v>-15.92</v>
       </c>
-      <c r="S34" s="421">
+      <c r="S34" s="424">
         <v>-14.76</v>
       </c>
-      <c r="T34" s="428">
-        <v>6.22</v>
+      <c r="T34" s="427">
+        <v>7.67</v>
       </c>
     </row>
     <row r="35">
@@ -10759,37 +10791,37 @@
       <c r="H35">
         <v>-8.89</v>
       </c>
-      <c r="I35" s="434">
+      <c r="I35" s="439">
         <v>-21.22</v>
       </c>
-      <c r="J35" s="435">
+      <c r="J35" s="441">
         <v>-19.61</v>
       </c>
-      <c r="K35" s="440">
+      <c r="K35" s="442">
         <v>-23.32</v>
       </c>
-      <c r="L35" s="441">
+      <c r="L35" s="434">
         <v>-23.12</v>
       </c>
-      <c r="M35" s="438">
+      <c r="M35" s="430">
         <v>-27.46</v>
       </c>
-      <c r="N35" s="431">
+      <c r="N35" s="435">
         <v>-27.71</v>
       </c>
       <c r="O35" s="436">
         <v>-26.34</v>
       </c>
-      <c r="P35" s="439">
+      <c r="P35" s="437">
         <v>-23.22</v>
       </c>
-      <c r="Q35" s="437">
+      <c r="Q35" s="438">
         <v>-26.44</v>
       </c>
-      <c r="R35" s="442">
+      <c r="R35" s="431">
         <v>-27.12</v>
       </c>
-      <c r="S35" s="430">
+      <c r="S35" s="440">
         <v>-26.68</v>
       </c>
       <c r="T35" s="432">
@@ -10806,7 +10838,7 @@
       <c r="C36" t="str">
         <v>920427</v>
       </c>
-      <c r="D36" s="452" t="str">
+      <c r="D36" s="450" t="str">
         <v>净卖: -130.63万</v>
       </c>
       <c r="E36">
@@ -10821,40 +10853,40 @@
       <c r="H36">
         <v>-4.33</v>
       </c>
-      <c r="I36" s="453">
+      <c r="I36" s="445">
         <v>6.67</v>
       </c>
-      <c r="J36" s="454">
+      <c r="J36" s="448">
         <v>1.75</v>
       </c>
-      <c r="K36" s="450">
+      <c r="K36" s="453">
         <v>2.01</v>
       </c>
-      <c r="L36" s="447">
+      <c r="L36" s="446">
         <v>-3.75</v>
       </c>
-      <c r="M36" s="455">
+      <c r="M36" s="451">
         <v>-4.08</v>
       </c>
-      <c r="N36" s="443">
+      <c r="N36" s="454">
         <v>-2.27</v>
       </c>
-      <c r="O36" s="444">
+      <c r="O36" s="452">
         <v>1.88</v>
       </c>
-      <c r="P36" s="445">
+      <c r="P36" s="455">
         <v>-2.39</v>
       </c>
-      <c r="Q36" s="451">
+      <c r="Q36" s="443">
         <v>-3.3</v>
       </c>
-      <c r="R36" s="449">
+      <c r="R36" s="447">
         <v>-2.72</v>
       </c>
-      <c r="S36" s="448">
+      <c r="S36" s="449">
         <v>-6.54</v>
       </c>
-      <c r="T36" s="446">
+      <c r="T36" s="444">
         <v>-18.25</v>
       </c>
     </row>
@@ -10868,7 +10900,7 @@
       <c r="C37" t="str">
         <v>603798</v>
       </c>
-      <c r="D37" s="468" t="str">
+      <c r="D37" s="467" t="str">
         <v>净卖: -286.39万</v>
       </c>
       <c r="E37">
@@ -10883,41 +10915,41 @@
       <c r="H37">
         <v>-9.99</v>
       </c>
-      <c r="I37" s="464">
+      <c r="I37" s="461">
         <v>0</v>
       </c>
-      <c r="J37" s="465">
+      <c r="J37" s="462">
         <v>-5.52</v>
       </c>
-      <c r="K37" s="466">
+      <c r="K37" s="468">
         <v>-0.12</v>
       </c>
       <c r="L37" s="456">
         <v>-0.72</v>
       </c>
-      <c r="M37" s="459">
+      <c r="M37" s="457">
         <v>-6.3</v>
       </c>
-      <c r="N37" s="457">
+      <c r="N37" s="465">
         <v>-2.82</v>
       </c>
-      <c r="O37" s="460">
+      <c r="O37" s="459">
         <v>-3.3</v>
       </c>
-      <c r="P37" s="461">
+      <c r="P37" s="463">
         <v>-5.34</v>
       </c>
-      <c r="Q37" s="467">
+      <c r="Q37" s="466">
         <v>-4.92</v>
       </c>
-      <c r="R37" s="462">
+      <c r="R37" s="458">
         <v>0.72</v>
       </c>
-      <c r="S37" s="458">
+      <c r="S37" s="460">
         <v>-4.08</v>
       </c>
-      <c r="T37" s="463">
-        <v>0.54</v>
+      <c r="T37" s="464">
+        <v>1.5</v>
       </c>
     </row>
     <row r="38">
@@ -10930,7 +10962,7 @@
       <c r="C38" t="str">
         <v>603291</v>
       </c>
-      <c r="D38" s="476" t="str">
+      <c r="D38" s="472" t="str">
         <v>净买: 465.04万</v>
       </c>
       <c r="E38">
@@ -10945,41 +10977,41 @@
       <c r="H38">
         <v>1.97</v>
       </c>
-      <c r="I38" s="477">
+      <c r="I38" s="476">
         <v>-11.73</v>
       </c>
-      <c r="J38" s="471">
+      <c r="J38" s="473">
         <v>-11.73</v>
       </c>
-      <c r="K38" s="474">
+      <c r="K38" s="481">
         <v>-15.59</v>
       </c>
-      <c r="L38" s="478">
+      <c r="L38" s="477">
         <v>-15.51</v>
       </c>
-      <c r="M38" s="472">
+      <c r="M38" s="469">
         <v>-14.97</v>
       </c>
-      <c r="N38" s="469">
+      <c r="N38" s="471">
         <v>-15.66</v>
       </c>
-      <c r="O38" s="479">
+      <c r="O38" s="478">
         <v>-15.82</v>
       </c>
-      <c r="P38" s="473">
+      <c r="P38" s="474">
         <v>-16.05</v>
       </c>
-      <c r="Q38" s="475">
+      <c r="Q38" s="479">
         <v>-15.97</v>
       </c>
-      <c r="R38" s="470">
+      <c r="R38" s="480">
         <v>-15.51</v>
       </c>
-      <c r="S38" s="480">
+      <c r="S38" s="470">
         <v>-15.59</v>
       </c>
-      <c r="T38" s="481">
-        <v>-9.34</v>
+      <c r="T38" s="475">
+        <v>-7.56</v>
       </c>
     </row>
     <row r="39">
@@ -10992,7 +11024,7 @@
       <c r="C39" t="str">
         <v>603284</v>
       </c>
-      <c r="D39" s="489" t="str">
+      <c r="D39" s="484" t="str">
         <v>净买: 1322.73万</v>
       </c>
       <c r="E39">
@@ -11007,33 +11039,35 @@
       <c r="H39">
         <v>-0.79</v>
       </c>
-      <c r="I39" s="487">
+      <c r="I39" s="485">
         <v>4.15</v>
       </c>
-      <c r="J39" s="482">
+      <c r="J39" s="486">
         <v>7.16</v>
       </c>
-      <c r="K39" s="486">
+      <c r="K39" s="488">
         <v>7.16</v>
       </c>
-      <c r="L39" s="488">
+      <c r="L39" s="487">
         <v>7.39</v>
       </c>
-      <c r="M39" s="483">
+      <c r="M39" s="489">
         <v>7.45</v>
       </c>
-      <c r="N39" s="484">
+      <c r="N39" s="482">
         <v>8.48</v>
       </c>
       <c r="O39" s="490">
         <v>6.71</v>
       </c>
-      <c r="P39" t="str"/>
+      <c r="P39" s="483">
+        <v>7.41</v>
+      </c>
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="485">
-        <v>6.71</v>
+      <c r="T39" s="491">
+        <v>7.41</v>
       </c>
     </row>
     <row r="40">
@@ -11046,7 +11080,7 @@
       <c r="C40" t="str">
         <v>600605</v>
       </c>
-      <c r="D40" s="495" t="str">
+      <c r="D40" s="494" t="str">
         <v>净卖: -789.04万</v>
       </c>
       <c r="E40">
@@ -11061,16 +11095,18 @@
       <c r="H40">
         <v>6.5</v>
       </c>
-      <c r="I40" s="491">
+      <c r="I40" s="495">
         <v>3.29</v>
       </c>
-      <c r="J40" s="492">
+      <c r="J40" s="496">
         <v>-0.16</v>
       </c>
-      <c r="K40" s="493">
+      <c r="K40" s="497">
         <v>-1.47</v>
       </c>
-      <c r="L40" t="str"/>
+      <c r="L40" s="492">
+        <v>-3.1</v>
+      </c>
       <c r="M40" t="str"/>
       <c r="N40" t="str"/>
       <c r="O40" t="str"/>
@@ -11078,8 +11114,8 @@
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="494">
-        <v>-1.47</v>
+      <c r="T40" s="493">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="41">
@@ -11103,7 +11139,7 @@
         <v>39</v>
       </c>
       <c r="L41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M41">
         <v>38</v>
@@ -11115,7 +11151,7 @@
         <v>38</v>
       </c>
       <c r="P41">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q41">
         <v>37</v>
@@ -11141,41 +11177,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="499">
+      <c r="I42" s="507">
         <v>38.46</v>
       </c>
-      <c r="J42" s="504">
+      <c r="J42" s="505">
         <v>41.03</v>
       </c>
-      <c r="K42" s="506">
+      <c r="K42" s="498">
         <v>38.46</v>
       </c>
-      <c r="L42" s="500">
-        <v>36.84</v>
-      </c>
-      <c r="M42" s="507">
+      <c r="L42" s="499">
+        <v>35.9</v>
+      </c>
+      <c r="M42" s="500">
         <v>28.95</v>
       </c>
-      <c r="N42" s="505">
+      <c r="N42" s="508">
         <v>26.32</v>
       </c>
-      <c r="O42" s="496">
+      <c r="O42" s="501">
         <v>31.58</v>
       </c>
-      <c r="P42" s="497">
-        <v>32.43</v>
-      </c>
-      <c r="Q42" s="501">
+      <c r="P42" s="502">
+        <v>34.21</v>
+      </c>
+      <c r="Q42" s="503">
         <v>24.32</v>
       </c>
-      <c r="R42" s="498">
+      <c r="R42" s="509">
         <v>29.73</v>
       </c>
-      <c r="S42" s="502">
+      <c r="S42" s="504">
         <v>18.92</v>
       </c>
-      <c r="T42" s="503">
-        <v>51.28</v>
+      <c r="T42" s="506">
+        <v>56.41</v>
       </c>
     </row>
     <row r="43">
@@ -11189,41 +11225,41 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="513">
+      <c r="I43" s="515">
         <v>-0.38</v>
       </c>
-      <c r="J43" s="509">
+      <c r="J43" s="516">
         <v>-0.74</v>
       </c>
       <c r="K43" s="510">
         <v>-2.11</v>
       </c>
       <c r="L43" s="511">
-        <v>-4.14</v>
-      </c>
-      <c r="M43" s="508">
+        <v>-4.11</v>
+      </c>
+      <c r="M43" s="519">
         <v>-5.26</v>
       </c>
-      <c r="N43" s="518">
+      <c r="N43" s="520">
         <v>-6.6</v>
       </c>
-      <c r="O43" s="514">
+      <c r="O43" s="517">
         <v>-5.4</v>
       </c>
-      <c r="P43" s="519">
-        <v>-6.06</v>
-      </c>
-      <c r="Q43" s="515">
+      <c r="P43" s="512">
+        <v>-5.71</v>
+      </c>
+      <c r="Q43" s="513">
         <v>-6.48</v>
       </c>
-      <c r="R43" s="516">
+      <c r="R43" s="514">
         <v>-5.55</v>
       </c>
-      <c r="S43" s="512">
+      <c r="S43" s="518">
         <v>-7.91</v>
       </c>
-      <c r="T43" s="517">
-        <v>16.46</v>
+      <c r="T43" s="521">
+        <v>16.2</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/申港广东分/index.xlsx
+++ b/youzi/申港广东分/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="523">
+  <fills count="525">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF4C3C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -51,19 +57,433 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
+        <fgColor rgb="FF98D4A6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,13 +495,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,7 +609,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4C3C8"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,25 +627,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,19 +765,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,43 +813,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,7 +939,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,19 +993,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,13 +1167,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,7 +1251,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
+        <fgColor rgb="FF77C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -273,49 +1293,565 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB2222F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -327,13 +1863,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,13 +1875,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -363,61 +1887,427 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -429,19 +2319,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -453,2670 +2385,768 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF27A343"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -3129,42 +3159,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="522">
+  <borders count="524">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6823,7 +6849,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="522">
+  <cellXfs count="524">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8386,6 +8412,12 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="521" fillId="522" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="522" fillId="523" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="523" fillId="524" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8754,32 +8786,32 @@
       <c r="K2" s="5">
         <v>3.91</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="1">
         <v>1.47</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="2">
         <v>11.62</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="3">
         <v>22.79</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="10">
         <v>15.02</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="6">
         <v>26.53</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="7">
         <v>32.65</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="11">
         <v>28.74</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="8">
         <v>21.77</v>
       </c>
-      <c r="T2" s="8">
-        <v>2.15</v>
+      <c r="T2" s="12">
+        <v>1.19</v>
       </c>
     </row>
     <row r="3">
@@ -8792,7 +8824,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="22" t="str">
         <v>净买: 486.49万</v>
       </c>
       <c r="E3">
@@ -8807,41 +8839,41 @@
       <c r="H3">
         <v>6.6</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="23">
         <v>-11.36</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="19">
         <v>-13.44</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="15">
         <v>-4.79</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="24">
         <v>4.74</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="20">
         <v>-1.89</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="16">
         <v>7.93</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="25">
         <v>13.15</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="26">
         <v>9.82</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="17">
         <v>3.87</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="21">
         <v>6.53</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="14">
         <v>-4.11</v>
       </c>
-      <c r="T3" s="26">
-        <v>-12.86</v>
+      <c r="T3" s="18">
+        <v>-13.68</v>
       </c>
     </row>
     <row r="4">
@@ -8854,7 +8886,7 @@
       <c r="C4" t="str">
         <v>603881</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="38" t="str">
         <v>净买: 7242.53万</v>
       </c>
       <c r="E4">
@@ -8869,41 +8901,41 @@
       <c r="H4">
         <v>8.87</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="35">
         <v>1.04</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="39">
         <v>11.14</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="36">
         <v>0.03</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="31">
         <v>7.5</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="32">
         <v>8.74</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="29">
         <v>19.61</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="37">
         <v>25.9</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="30">
         <v>21.45</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="27">
         <v>15.56</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="33">
         <v>9.81</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="28">
         <v>-0.74</v>
       </c>
-      <c r="T4" s="28">
-        <v>16.95</v>
+      <c r="T4" s="34">
+        <v>12.83</v>
       </c>
     </row>
     <row r="5">
@@ -8916,7 +8948,7 @@
       <c r="C5" t="str">
         <v>603881</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="44" t="str">
         <v>净卖: -9194.30万</v>
       </c>
       <c r="E5">
@@ -8931,41 +8963,41 @@
       <c r="H5">
         <v>-4.56</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="48">
         <v>-5.7</v>
       </c>
       <c r="J5" s="49">
         <v>1.34</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="45">
         <v>2.51</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="50">
         <v>12.77</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="52">
         <v>18.69</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="46">
         <v>14.5</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="40">
         <v>8.94</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="47">
         <v>3.52</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="41">
         <v>-6.42</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="51">
         <v>-4.83</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="42">
         <v>-3.18</v>
       </c>
-      <c r="T5" s="51">
-        <v>10.25</v>
+      <c r="T5" s="43">
+        <v>6.37</v>
       </c>
     </row>
     <row r="6">
@@ -8978,7 +9010,7 @@
       <c r="C6" t="str">
         <v>000818</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 5099.54万</v>
       </c>
       <c r="E6">
@@ -8993,16 +9025,16 @@
       <c r="H6">
         <v>5.63</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="57">
         <v>4.13</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="64">
         <v>14.56</v>
       </c>
       <c r="K6" s="60">
         <v>7.97</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="65">
         <v>-2.83</v>
       </c>
       <c r="M6" s="61">
@@ -9011,23 +9043,23 @@
       <c r="N6" s="62">
         <v>-15.63</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="53">
         <v>-12.8</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="54">
         <v>-16.13</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="58">
         <v>-19.84</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="55">
         <v>-20.37</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="59">
         <v>-19.6</v>
       </c>
-      <c r="T6" s="64">
-        <v>-60.05</v>
+      <c r="T6" s="56">
+        <v>-61.47</v>
       </c>
     </row>
     <row r="7">
@@ -9040,7 +9072,7 @@
       <c r="C7" t="str">
         <v>600590</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 1013.84万</v>
       </c>
       <c r="E7">
@@ -9055,41 +9087,41 @@
       <c r="H7">
         <v>10.05</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="74">
         <v>0</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="75">
         <v>-2.39</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="68">
         <v>7.39</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="69">
         <v>1.85</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="77">
         <v>1.63</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="70">
         <v>-5.76</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="71">
         <v>-3.48</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="72">
         <v>6.2</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="76">
         <v>16.85</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="78">
         <v>26.41</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="66">
         <v>21.74</v>
       </c>
-      <c r="T7" s="76">
-        <v>89.35</v>
+      <c r="T7" s="67">
+        <v>88.37</v>
       </c>
     </row>
     <row r="8">
@@ -9102,7 +9134,7 @@
       <c r="C8" t="str">
         <v>000818</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="86" t="str">
         <v>净卖: -5301.29万</v>
       </c>
       <c r="E8">
@@ -9117,41 +9149,41 @@
       <c r="H8">
         <v>-10</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="87">
         <v>0</v>
       </c>
       <c r="J8" s="88">
         <v>-9.99</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="83">
         <v>-13.17</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="79">
         <v>-10.26</v>
       </c>
       <c r="M8" s="80">
         <v>-13.69</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="84">
         <v>-17.51</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="89">
         <v>-18.06</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="81">
         <v>-17.26</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="90">
         <v>-14.79</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8" s="82">
         <v>-16.85</v>
       </c>
       <c r="S8" s="91">
         <v>-14.02</v>
       </c>
-      <c r="T8" s="87">
-        <v>-58.89</v>
+      <c r="T8" s="85">
+        <v>-60.35</v>
       </c>
     </row>
     <row r="9">
@@ -9164,7 +9196,7 @@
       <c r="C9" t="str">
         <v>002290</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -2168.44万</v>
       </c>
       <c r="E9">
@@ -9179,41 +9211,41 @@
       <c r="H9">
         <v>-9.5</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="102">
         <v>-0.54</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="97">
         <v>0</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="99">
         <v>0.33</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="92">
         <v>3.33</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="103">
         <v>-7</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="93">
         <v>-1.67</v>
       </c>
-      <c r="O9" s="103">
+      <c r="O9" s="100">
         <v>6.04</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="94">
         <v>7.58</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="101">
         <v>12.71</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="98">
         <v>16.92</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="95">
         <v>12.79</v>
       </c>
-      <c r="T9" s="94">
-        <v>209.79</v>
+      <c r="T9" s="104">
+        <v>196.54</v>
       </c>
     </row>
     <row r="10">
@@ -9244,38 +9276,38 @@
       <c r="I10" s="110">
         <v>8.41</v>
       </c>
-      <c r="J10" s="105">
+      <c r="J10" s="113">
         <v>-2.41</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="116">
         <v>-12.18</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="117">
         <v>-15</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="105">
         <v>-12.88</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="114">
         <v>-14.71</v>
       </c>
-      <c r="O10" s="116">
+      <c r="O10" s="107">
         <v>-15.65</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="115">
         <v>-16.18</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="108">
         <v>-16.82</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="111">
         <v>-18.35</v>
       </c>
-      <c r="S10" s="114">
+      <c r="S10" s="112">
         <v>-15.18</v>
       </c>
-      <c r="T10" s="108">
-        <v>-36</v>
+      <c r="T10" s="106">
+        <v>-35.65</v>
       </c>
     </row>
     <row r="11">
@@ -9288,7 +9320,7 @@
       <c r="C11" t="str">
         <v>605100</v>
       </c>
-      <c r="D11" s="122" t="str">
+      <c r="D11" s="129" t="str">
         <v>净买: 1795.46万</v>
       </c>
       <c r="E11">
@@ -9306,38 +9338,38 @@
       <c r="I11" s="125">
         <v>0</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="130">
         <v>-9.16</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="118">
         <v>-0.08</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="119">
         <v>0</v>
       </c>
-      <c r="M11" s="128">
+      <c r="M11" s="126">
         <v>9.99</v>
       </c>
       <c r="N11" s="120">
         <v>-0.99</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="127">
         <v>8.93</v>
       </c>
-      <c r="P11" s="130">
+      <c r="P11" s="121">
         <v>19.83</v>
       </c>
-      <c r="Q11" s="118">
+      <c r="Q11" s="122">
         <v>12.16</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="123">
         <v>23.38</v>
       </c>
       <c r="S11" s="124">
         <v>13.07</v>
       </c>
-      <c r="T11" s="121">
-        <v>93.44</v>
+      <c r="T11" s="128">
+        <v>92.42</v>
       </c>
     </row>
     <row r="12">
@@ -9350,7 +9382,7 @@
       <c r="C12" t="str">
         <v>605300</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="138" t="str">
         <v>净卖: -1034.72万</v>
       </c>
       <c r="E12">
@@ -9365,41 +9397,41 @@
       <c r="H12">
         <v>-5.36</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="141">
         <v>2.26</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="131">
         <v>4.81</v>
       </c>
-      <c r="K12" s="141">
+      <c r="K12" s="137">
         <v>2.62</v>
       </c>
-      <c r="L12" s="136">
+      <c r="L12" s="132">
         <v>1.49</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="142">
         <v>0.85</v>
       </c>
-      <c r="N12" s="138">
+      <c r="N12" s="133">
         <v>0.07</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="134">
         <v>-1.77</v>
       </c>
-      <c r="P12" s="132">
+      <c r="P12" s="139">
         <v>2.05</v>
       </c>
-      <c r="Q12" s="133">
+      <c r="Q12" s="140">
         <v>0.85</v>
       </c>
-      <c r="R12" s="134">
+      <c r="R12" s="143">
         <v>0.21</v>
       </c>
-      <c r="S12" s="137">
+      <c r="S12" s="135">
         <v>-0.92</v>
       </c>
-      <c r="T12" s="140">
-        <v>-23</v>
+      <c r="T12" s="136">
+        <v>-22.58</v>
       </c>
     </row>
     <row r="13">
@@ -9412,7 +9444,7 @@
       <c r="C13" t="str">
         <v>002114</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="153" t="str">
         <v>净买: 1554.85万</v>
       </c>
       <c r="E13">
@@ -9427,31 +9459,31 @@
       <c r="H13">
         <v>9.83</v>
       </c>
-      <c r="I13" s="152">
+      <c r="I13" s="145">
         <v>0.13</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="156">
         <v>-1.41</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="154">
         <v>-4.6</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="144">
         <v>-6.65</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="146">
         <v>-6.01</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="151">
         <v>-6.52</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="155">
         <v>-5.5</v>
       </c>
-      <c r="P13" s="155">
+      <c r="P13" s="147">
         <v>-10.1</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="152">
         <v>-9.59</v>
       </c>
       <c r="R13" s="148">
@@ -9460,8 +9492,8 @@
       <c r="S13" s="149">
         <v>-11.76</v>
       </c>
-      <c r="T13" s="144">
-        <v>17.39</v>
+      <c r="T13" s="150">
+        <v>15.47</v>
       </c>
     </row>
     <row r="14">
@@ -9474,7 +9506,7 @@
       <c r="C14" t="str">
         <v>605303</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="168" t="str">
         <v>净买: 1578.26万</v>
       </c>
       <c r="E14">
@@ -9489,41 +9521,41 @@
       <c r="H14">
         <v>10.03</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="160">
         <v>0</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="161">
         <v>-7.6</v>
       </c>
       <c r="K14" s="169">
         <v>-13.68</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="164">
         <v>-20.06</v>
       </c>
-      <c r="M14" s="163">
+      <c r="M14" s="166">
         <v>-20.21</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="157">
         <v>-21.58</v>
       </c>
       <c r="O14" s="165">
         <v>-22.87</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="167">
         <v>-23.86</v>
       </c>
-      <c r="Q14" s="166">
+      <c r="Q14" s="158">
         <v>-24.62</v>
       </c>
-      <c r="R14" s="167">
+      <c r="R14" s="162">
         <v>-27.13</v>
       </c>
-      <c r="S14" s="160">
+      <c r="S14" s="163">
         <v>-26.6</v>
       </c>
-      <c r="T14" s="158">
-        <v>72.95</v>
+      <c r="T14" s="159">
+        <v>70.82</v>
       </c>
     </row>
     <row r="15">
@@ -9536,7 +9568,7 @@
       <c r="C15" t="str">
         <v>605303</v>
       </c>
-      <c r="D15" s="180" t="str">
+      <c r="D15" s="172" t="str">
         <v>净卖: -1462.35万</v>
       </c>
       <c r="E15">
@@ -9557,35 +9589,35 @@
       <c r="J15" s="174">
         <v>-5.15</v>
       </c>
-      <c r="K15" s="181">
+      <c r="K15" s="175">
         <v>-6.78</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="179">
         <v>-8.31</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="180">
         <v>-9.49</v>
       </c>
-      <c r="N15" s="170">
+      <c r="N15" s="181">
         <v>-10.39</v>
       </c>
-      <c r="O15" s="171">
+      <c r="O15" s="176">
         <v>-13.37</v>
       </c>
-      <c r="P15" s="178">
+      <c r="P15" s="182">
         <v>-12.74</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="170">
         <v>-14.27</v>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="171">
         <v>-15.54</v>
       </c>
-      <c r="S15" s="172">
+      <c r="S15" s="177">
         <v>-16.71</v>
       </c>
-      <c r="T15" s="179">
-        <v>105.6</v>
+      <c r="T15" s="178">
+        <v>103.07</v>
       </c>
     </row>
     <row r="16">
@@ -9598,7 +9630,7 @@
       <c r="C16" t="str">
         <v>600301</v>
       </c>
-      <c r="D16" s="189" t="str">
+      <c r="D16" s="193" t="str">
         <v>净卖: -3080.81万</v>
       </c>
       <c r="E16">
@@ -9613,41 +9645,41 @@
       <c r="H16">
         <v>-2.8</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="189">
         <v>-4.62</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="190">
         <v>-5.96</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="194">
         <v>-4.88</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="185">
         <v>-5.27</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="183">
         <v>-3.31</v>
       </c>
-      <c r="N16" s="194">
+      <c r="N16" s="186">
         <v>-7.19</v>
       </c>
-      <c r="O16" s="195">
+      <c r="O16" s="191">
         <v>-7.88</v>
       </c>
-      <c r="P16" s="183">
+      <c r="P16" s="184">
         <v>-7.88</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="195">
         <v>-10.35</v>
       </c>
-      <c r="R16" s="184">
+      <c r="R16" s="187">
         <v>-11.15</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="192">
         <v>-14.38</v>
       </c>
-      <c r="T16" s="191">
-        <v>99.42</v>
+      <c r="T16" s="188">
+        <v>111.46</v>
       </c>
     </row>
     <row r="17">
@@ -9660,7 +9692,7 @@
       <c r="C17" t="str">
         <v>000815</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="197" t="str">
         <v>净买: 5327.66万</v>
       </c>
       <c r="E17">
@@ -9675,41 +9707,41 @@
       <c r="H17">
         <v>2.39</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="204">
         <v>2.95</v>
       </c>
-      <c r="J17" s="199">
+      <c r="J17" s="203">
         <v>-3.14</v>
       </c>
-      <c r="K17" s="206">
+      <c r="K17" s="207">
         <v>-4.8</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="198">
         <v>-6.52</v>
       </c>
-      <c r="M17" s="200">
+      <c r="M17" s="199">
         <v>-12.98</v>
       </c>
-      <c r="N17" s="204">
+      <c r="N17" s="205">
         <v>-17.22</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="208">
         <v>-16.91</v>
       </c>
-      <c r="P17" s="208">
+      <c r="P17" s="200">
         <v>-20.79</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="206">
         <v>-20.3</v>
       </c>
-      <c r="R17" s="205">
+      <c r="R17" s="201">
         <v>-19.74</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="196">
         <v>-20.85</v>
       </c>
       <c r="T17" s="202">
-        <v>34.99</v>
+        <v>28.47</v>
       </c>
     </row>
     <row r="18">
@@ -9722,7 +9754,7 @@
       <c r="C18" t="str">
         <v>603315</v>
       </c>
-      <c r="D18" s="209" t="str">
+      <c r="D18" s="214" t="str">
         <v>净买: 2006.31万</v>
       </c>
       <c r="E18">
@@ -9737,41 +9769,41 @@
       <c r="H18">
         <v>10.03</v>
       </c>
-      <c r="I18" s="213">
+      <c r="I18" s="218">
         <v>0</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="219">
         <v>9.99</v>
       </c>
-      <c r="K18" s="214">
+      <c r="K18" s="209">
         <v>20.99</v>
       </c>
-      <c r="L18" s="216">
+      <c r="L18" s="210">
         <v>8.87</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="220">
         <v>-2</v>
       </c>
-      <c r="N18" s="219">
+      <c r="N18" s="217">
         <v>-11.81</v>
       </c>
       <c r="O18" s="215">
         <v>-12.8</v>
       </c>
-      <c r="P18" s="217">
+      <c r="P18" s="221">
         <v>-17.49</v>
       </c>
-      <c r="Q18" s="218">
+      <c r="Q18" s="216">
         <v>-18.11</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="211">
         <v>-16.36</v>
       </c>
       <c r="S18" s="212">
         <v>-16.55</v>
       </c>
-      <c r="T18" s="221">
-        <v>9.93</v>
+      <c r="T18" s="213">
+        <v>9.43</v>
       </c>
     </row>
     <row r="19">
@@ -9784,7 +9816,7 @@
       <c r="C19" t="str">
         <v>603315</v>
       </c>
-      <c r="D19" s="234" t="str">
+      <c r="D19" s="231" t="str">
         <v>净卖: -2227.67万</v>
       </c>
       <c r="E19">
@@ -9799,41 +9831,41 @@
       <c r="H19">
         <v>-4.2</v>
       </c>
-      <c r="I19" s="226">
+      <c r="I19" s="224">
         <v>14.82</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="232">
         <v>3.32</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="233">
         <v>-6.99</v>
       </c>
-      <c r="L19" s="231">
+      <c r="L19" s="227">
         <v>-16.3</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="225">
         <v>-17.25</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="226">
         <v>-21.7</v>
       </c>
-      <c r="O19" s="223">
+      <c r="O19" s="234">
         <v>-22.29</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="222">
         <v>-20.63</v>
       </c>
-      <c r="Q19" s="224">
+      <c r="Q19" s="228">
         <v>-20.81</v>
       </c>
-      <c r="R19" s="233">
+      <c r="R19" s="223">
         <v>-20.09</v>
       </c>
-      <c r="S19" s="225">
+      <c r="S19" s="229">
         <v>-22.05</v>
       </c>
-      <c r="T19" s="229">
-        <v>4.33</v>
+      <c r="T19" s="230">
+        <v>3.85</v>
       </c>
     </row>
     <row r="20">
@@ -9846,7 +9878,7 @@
       <c r="C20" t="str">
         <v>000737</v>
       </c>
-      <c r="D20" s="236" t="str">
+      <c r="D20" s="235" t="str">
         <v>净买: 2607.05万</v>
       </c>
       <c r="E20">
@@ -9861,41 +9893,41 @@
       <c r="H20">
         <v>0.79</v>
       </c>
-      <c r="I20" s="237">
+      <c r="I20" s="236">
         <v>9.19</v>
       </c>
-      <c r="J20" s="245">
+      <c r="J20" s="240">
         <v>15.54</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="243">
         <v>20.43</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="244">
         <v>11.93</v>
       </c>
-      <c r="M20" s="242">
+      <c r="M20" s="238">
         <v>4.79</v>
       </c>
-      <c r="N20" s="247">
+      <c r="N20" s="237">
         <v>2.64</v>
       </c>
-      <c r="O20" s="243">
+      <c r="O20" s="241">
         <v>2.83</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="245">
         <v>1.08</v>
       </c>
-      <c r="Q20" s="240">
+      <c r="Q20" s="242">
         <v>-2.15</v>
       </c>
-      <c r="R20" s="244">
+      <c r="R20" s="246">
         <v>-11.93</v>
       </c>
-      <c r="S20" s="235">
+      <c r="S20" s="239">
         <v>-19.65</v>
       </c>
-      <c r="T20" s="239">
-        <v>38.51</v>
+      <c r="T20" s="247">
+        <v>38.12</v>
       </c>
     </row>
     <row r="21">
@@ -9908,7 +9940,7 @@
       <c r="C21" t="str">
         <v>000779</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="259" t="str">
         <v>净买: 1464.90万</v>
       </c>
       <c r="E21">
@@ -9923,41 +9955,41 @@
       <c r="H21">
         <v>9.36</v>
       </c>
-      <c r="I21" s="254">
+      <c r="I21" s="260">
         <v>-14.36</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="252">
         <v>-22.92</v>
       </c>
-      <c r="K21" s="260">
+      <c r="K21" s="248">
         <v>-25.67</v>
       </c>
-      <c r="L21" s="258">
+      <c r="L21" s="253">
         <v>-28.8</v>
       </c>
-      <c r="M21" s="259">
+      <c r="M21" s="249">
         <v>-29.11</v>
       </c>
-      <c r="N21" s="248">
+      <c r="N21" s="256">
         <v>-26.05</v>
       </c>
-      <c r="O21" s="255">
+      <c r="O21" s="257">
         <v>-28.27</v>
       </c>
-      <c r="P21" s="252">
+      <c r="P21" s="250">
         <v>-29.03</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="258">
         <v>-29.95</v>
       </c>
-      <c r="R21" s="250">
+      <c r="R21" s="251">
         <v>-36.97</v>
       </c>
-      <c r="S21" s="251">
+      <c r="S21" s="254">
         <v>-35.91</v>
       </c>
-      <c r="T21" s="256">
-        <v>-32.93</v>
+      <c r="T21" s="255">
+        <v>-33.23</v>
       </c>
     </row>
     <row r="22">
@@ -9970,7 +10002,7 @@
       <c r="C22" t="str">
         <v>600727</v>
       </c>
-      <c r="D22" s="267" t="str">
+      <c r="D22" s="268" t="str">
         <v>净卖: -2220.75万</v>
       </c>
       <c r="E22">
@@ -9985,41 +10017,41 @@
       <c r="H22">
         <v>4.31</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="266">
         <v>-1.31</v>
       </c>
-      <c r="J22" s="271">
+      <c r="J22" s="269">
         <v>0.76</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="261">
         <v>-9.36</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="262">
         <v>-13.71</v>
       </c>
-      <c r="M22" s="270">
+      <c r="M22" s="272">
         <v>-11.32</v>
       </c>
-      <c r="N22" s="272">
+      <c r="N22" s="263">
         <v>-12.08</v>
       </c>
-      <c r="O22" s="263">
+      <c r="O22" s="270">
         <v>-7.51</v>
       </c>
-      <c r="P22" s="273">
+      <c r="P22" s="264">
         <v>-16.76</v>
       </c>
-      <c r="Q22" s="264">
+      <c r="Q22" s="271">
         <v>-15.13</v>
       </c>
       <c r="R22" s="265">
         <v>-16.76</v>
       </c>
-      <c r="S22" s="266">
+      <c r="S22" s="267">
         <v>-15.67</v>
       </c>
-      <c r="T22" s="261">
-        <v>-15.13</v>
+      <c r="T22" s="273">
+        <v>-13.71</v>
       </c>
     </row>
     <row r="23">
@@ -10032,7 +10064,7 @@
       <c r="C23" t="str">
         <v>001217</v>
       </c>
-      <c r="D23" s="282" t="str">
+      <c r="D23" s="276" t="str">
         <v>净买: 3127.44万</v>
       </c>
       <c r="E23">
@@ -10047,41 +10079,41 @@
       <c r="H23">
         <v>9.99</v>
       </c>
-      <c r="I23" s="278">
+      <c r="I23" s="286">
         <v>0</v>
       </c>
-      <c r="J23" s="279">
+      <c r="J23" s="281">
         <v>-8.55</v>
       </c>
-      <c r="K23" s="283">
+      <c r="K23" s="277">
         <v>-13.73</v>
       </c>
-      <c r="L23" s="286">
+      <c r="L23" s="278">
         <v>-17.5</v>
       </c>
-      <c r="M23" s="276">
+      <c r="M23" s="283">
         <v>-20.66</v>
       </c>
-      <c r="N23" s="284">
+      <c r="N23" s="274">
         <v>-28.6</v>
       </c>
-      <c r="O23" s="274">
+      <c r="O23" s="284">
         <v>-31.02</v>
       </c>
-      <c r="P23" s="280">
+      <c r="P23" s="279">
         <v>-31.09</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="285">
         <v>-29.48</v>
       </c>
-      <c r="R23" s="277">
+      <c r="R23" s="280">
         <v>-28.33</v>
       </c>
-      <c r="S23" s="285">
+      <c r="S23" s="275">
         <v>-26.72</v>
       </c>
-      <c r="T23" s="281">
-        <v>-20.05</v>
+      <c r="T23" s="282">
+        <v>-20.12</v>
       </c>
     </row>
     <row r="24">
@@ -10094,7 +10126,7 @@
       <c r="C24" t="str">
         <v>000422</v>
       </c>
-      <c r="D24" s="291" t="str">
+      <c r="D24" s="287" t="str">
         <v>净卖: -6435.12万</v>
       </c>
       <c r="E24">
@@ -10109,41 +10141,41 @@
       <c r="H24">
         <v>-3.3</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="291">
         <v>-6.9</v>
       </c>
-      <c r="J24" s="293">
+      <c r="J24" s="296">
         <v>-8.84</v>
       </c>
       <c r="K24" s="299">
         <v>-7.5</v>
       </c>
-      <c r="L24" s="289">
+      <c r="L24" s="292">
         <v>-7.64</v>
       </c>
-      <c r="M24" s="295">
+      <c r="M24" s="293">
         <v>-12.93</v>
       </c>
-      <c r="N24" s="290">
+      <c r="N24" s="288">
         <v>-21.63</v>
       </c>
-      <c r="O24" s="296">
+      <c r="O24" s="297">
         <v>-20.23</v>
       </c>
-      <c r="P24" s="294">
+      <c r="P24" s="289">
         <v>-21.57</v>
       </c>
-      <c r="Q24" s="287">
+      <c r="Q24" s="290">
         <v>-20.09</v>
       </c>
-      <c r="R24" s="297">
+      <c r="R24" s="294">
         <v>-20.03</v>
       </c>
-      <c r="S24" s="298">
+      <c r="S24" s="295">
         <v>-17.62</v>
       </c>
-      <c r="T24" s="288">
-        <v>6.03</v>
+      <c r="T24" s="298">
+        <v>8.91</v>
       </c>
     </row>
     <row r="25">
@@ -10156,7 +10188,7 @@
       <c r="C25" t="str">
         <v>001333</v>
       </c>
-      <c r="D25" s="301" t="str">
+      <c r="D25" s="303" t="str">
         <v>净买: 1650.82万</v>
       </c>
       <c r="E25">
@@ -10171,41 +10203,41 @@
       <c r="H25">
         <v>-1.88</v>
       </c>
-      <c r="I25" s="305">
+      <c r="I25" s="308">
         <v>12.11</v>
       </c>
-      <c r="J25" s="309">
+      <c r="J25" s="306">
         <v>23.33</v>
       </c>
-      <c r="K25" s="310">
+      <c r="K25" s="304">
         <v>11.01</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="309">
         <v>-0.08</v>
       </c>
-      <c r="M25" s="302">
+      <c r="M25" s="307">
         <v>-10.07</v>
       </c>
-      <c r="N25" s="311">
+      <c r="N25" s="300">
         <v>-18.1</v>
       </c>
-      <c r="O25" s="303">
+      <c r="O25" s="301">
         <v>-17.47</v>
       </c>
-      <c r="P25" s="312">
+      <c r="P25" s="310">
         <v>-15.81</v>
       </c>
-      <c r="Q25" s="304">
+      <c r="Q25" s="305">
         <v>-10.96</v>
       </c>
-      <c r="R25" s="307">
+      <c r="R25" s="311">
         <v>-8.75</v>
       </c>
-      <c r="S25" s="308">
+      <c r="S25" s="312">
         <v>-10.28</v>
       </c>
-      <c r="T25" s="300">
-        <v>6.16</v>
+      <c r="T25" s="302">
+        <v>5.65</v>
       </c>
     </row>
     <row r="26">
@@ -10218,7 +10250,7 @@
       <c r="C26" t="str">
         <v>002365</v>
       </c>
-      <c r="D26" s="313" t="str">
+      <c r="D26" s="317" t="str">
         <v>净卖: -918.91万</v>
       </c>
       <c r="E26">
@@ -10233,41 +10265,41 @@
       <c r="H26">
         <v>-8.32</v>
       </c>
-      <c r="I26" s="314">
+      <c r="I26" s="321">
         <v>20.02</v>
       </c>
-      <c r="J26" s="316">
+      <c r="J26" s="314">
         <v>15.9</v>
       </c>
-      <c r="K26" s="317">
+      <c r="K26" s="315">
         <v>22.97</v>
       </c>
-      <c r="L26" s="323">
+      <c r="L26" s="318">
         <v>19.43</v>
       </c>
-      <c r="M26" s="318">
+      <c r="M26" s="322">
         <v>16.02</v>
       </c>
-      <c r="N26" s="319">
+      <c r="N26" s="323">
         <v>10.37</v>
       </c>
-      <c r="O26" s="320">
+      <c r="O26" s="319">
         <v>9.42</v>
       </c>
-      <c r="P26" s="324">
+      <c r="P26" s="320">
         <v>11.66</v>
       </c>
-      <c r="Q26" s="315">
+      <c r="Q26" s="324">
         <v>6.24</v>
       </c>
       <c r="R26" s="325">
         <v>16.84</v>
       </c>
-      <c r="S26" s="321">
+      <c r="S26" s="313">
         <v>20.49</v>
       </c>
-      <c r="T26" s="322">
-        <v>61.13</v>
+      <c r="T26" s="316">
+        <v>58.54</v>
       </c>
     </row>
     <row r="27">
@@ -10280,7 +10312,7 @@
       <c r="C27" t="str">
         <v>600180</v>
       </c>
-      <c r="D27" s="329" t="str">
+      <c r="D27" s="327" t="str">
         <v>净卖: -1973.71万</v>
       </c>
       <c r="E27">
@@ -10295,41 +10327,41 @@
       <c r="H27">
         <v>-4.9</v>
       </c>
-      <c r="I27" s="330">
+      <c r="I27" s="336">
         <v>0.21</v>
       </c>
-      <c r="J27" s="331">
+      <c r="J27" s="337">
         <v>-1.93</v>
       </c>
-      <c r="K27" s="332">
+      <c r="K27" s="331">
         <v>-3.86</v>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="338">
         <v>-2.58</v>
       </c>
-      <c r="M27" s="333">
+      <c r="M27" s="326">
         <v>-1.5</v>
       </c>
-      <c r="N27" s="338">
+      <c r="N27" s="332">
         <v>-3.43</v>
       </c>
-      <c r="O27" s="326">
+      <c r="O27" s="333">
         <v>-5.79</v>
       </c>
-      <c r="P27" s="334">
+      <c r="P27" s="328">
         <v>-4.94</v>
       </c>
-      <c r="Q27" s="327">
+      <c r="Q27" s="329">
         <v>-8.58</v>
       </c>
-      <c r="R27" s="335">
+      <c r="R27" s="330">
         <v>-7.73</v>
       </c>
-      <c r="S27" s="328">
+      <c r="S27" s="334">
         <v>-8.37</v>
       </c>
-      <c r="T27" s="336">
-        <v>-31.33</v>
+      <c r="T27" s="335">
+        <v>-31.12</v>
       </c>
     </row>
     <row r="28">
@@ -10342,7 +10374,7 @@
       <c r="C28" t="str">
         <v>002743</v>
       </c>
-      <c r="D28" s="350" t="str">
+      <c r="D28" s="343" t="str">
         <v>净卖: -345.80万</v>
       </c>
       <c r="E28">
@@ -10357,41 +10389,41 @@
       <c r="H28">
         <v>-9.98</v>
       </c>
-      <c r="I28" s="351">
+      <c r="I28" s="346">
         <v>0</v>
       </c>
-      <c r="J28" s="342">
+      <c r="J28" s="349">
         <v>-5.83</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="340">
         <v>-3.38</v>
       </c>
-      <c r="L28" s="339">
+      <c r="L28" s="350">
         <v>0.75</v>
       </c>
-      <c r="M28" s="343">
+      <c r="M28" s="344">
         <v>1.88</v>
       </c>
-      <c r="N28" s="340">
+      <c r="N28" s="347">
         <v>3.01</v>
       </c>
-      <c r="O28" s="347">
+      <c r="O28" s="341">
         <v>3.95</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="348">
         <v>0.75</v>
       </c>
-      <c r="Q28" s="348">
+      <c r="Q28" s="351">
         <v>-0.19</v>
       </c>
-      <c r="R28" s="349">
+      <c r="R28" s="345">
         <v>1.5</v>
       </c>
-      <c r="S28" s="341">
+      <c r="S28" s="342">
         <v>5.83</v>
       </c>
-      <c r="T28" s="345">
-        <v>0.19</v>
+      <c r="T28" s="339">
+        <v>-0.56</v>
       </c>
     </row>
     <row r="29">
@@ -10404,7 +10436,7 @@
       <c r="C29" t="str">
         <v>600173</v>
       </c>
-      <c r="D29" s="358" t="str">
+      <c r="D29" s="362" t="str">
         <v>净卖: -1818.07万</v>
       </c>
       <c r="E29">
@@ -10419,41 +10451,41 @@
       <c r="H29">
         <v>-1.2</v>
       </c>
-      <c r="I29" s="359">
+      <c r="I29" s="363">
         <v>-8.91</v>
       </c>
-      <c r="J29" s="363">
+      <c r="J29" s="357">
         <v>0.2</v>
       </c>
-      <c r="K29" s="360">
+      <c r="K29" s="358">
         <v>4.45</v>
       </c>
-      <c r="L29" s="354">
+      <c r="L29" s="353">
         <v>-2.94</v>
       </c>
-      <c r="M29" s="361">
+      <c r="M29" s="359">
         <v>-7.89</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="354">
         <v>-12.45</v>
       </c>
-      <c r="O29" s="352">
+      <c r="O29" s="360">
         <v>-11.84</v>
       </c>
       <c r="P29" s="355">
         <v>-8.1</v>
       </c>
-      <c r="Q29" s="356">
+      <c r="Q29" s="364">
         <v>-5.36</v>
       </c>
-      <c r="R29" s="357">
+      <c r="R29" s="361">
         <v>-2.53</v>
       </c>
-      <c r="S29" s="362">
+      <c r="S29" s="352">
         <v>-3.54</v>
       </c>
-      <c r="T29" s="353">
-        <v>-22.27</v>
+      <c r="T29" s="356">
+        <v>-21.46</v>
       </c>
     </row>
     <row r="30">
@@ -10466,7 +10498,7 @@
       <c r="C30" t="str">
         <v>000637</v>
       </c>
-      <c r="D30" s="369" t="str">
+      <c r="D30" s="375" t="str">
         <v>净卖: -692.69万</v>
       </c>
       <c r="E30">
@@ -10481,41 +10513,41 @@
       <c r="H30">
         <v>-4.62</v>
       </c>
-      <c r="I30" s="365">
+      <c r="I30" s="369">
         <v>-5.65</v>
       </c>
-      <c r="J30" s="370">
+      <c r="J30" s="372">
         <v>3.83</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="370">
         <v>-0.81</v>
       </c>
-      <c r="L30" s="371">
+      <c r="L30" s="376">
         <v>0.6</v>
       </c>
-      <c r="M30" s="372">
+      <c r="M30" s="377">
         <v>-2.02</v>
       </c>
-      <c r="N30" s="366">
+      <c r="N30" s="365">
         <v>-6.25</v>
       </c>
-      <c r="O30" s="367">
+      <c r="O30" s="373">
         <v>-4.84</v>
       </c>
-      <c r="P30" s="374">
+      <c r="P30" s="366">
         <v>-4.23</v>
       </c>
-      <c r="Q30" s="375">
+      <c r="Q30" s="367">
         <v>-3.43</v>
       </c>
       <c r="R30" s="368">
         <v>-0.81</v>
       </c>
-      <c r="S30" s="373">
+      <c r="S30" s="371">
         <v>-1.01</v>
       </c>
-      <c r="T30" s="377">
-        <v>-11.69</v>
+      <c r="T30" s="374">
+        <v>-10.89</v>
       </c>
     </row>
     <row r="31">
@@ -10528,7 +10560,7 @@
       <c r="C31" t="str">
         <v>003038</v>
       </c>
-      <c r="D31" s="390" t="str">
+      <c r="D31" s="380" t="str">
         <v>净买: 1673.87万</v>
       </c>
       <c r="E31">
@@ -10543,41 +10575,41 @@
       <c r="H31">
         <v>-3.7</v>
       </c>
-      <c r="I31" s="387">
+      <c r="I31" s="388">
         <v>-1.79</v>
       </c>
-      <c r="J31" s="384">
+      <c r="J31" s="383">
         <v>-1.79</v>
       </c>
-      <c r="K31" s="388">
+      <c r="K31" s="378">
         <v>-7.21</v>
       </c>
-      <c r="L31" s="381">
+      <c r="L31" s="389">
         <v>-9</v>
       </c>
-      <c r="M31" s="378">
+      <c r="M31" s="390">
         <v>-11.53</v>
       </c>
-      <c r="N31" s="385">
+      <c r="N31" s="384">
         <v>-10.42</v>
       </c>
-      <c r="O31" s="386">
+      <c r="O31" s="385">
         <v>-9.79</v>
       </c>
-      <c r="P31" s="382">
+      <c r="P31" s="381">
         <v>-11.32</v>
       </c>
-      <c r="Q31" s="389">
+      <c r="Q31" s="386">
         <v>-11.26</v>
       </c>
-      <c r="R31" s="383">
+      <c r="R31" s="379">
         <v>-9.89</v>
       </c>
-      <c r="S31" s="379">
+      <c r="S31" s="387">
         <v>-11.89</v>
       </c>
-      <c r="T31" s="380">
-        <v>-20.32</v>
+      <c r="T31" s="382">
+        <v>-20.63</v>
       </c>
     </row>
     <row r="32">
@@ -10590,7 +10622,7 @@
       <c r="C32" t="str">
         <v>300390</v>
       </c>
-      <c r="D32" s="397" t="str">
+      <c r="D32" s="402" t="str">
         <v>净卖: -2712.20万</v>
       </c>
       <c r="E32">
@@ -10605,41 +10637,41 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="401">
+      <c r="I32" s="395">
         <v>15.32</v>
       </c>
-      <c r="J32" s="400">
+      <c r="J32" s="398">
         <v>19.24</v>
       </c>
-      <c r="K32" s="402">
+      <c r="K32" s="403">
         <v>21.18</v>
       </c>
-      <c r="L32" s="403">
+      <c r="L32" s="391">
         <v>17.01</v>
       </c>
-      <c r="M32" s="394">
+      <c r="M32" s="399">
         <v>39.41</v>
       </c>
-      <c r="N32" s="395">
+      <c r="N32" s="392">
         <v>44.54</v>
       </c>
-      <c r="O32" s="391">
+      <c r="O32" s="396">
         <v>73.45</v>
       </c>
-      <c r="P32" s="398">
+      <c r="P32" s="400">
         <v>64.28</v>
       </c>
-      <c r="Q32" s="392">
+      <c r="Q32" s="393">
         <v>66.69</v>
       </c>
-      <c r="R32" s="393">
+      <c r="R32" s="401">
         <v>76.84</v>
       </c>
-      <c r="S32" s="396">
+      <c r="S32" s="397">
         <v>41.99</v>
       </c>
-      <c r="T32" s="399">
-        <v>151.33</v>
+      <c r="T32" s="394">
+        <v>149.01</v>
       </c>
     </row>
     <row r="33">
@@ -10667,41 +10699,41 @@
       <c r="H33">
         <v>0.16</v>
       </c>
-      <c r="I33" s="414">
+      <c r="I33" s="404">
         <v>-10.16</v>
       </c>
-      <c r="J33" s="415">
+      <c r="J33" s="407">
         <v>-9.96</v>
       </c>
-      <c r="K33" s="416">
+      <c r="K33" s="405">
         <v>-18.94</v>
       </c>
-      <c r="L33" s="408">
+      <c r="L33" s="412">
         <v>-22.65</v>
       </c>
-      <c r="M33" s="409">
+      <c r="M33" s="408">
         <v>-22.75</v>
       </c>
-      <c r="N33" s="404">
+      <c r="N33" s="409">
         <v>-25.3</v>
       </c>
-      <c r="O33" s="410">
+      <c r="O33" s="414">
         <v>-26.94</v>
       </c>
-      <c r="P33" s="405">
+      <c r="P33" s="415">
         <v>-27.14</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="410">
         <v>-26.97</v>
       </c>
-      <c r="R33" s="406">
+      <c r="R33" s="411">
         <v>-27.01</v>
       </c>
-      <c r="S33" s="407">
+      <c r="S33" s="406">
         <v>-25.4</v>
       </c>
-      <c r="T33" s="411">
-        <v>-2.92</v>
+      <c r="T33" s="416">
+        <v>-8.55</v>
       </c>
     </row>
     <row r="34">
@@ -10714,7 +10746,7 @@
       <c r="C34" t="str">
         <v>603829</v>
       </c>
-      <c r="D34" s="428" t="str">
+      <c r="D34" s="426" t="str">
         <v>净卖: -2802.75万</v>
       </c>
       <c r="E34">
@@ -10729,41 +10761,41 @@
       <c r="H34">
         <v>0.15</v>
       </c>
-      <c r="I34" s="418">
+      <c r="I34" s="423">
         <v>-10.11</v>
       </c>
-      <c r="J34" s="419">
+      <c r="J34" s="427">
         <v>-14.21</v>
       </c>
-      <c r="K34" s="422">
+      <c r="K34" s="428">
         <v>-14.32</v>
       </c>
-      <c r="L34" s="423">
+      <c r="L34" s="419">
         <v>-17.16</v>
       </c>
-      <c r="M34" s="429">
+      <c r="M34" s="421">
         <v>-18.97</v>
       </c>
-      <c r="N34" s="425">
+      <c r="N34" s="424">
         <v>-19.19</v>
       </c>
-      <c r="O34" s="426">
+      <c r="O34" s="422">
         <v>-19.01</v>
       </c>
-      <c r="P34" s="417">
+      <c r="P34" s="420">
         <v>-19.05</v>
       </c>
-      <c r="Q34" s="420">
+      <c r="Q34" s="429">
         <v>-17.27</v>
       </c>
-      <c r="R34" s="421">
+      <c r="R34" s="417">
         <v>-15.92</v>
       </c>
-      <c r="S34" s="424">
+      <c r="S34" s="418">
         <v>-14.76</v>
       </c>
-      <c r="T34" s="427">
-        <v>7.67</v>
+      <c r="T34" s="425">
+        <v>1.42</v>
       </c>
     </row>
     <row r="35">
@@ -10776,7 +10808,7 @@
       <c r="C35" t="str">
         <v>920427</v>
       </c>
-      <c r="D35" s="433" t="str">
+      <c r="D35" s="432" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E35">
@@ -10791,41 +10823,41 @@
       <c r="H35">
         <v>-8.89</v>
       </c>
-      <c r="I35" s="439">
+      <c r="I35" s="442">
         <v>-21.22</v>
       </c>
-      <c r="J35" s="441">
+      <c r="J35" s="439">
         <v>-19.61</v>
       </c>
-      <c r="K35" s="442">
+      <c r="K35" s="435">
         <v>-23.32</v>
       </c>
-      <c r="L35" s="434">
+      <c r="L35" s="436">
         <v>-23.12</v>
       </c>
       <c r="M35" s="430">
         <v>-27.46</v>
       </c>
-      <c r="N35" s="435">
+      <c r="N35" s="433">
         <v>-27.71</v>
       </c>
-      <c r="O35" s="436">
+      <c r="O35" s="440">
         <v>-26.34</v>
       </c>
-      <c r="P35" s="437">
+      <c r="P35" s="434">
         <v>-23.22</v>
       </c>
-      <c r="Q35" s="438">
+      <c r="Q35" s="437">
         <v>-26.44</v>
       </c>
       <c r="R35" s="431">
         <v>-27.12</v>
       </c>
-      <c r="S35" s="440">
+      <c r="S35" s="441">
         <v>-26.68</v>
       </c>
-      <c r="T35" s="432">
-        <v>-38.39</v>
+      <c r="T35" s="438">
+        <v>-39.32</v>
       </c>
     </row>
     <row r="36">
@@ -10838,7 +10870,7 @@
       <c r="C36" t="str">
         <v>920427</v>
       </c>
-      <c r="D36" s="450" t="str">
+      <c r="D36" s="454" t="str">
         <v>净卖: -130.63万</v>
       </c>
       <c r="E36">
@@ -10853,41 +10885,41 @@
       <c r="H36">
         <v>-4.33</v>
       </c>
-      <c r="I36" s="445">
+      <c r="I36" s="455">
         <v>6.67</v>
       </c>
-      <c r="J36" s="448">
+      <c r="J36" s="443">
         <v>1.75</v>
       </c>
-      <c r="K36" s="453">
+      <c r="K36" s="444">
         <v>2.01</v>
       </c>
-      <c r="L36" s="446">
+      <c r="L36" s="449">
         <v>-3.75</v>
       </c>
-      <c r="M36" s="451">
+      <c r="M36" s="445">
         <v>-4.08</v>
       </c>
-      <c r="N36" s="454">
+      <c r="N36" s="450">
         <v>-2.27</v>
       </c>
-      <c r="O36" s="452">
+      <c r="O36" s="451">
         <v>1.88</v>
       </c>
-      <c r="P36" s="455">
+      <c r="P36" s="446">
         <v>-2.39</v>
       </c>
-      <c r="Q36" s="443">
+      <c r="Q36" s="447">
         <v>-3.3</v>
       </c>
-      <c r="R36" s="447">
+      <c r="R36" s="452">
         <v>-2.72</v>
       </c>
-      <c r="S36" s="449">
+      <c r="S36" s="453">
         <v>-6.54</v>
       </c>
-      <c r="T36" s="444">
-        <v>-18.25</v>
+      <c r="T36" s="448">
+        <v>-19.48</v>
       </c>
     </row>
     <row r="37">
@@ -10918,38 +10950,38 @@
       <c r="I37" s="461">
         <v>0</v>
       </c>
-      <c r="J37" s="462">
+      <c r="J37" s="458">
         <v>-5.52</v>
       </c>
       <c r="K37" s="468">
         <v>-0.12</v>
       </c>
-      <c r="L37" s="456">
+      <c r="L37" s="462">
         <v>-0.72</v>
       </c>
-      <c r="M37" s="457">
+      <c r="M37" s="466">
         <v>-6.3</v>
       </c>
-      <c r="N37" s="465">
+      <c r="N37" s="463">
         <v>-2.82</v>
       </c>
-      <c r="O37" s="459">
+      <c r="O37" s="456">
         <v>-3.3</v>
       </c>
-      <c r="P37" s="463">
+      <c r="P37" s="459">
         <v>-5.34</v>
       </c>
-      <c r="Q37" s="466">
+      <c r="Q37" s="457">
         <v>-4.92</v>
       </c>
-      <c r="R37" s="458">
+      <c r="R37" s="464">
         <v>0.72</v>
       </c>
-      <c r="S37" s="460">
+      <c r="S37" s="465">
         <v>-4.08</v>
       </c>
-      <c r="T37" s="464">
-        <v>1.5</v>
+      <c r="T37" s="460">
+        <v>3.66</v>
       </c>
     </row>
     <row r="38">
@@ -10962,7 +10994,7 @@
       <c r="C38" t="str">
         <v>603291</v>
       </c>
-      <c r="D38" s="472" t="str">
+      <c r="D38" s="475" t="str">
         <v>净买: 465.04万</v>
       </c>
       <c r="E38">
@@ -10977,41 +11009,41 @@
       <c r="H38">
         <v>1.97</v>
       </c>
-      <c r="I38" s="476">
+      <c r="I38" s="481">
         <v>-11.73</v>
       </c>
-      <c r="J38" s="473">
+      <c r="J38" s="472">
         <v>-11.73</v>
       </c>
-      <c r="K38" s="481">
+      <c r="K38" s="473">
         <v>-15.59</v>
       </c>
-      <c r="L38" s="477">
+      <c r="L38" s="469">
         <v>-15.51</v>
       </c>
-      <c r="M38" s="469">
+      <c r="M38" s="470">
         <v>-14.97</v>
       </c>
-      <c r="N38" s="471">
+      <c r="N38" s="478">
         <v>-15.66</v>
       </c>
-      <c r="O38" s="478">
+      <c r="O38" s="479">
         <v>-15.82</v>
       </c>
-      <c r="P38" s="474">
+      <c r="P38" s="476">
         <v>-16.05</v>
       </c>
-      <c r="Q38" s="479">
+      <c r="Q38" s="471">
         <v>-15.97</v>
       </c>
-      <c r="R38" s="480">
+      <c r="R38" s="477">
         <v>-15.51</v>
       </c>
-      <c r="S38" s="470">
+      <c r="S38" s="480">
         <v>-15.59</v>
       </c>
-      <c r="T38" s="475">
-        <v>-7.56</v>
+      <c r="T38" s="474">
+        <v>-6.56</v>
       </c>
     </row>
     <row r="39">
@@ -11024,7 +11056,7 @@
       <c r="C39" t="str">
         <v>603284</v>
       </c>
-      <c r="D39" s="484" t="str">
+      <c r="D39" s="492" t="str">
         <v>净买: 1322.73万</v>
       </c>
       <c r="E39">
@@ -11039,35 +11071,37 @@
       <c r="H39">
         <v>-0.79</v>
       </c>
-      <c r="I39" s="485">
+      <c r="I39" s="487">
         <v>4.15</v>
       </c>
-      <c r="J39" s="486">
+      <c r="J39" s="484">
         <v>7.16</v>
       </c>
       <c r="K39" s="488">
         <v>7.16</v>
       </c>
-      <c r="L39" s="487">
+      <c r="L39" s="491">
         <v>7.39</v>
       </c>
       <c r="M39" s="489">
         <v>7.45</v>
       </c>
-      <c r="N39" s="482">
+      <c r="N39" s="490">
         <v>8.48</v>
       </c>
-      <c r="O39" s="490">
+      <c r="O39" s="482">
         <v>6.71</v>
       </c>
       <c r="P39" s="483">
         <v>7.41</v>
       </c>
-      <c r="Q39" t="str"/>
+      <c r="Q39" s="485">
+        <v>7.64</v>
+      </c>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="491">
-        <v>7.41</v>
+      <c r="T39" s="486">
+        <v>7.64</v>
       </c>
     </row>
     <row r="40">
@@ -11080,7 +11114,7 @@
       <c r="C40" t="str">
         <v>600605</v>
       </c>
-      <c r="D40" s="494" t="str">
+      <c r="D40" s="498" t="str">
         <v>净卖: -789.04万</v>
       </c>
       <c r="E40">
@@ -11095,27 +11129,29 @@
       <c r="H40">
         <v>6.5</v>
       </c>
-      <c r="I40" s="495">
+      <c r="I40" s="499">
         <v>3.29</v>
       </c>
-      <c r="J40" s="496">
+      <c r="J40" s="493">
         <v>-0.16</v>
       </c>
-      <c r="K40" s="497">
+      <c r="K40" s="494">
         <v>-1.47</v>
       </c>
-      <c r="L40" s="492">
+      <c r="L40" s="495">
         <v>-3.1</v>
       </c>
-      <c r="M40" t="str"/>
+      <c r="M40" s="496">
+        <v>-2.08</v>
+      </c>
       <c r="N40" t="str"/>
       <c r="O40" t="str"/>
       <c r="P40" t="str"/>
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="493">
-        <v>-3.1</v>
+      <c r="T40" s="497">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="41">
@@ -11142,7 +11178,7 @@
         <v>39</v>
       </c>
       <c r="M41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N41">
         <v>38</v>
@@ -11154,7 +11190,7 @@
         <v>38</v>
       </c>
       <c r="Q41">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R41">
         <v>37</v>
@@ -11177,41 +11213,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="507">
+      <c r="I42" s="502">
         <v>38.46</v>
       </c>
-      <c r="J42" s="505">
+      <c r="J42" s="500">
         <v>41.03</v>
       </c>
-      <c r="K42" s="498">
+      <c r="K42" s="510">
         <v>38.46</v>
       </c>
-      <c r="L42" s="499">
+      <c r="L42" s="503">
         <v>35.9</v>
       </c>
-      <c r="M42" s="500">
-        <v>28.95</v>
-      </c>
-      <c r="N42" s="508">
+      <c r="M42" s="511">
+        <v>28.21</v>
+      </c>
+      <c r="N42" s="504">
         <v>26.32</v>
       </c>
-      <c r="O42" s="501">
+      <c r="O42" s="505">
         <v>31.58</v>
       </c>
-      <c r="P42" s="502">
+      <c r="P42" s="506">
         <v>34.21</v>
       </c>
-      <c r="Q42" s="503">
-        <v>24.32</v>
-      </c>
-      <c r="R42" s="509">
+      <c r="Q42" s="507">
+        <v>26.32</v>
+      </c>
+      <c r="R42" s="501">
         <v>29.73</v>
       </c>
-      <c r="S42" s="504">
+      <c r="S42" s="508">
         <v>18.92</v>
       </c>
-      <c r="T42" s="506">
-        <v>56.41</v>
+      <c r="T42" s="509">
+        <v>53.85</v>
       </c>
     </row>
     <row r="43">
@@ -11225,41 +11261,41 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="515">
+      <c r="I43" s="520">
         <v>-0.38</v>
       </c>
-      <c r="J43" s="516">
+      <c r="J43" s="515">
         <v>-0.74</v>
       </c>
-      <c r="K43" s="510">
+      <c r="K43" s="518">
         <v>-2.11</v>
       </c>
-      <c r="L43" s="511">
+      <c r="L43" s="521">
         <v>-4.11</v>
       </c>
-      <c r="M43" s="519">
-        <v>-5.26</v>
-      </c>
-      <c r="N43" s="520">
+      <c r="M43" s="516">
+        <v>-5.17</v>
+      </c>
+      <c r="N43" s="522">
         <v>-6.6</v>
       </c>
-      <c r="O43" s="517">
+      <c r="O43" s="519">
         <v>-5.4</v>
       </c>
       <c r="P43" s="512">
         <v>-5.71</v>
       </c>
-      <c r="Q43" s="513">
-        <v>-6.48</v>
-      </c>
-      <c r="R43" s="514">
+      <c r="Q43" s="523">
+        <v>-6.11</v>
+      </c>
+      <c r="R43" s="513">
         <v>-5.55</v>
       </c>
-      <c r="S43" s="518">
+      <c r="S43" s="514">
         <v>-7.91</v>
       </c>
-      <c r="T43" s="521">
-        <v>16.2</v>
+      <c r="T43" s="517">
+        <v>15.17</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/申港广东分/index.xlsx
+++ b/youzi/申港广东分/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="525">
+  <fills count="530">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF4C3C8"/>
         <bgColor/>
       </patternFill>
@@ -57,6 +63,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -75,24 +105,126 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -105,7 +237,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED2"/>
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,49 +429,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,7 +513,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,7 +597,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,7 +615,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0303F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,19 +651,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,13 +771,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
+        <fgColor rgb="FF1B7531"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,31 +783,2215 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,13 +3003,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,829 +3153,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1149,2011 +3183,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3176,7 +3206,42 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="524">
+  <borders count="529">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6849,7 +6914,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="524">
+  <cellXfs count="529">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8418,6 +8483,21 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="523" fillId="524" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="524" fillId="525" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="525" fillId="526" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="526" fillId="527" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="527" fillId="528" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="528" fillId="529" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8762,7 +8842,7 @@
       <c r="C2" t="str">
         <v>603110</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="8" t="str">
         <v>净买: 1763.82万</v>
       </c>
       <c r="E2">
@@ -8777,41 +8857,41 @@
       <c r="H2">
         <v>9.98</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="13">
         <v>9.98</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="10">
         <v>3.91</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <v>1.47</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="5">
         <v>11.62</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="6">
         <v>22.79</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="3">
         <v>15.02</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="7">
         <v>26.53</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="1">
         <v>32.65</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="4">
         <v>28.74</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="11">
         <v>21.77</v>
       </c>
       <c r="T2" s="12">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
@@ -8824,7 +8904,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 486.49万</v>
       </c>
       <c r="E3">
@@ -8839,41 +8919,41 @@
       <c r="H3">
         <v>6.6</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="16">
         <v>-11.36</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="17">
         <v>-13.44</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="22">
         <v>-4.79</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="18">
         <v>4.74</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="19">
         <v>-1.89</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="23">
         <v>7.93</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="20">
         <v>13.15</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="24">
         <v>9.82</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="25">
         <v>3.87</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="26">
         <v>6.53</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="21">
         <v>-4.11</v>
       </c>
-      <c r="T3" s="18">
-        <v>-13.68</v>
+      <c r="T3" s="14">
+        <v>-13.59</v>
       </c>
     </row>
     <row r="4">
@@ -8886,7 +8966,7 @@
       <c r="C4" t="str">
         <v>603881</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 7242.53万</v>
       </c>
       <c r="E4">
@@ -8901,41 +8981,41 @@
       <c r="H4">
         <v>8.87</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="34">
         <v>1.04</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="35">
         <v>11.14</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="27">
         <v>0.03</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="36">
         <v>7.5</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="37">
         <v>8.74</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="38">
         <v>19.61</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="32">
         <v>25.9</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="28">
         <v>21.45</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="33">
         <v>15.56</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="29">
         <v>9.81</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="30">
         <v>-0.74</v>
       </c>
-      <c r="T4" s="34">
-        <v>12.83</v>
+      <c r="T4" s="39">
+        <v>12.36</v>
       </c>
     </row>
     <row r="5">
@@ -8963,41 +9043,41 @@
       <c r="H5">
         <v>-4.56</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="49">
         <v>-5.7</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="45">
         <v>1.34</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="50">
         <v>2.51</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="40">
         <v>12.77</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="41">
         <v>18.69</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="51">
         <v>14.5</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="47">
         <v>8.94</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="46">
         <v>3.52</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="52">
         <v>-6.42</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="48">
         <v>-4.83</v>
       </c>
       <c r="S5" s="42">
         <v>-3.18</v>
       </c>
       <c r="T5" s="43">
-        <v>6.37</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="6">
@@ -9010,7 +9090,7 @@
       <c r="C6" t="str">
         <v>000818</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 5099.54万</v>
       </c>
       <c r="E6">
@@ -9025,41 +9105,41 @@
       <c r="H6">
         <v>5.63</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="61">
         <v>4.13</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="57">
         <v>14.56</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="64">
         <v>7.97</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="62">
         <v>-2.83</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="63">
         <v>-12.53</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="58">
         <v>-15.63</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="59">
         <v>-12.8</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="53">
         <v>-16.13</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="60">
         <v>-19.84</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="54">
         <v>-20.37</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="55">
         <v>-19.6</v>
       </c>
       <c r="T6" s="56">
-        <v>-61.47</v>
+        <v>-61.17</v>
       </c>
     </row>
     <row r="7">
@@ -9072,7 +9152,7 @@
       <c r="C7" t="str">
         <v>600590</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="78" t="str">
         <v>净买: 1013.84万</v>
       </c>
       <c r="E7">
@@ -9087,41 +9167,41 @@
       <c r="H7">
         <v>10.05</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="66">
         <v>0</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="71">
         <v>-2.39</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="67">
         <v>7.39</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="68">
         <v>1.85</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="76">
         <v>1.63</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="73">
         <v>-5.76</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="74">
         <v>-3.48</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="77">
         <v>6.2</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="69">
         <v>16.85</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="75">
         <v>26.41</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="72">
         <v>21.74</v>
       </c>
-      <c r="T7" s="67">
-        <v>88.37</v>
+      <c r="T7" s="70">
+        <v>85.43</v>
       </c>
     </row>
     <row r="8">
@@ -9134,7 +9214,7 @@
       <c r="C8" t="str">
         <v>000818</v>
       </c>
-      <c r="D8" s="86" t="str">
+      <c r="D8" s="88" t="str">
         <v>净卖: -5301.29万</v>
       </c>
       <c r="E8">
@@ -9149,41 +9229,41 @@
       <c r="H8">
         <v>-10</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="83">
         <v>0</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="89">
         <v>-9.99</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="80">
         <v>-13.17</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="84">
         <v>-10.26</v>
       </c>
-      <c r="M8" s="80">
+      <c r="M8" s="85">
         <v>-13.69</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="87">
         <v>-17.51</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="81">
         <v>-18.06</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="90">
         <v>-17.26</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="82">
         <v>-14.79</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="91">
         <v>-16.85</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="79">
         <v>-14.02</v>
       </c>
-      <c r="T8" s="85">
-        <v>-60.35</v>
+      <c r="T8" s="86">
+        <v>-60.04</v>
       </c>
     </row>
     <row r="9">
@@ -9196,7 +9276,7 @@
       <c r="C9" t="str">
         <v>002290</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="97" t="str">
         <v>净卖: -2168.44万</v>
       </c>
       <c r="E9">
@@ -9211,41 +9291,41 @@
       <c r="H9">
         <v>-9.5</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="98">
         <v>-0.54</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="103">
         <v>0</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="94">
         <v>0.33</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="104">
         <v>3.33</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="92">
         <v>-7</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="99">
         <v>-1.67</v>
       </c>
       <c r="O9" s="100">
         <v>6.04</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="95">
         <v>7.58</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="96">
         <v>12.71</v>
       </c>
-      <c r="R9" s="98">
+      <c r="R9" s="93">
         <v>16.92</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="101">
         <v>12.79</v>
       </c>
-      <c r="T9" s="104">
-        <v>196.54</v>
+      <c r="T9" s="102">
+        <v>238.96</v>
       </c>
     </row>
     <row r="10">
@@ -9258,7 +9338,7 @@
       <c r="C10" t="str">
         <v>605300</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="110" t="str">
         <v>净买: 1145.88万</v>
       </c>
       <c r="E10">
@@ -9273,10 +9353,10 @@
       <c r="H10">
         <v>1.49</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="108">
         <v>8.41</v>
       </c>
-      <c r="J10" s="113">
+      <c r="J10" s="109">
         <v>-2.41</v>
       </c>
       <c r="K10" s="116">
@@ -9285,29 +9365,29 @@
       <c r="L10" s="117">
         <v>-15</v>
       </c>
-      <c r="M10" s="105">
+      <c r="M10" s="111">
         <v>-12.88</v>
       </c>
-      <c r="N10" s="114">
+      <c r="N10" s="105">
         <v>-14.71</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="106">
         <v>-15.65</v>
       </c>
-      <c r="P10" s="115">
+      <c r="P10" s="107">
         <v>-16.18</v>
       </c>
-      <c r="Q10" s="108">
+      <c r="Q10" s="112">
         <v>-16.82</v>
       </c>
-      <c r="R10" s="111">
+      <c r="R10" s="113">
         <v>-18.35</v>
       </c>
-      <c r="S10" s="112">
+      <c r="S10" s="114">
         <v>-15.18</v>
       </c>
-      <c r="T10" s="106">
-        <v>-35.65</v>
+      <c r="T10" s="115">
+        <v>-35.76</v>
       </c>
     </row>
     <row r="11">
@@ -9320,7 +9400,7 @@
       <c r="C11" t="str">
         <v>605100</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="118" t="str">
         <v>净买: 1795.46万</v>
       </c>
       <c r="E11">
@@ -9335,41 +9415,41 @@
       <c r="H11">
         <v>9.99</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="119">
         <v>0</v>
       </c>
-      <c r="J11" s="130">
+      <c r="J11" s="123">
         <v>-9.16</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="128">
         <v>-0.08</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="120">
         <v>0</v>
       </c>
-      <c r="M11" s="126">
+      <c r="M11" s="124">
         <v>9.99</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="121">
         <v>-0.99</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="126">
         <v>8.93</v>
       </c>
-      <c r="P11" s="121">
+      <c r="P11" s="122">
         <v>19.83</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="127">
         <v>12.16</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="129">
         <v>23.38</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="125">
         <v>13.07</v>
       </c>
-      <c r="T11" s="128">
-        <v>92.42</v>
+      <c r="T11" s="130">
+        <v>92.54</v>
       </c>
     </row>
     <row r="12">
@@ -9382,7 +9462,7 @@
       <c r="C12" t="str">
         <v>605300</v>
       </c>
-      <c r="D12" s="138" t="str">
+      <c r="D12" s="135" t="str">
         <v>净卖: -1034.72万</v>
       </c>
       <c r="E12">
@@ -9397,41 +9477,41 @@
       <c r="H12">
         <v>-5.36</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="136">
         <v>2.26</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="137">
         <v>4.81</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="140">
         <v>2.62</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="141">
         <v>1.49</v>
       </c>
-      <c r="M12" s="142">
+      <c r="M12" s="134">
         <v>0.85</v>
       </c>
-      <c r="N12" s="133">
+      <c r="N12" s="142">
         <v>0.07</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="143">
         <v>-1.77</v>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="131">
         <v>2.05</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="138">
         <v>0.85</v>
       </c>
-      <c r="R12" s="143">
+      <c r="R12" s="132">
         <v>0.21</v>
       </c>
-      <c r="S12" s="135">
+      <c r="S12" s="133">
         <v>-0.92</v>
       </c>
-      <c r="T12" s="136">
-        <v>-22.58</v>
+      <c r="T12" s="139">
+        <v>-22.72</v>
       </c>
     </row>
     <row r="13">
@@ -9444,7 +9524,7 @@
       <c r="C13" t="str">
         <v>002114</v>
       </c>
-      <c r="D13" s="153" t="str">
+      <c r="D13" s="156" t="str">
         <v>净买: 1554.85万</v>
       </c>
       <c r="E13">
@@ -9459,41 +9539,41 @@
       <c r="H13">
         <v>9.83</v>
       </c>
-      <c r="I13" s="145">
+      <c r="I13" s="144">
         <v>0.13</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="145">
         <v>-1.41</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="149">
         <v>-4.6</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="150">
         <v>-6.65</v>
       </c>
       <c r="M13" s="146">
         <v>-6.01</v>
       </c>
-      <c r="N13" s="151">
+      <c r="N13" s="152">
         <v>-6.52</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="153">
         <v>-5.5</v>
       </c>
       <c r="P13" s="147">
         <v>-10.1</v>
       </c>
-      <c r="Q13" s="152">
+      <c r="Q13" s="154">
         <v>-9.59</v>
       </c>
       <c r="R13" s="148">
         <v>-10.87</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="151">
         <v>-11.76</v>
       </c>
-      <c r="T13" s="150">
-        <v>15.47</v>
+      <c r="T13" s="155">
+        <v>15.6</v>
       </c>
     </row>
     <row r="14">
@@ -9506,7 +9586,7 @@
       <c r="C14" t="str">
         <v>605303</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="169" t="str">
         <v>净买: 1578.26万</v>
       </c>
       <c r="E14">
@@ -9521,41 +9601,41 @@
       <c r="H14">
         <v>10.03</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="157">
         <v>0</v>
       </c>
-      <c r="J14" s="161">
+      <c r="J14" s="158">
         <v>-7.6</v>
       </c>
-      <c r="K14" s="169">
+      <c r="K14" s="162">
         <v>-13.68</v>
       </c>
-      <c r="L14" s="164">
+      <c r="L14" s="165">
         <v>-20.06</v>
       </c>
       <c r="M14" s="166">
         <v>-20.21</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="159">
         <v>-21.58</v>
       </c>
-      <c r="O14" s="165">
+      <c r="O14" s="160">
         <v>-22.87</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="168">
         <v>-23.86</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="163">
         <v>-24.62</v>
       </c>
-      <c r="R14" s="162">
+      <c r="R14" s="164">
         <v>-27.13</v>
       </c>
-      <c r="S14" s="163">
+      <c r="S14" s="167">
         <v>-26.6</v>
       </c>
-      <c r="T14" s="159">
-        <v>70.82</v>
+      <c r="T14" s="161">
+        <v>74.24</v>
       </c>
     </row>
     <row r="15">
@@ -9568,7 +9648,7 @@
       <c r="C15" t="str">
         <v>605303</v>
       </c>
-      <c r="D15" s="172" t="str">
+      <c r="D15" s="173" t="str">
         <v>净卖: -1462.35万</v>
       </c>
       <c r="E15">
@@ -9583,41 +9663,41 @@
       <c r="H15">
         <v>-2.55</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="174">
         <v>-4.97</v>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="175">
         <v>-5.15</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="178">
         <v>-6.78</v>
       </c>
-      <c r="L15" s="179">
+      <c r="L15" s="176">
         <v>-8.31</v>
       </c>
-      <c r="M15" s="180">
+      <c r="M15" s="179">
         <v>-9.49</v>
       </c>
-      <c r="N15" s="181">
+      <c r="N15" s="180">
         <v>-10.39</v>
       </c>
-      <c r="O15" s="176">
+      <c r="O15" s="170">
         <v>-13.37</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="181">
         <v>-12.74</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="177">
         <v>-14.27</v>
       </c>
       <c r="R15" s="171">
         <v>-15.54</v>
       </c>
-      <c r="S15" s="177">
+      <c r="S15" s="182">
         <v>-16.71</v>
       </c>
-      <c r="T15" s="178">
-        <v>103.07</v>
+      <c r="T15" s="172">
+        <v>107.14</v>
       </c>
     </row>
     <row r="16">
@@ -9630,7 +9710,7 @@
       <c r="C16" t="str">
         <v>600301</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="188" t="str">
         <v>净卖: -3080.81万</v>
       </c>
       <c r="E16">
@@ -9645,41 +9725,41 @@
       <c r="H16">
         <v>-2.8</v>
       </c>
-      <c r="I16" s="189">
+      <c r="I16" s="185">
         <v>-4.62</v>
       </c>
-      <c r="J16" s="190">
+      <c r="J16" s="189">
         <v>-5.96</v>
       </c>
-      <c r="K16" s="194">
+      <c r="K16" s="183">
         <v>-4.88</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="186">
         <v>-5.27</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="190">
         <v>-3.31</v>
       </c>
-      <c r="N16" s="186">
+      <c r="N16" s="187">
         <v>-7.19</v>
       </c>
       <c r="O16" s="191">
         <v>-7.88</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="192">
         <v>-7.88</v>
       </c>
-      <c r="Q16" s="195">
+      <c r="Q16" s="193">
         <v>-10.35</v>
       </c>
-      <c r="R16" s="187">
+      <c r="R16" s="195">
         <v>-11.15</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="194">
         <v>-14.38</v>
       </c>
-      <c r="T16" s="188">
-        <v>111.46</v>
+      <c r="T16" s="184">
+        <v>107.85</v>
       </c>
     </row>
     <row r="17">
@@ -9692,7 +9772,7 @@
       <c r="C17" t="str">
         <v>000815</v>
       </c>
-      <c r="D17" s="197" t="str">
+      <c r="D17" s="201" t="str">
         <v>净买: 5327.66万</v>
       </c>
       <c r="E17">
@@ -9707,41 +9787,41 @@
       <c r="H17">
         <v>2.39</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="202">
         <v>2.95</v>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="208">
         <v>-3.14</v>
       </c>
-      <c r="K17" s="207">
+      <c r="K17" s="205">
         <v>-4.8</v>
       </c>
-      <c r="L17" s="198">
+      <c r="L17" s="203">
         <v>-6.52</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="198">
         <v>-12.98</v>
       </c>
-      <c r="N17" s="205">
+      <c r="N17" s="199">
         <v>-17.22</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="206">
         <v>-16.91</v>
       </c>
       <c r="P17" s="200">
         <v>-20.79</v>
       </c>
-      <c r="Q17" s="206">
+      <c r="Q17" s="204">
         <v>-20.3</v>
       </c>
-      <c r="R17" s="201">
+      <c r="R17" s="196">
         <v>-19.74</v>
       </c>
-      <c r="S17" s="196">
+      <c r="S17" s="197">
         <v>-20.85</v>
       </c>
-      <c r="T17" s="202">
-        <v>28.47</v>
+      <c r="T17" s="207">
+        <v>17.9</v>
       </c>
     </row>
     <row r="18">
@@ -9754,7 +9834,7 @@
       <c r="C18" t="str">
         <v>603315</v>
       </c>
-      <c r="D18" s="214" t="str">
+      <c r="D18" s="217" t="str">
         <v>净买: 2006.31万</v>
       </c>
       <c r="E18">
@@ -9772,38 +9852,38 @@
       <c r="I18" s="218">
         <v>0</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="210">
         <v>9.99</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="219">
         <v>20.99</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="211">
         <v>8.87</v>
       </c>
-      <c r="M18" s="220">
+      <c r="M18" s="212">
         <v>-2</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="220">
         <v>-11.81</v>
       </c>
       <c r="O18" s="215">
         <v>-12.8</v>
       </c>
-      <c r="P18" s="221">
+      <c r="P18" s="216">
         <v>-17.49</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="214">
         <v>-18.11</v>
       </c>
-      <c r="R18" s="211">
+      <c r="R18" s="221">
         <v>-16.36</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="213">
         <v>-16.55</v>
       </c>
-      <c r="T18" s="213">
-        <v>9.43</v>
+      <c r="T18" s="209">
+        <v>14.3</v>
       </c>
     </row>
     <row r="19">
@@ -9816,7 +9896,7 @@
       <c r="C19" t="str">
         <v>603315</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="225" t="str">
         <v>净卖: -2227.67万</v>
       </c>
       <c r="E19">
@@ -9831,41 +9911,41 @@
       <c r="H19">
         <v>-4.2</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="226">
         <v>14.82</v>
       </c>
-      <c r="J19" s="232">
+      <c r="J19" s="227">
         <v>3.32</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="228">
         <v>-6.99</v>
       </c>
-      <c r="L19" s="227">
+      <c r="L19" s="222">
         <v>-16.3</v>
       </c>
-      <c r="M19" s="225">
+      <c r="M19" s="231">
         <v>-17.25</v>
       </c>
-      <c r="N19" s="226">
+      <c r="N19" s="229">
         <v>-21.7</v>
       </c>
-      <c r="O19" s="234">
+      <c r="O19" s="223">
         <v>-22.29</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="230">
         <v>-20.63</v>
       </c>
-      <c r="Q19" s="228">
+      <c r="Q19" s="224">
         <v>-20.81</v>
       </c>
-      <c r="R19" s="223">
+      <c r="R19" s="232">
         <v>-20.09</v>
       </c>
-      <c r="S19" s="229">
+      <c r="S19" s="233">
         <v>-22.05</v>
       </c>
-      <c r="T19" s="230">
-        <v>3.85</v>
+      <c r="T19" s="234">
+        <v>8.48</v>
       </c>
     </row>
     <row r="20">
@@ -9878,7 +9958,7 @@
       <c r="C20" t="str">
         <v>000737</v>
       </c>
-      <c r="D20" s="235" t="str">
+      <c r="D20" s="238" t="str">
         <v>净买: 2607.05万</v>
       </c>
       <c r="E20">
@@ -9893,41 +9973,41 @@
       <c r="H20">
         <v>0.79</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="245">
         <v>9.19</v>
       </c>
-      <c r="J20" s="240">
+      <c r="J20" s="246">
         <v>15.54</v>
       </c>
-      <c r="K20" s="243">
+      <c r="K20" s="239">
         <v>20.43</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="247">
         <v>11.93</v>
       </c>
-      <c r="M20" s="238">
+      <c r="M20" s="235">
         <v>4.79</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="240">
         <v>2.64</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="242">
         <v>2.83</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="243">
         <v>1.08</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="244">
         <v>-2.15</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="236">
         <v>-11.93</v>
       </c>
-      <c r="S20" s="239">
+      <c r="S20" s="241">
         <v>-19.65</v>
       </c>
-      <c r="T20" s="247">
-        <v>38.12</v>
+      <c r="T20" s="237">
+        <v>34.8</v>
       </c>
     </row>
     <row r="21">
@@ -9955,41 +10035,41 @@
       <c r="H21">
         <v>9.36</v>
       </c>
-      <c r="I21" s="260">
+      <c r="I21" s="249">
         <v>-14.36</v>
       </c>
-      <c r="J21" s="252">
+      <c r="J21" s="260">
         <v>-22.92</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="250">
         <v>-25.67</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="252">
         <v>-28.8</v>
       </c>
-      <c r="M21" s="249">
+      <c r="M21" s="248">
         <v>-29.11</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="253">
         <v>-26.05</v>
       </c>
-      <c r="O21" s="257">
+      <c r="O21" s="251">
         <v>-28.27</v>
       </c>
-      <c r="P21" s="250">
+      <c r="P21" s="254">
         <v>-29.03</v>
       </c>
-      <c r="Q21" s="258">
+      <c r="Q21" s="257">
         <v>-29.95</v>
       </c>
-      <c r="R21" s="251">
+      <c r="R21" s="255">
         <v>-36.97</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="256">
         <v>-35.91</v>
       </c>
-      <c r="T21" s="255">
-        <v>-33.23</v>
+      <c r="T21" s="258">
+        <v>-36.13</v>
       </c>
     </row>
     <row r="22">
@@ -10002,7 +10082,7 @@
       <c r="C22" t="str">
         <v>600727</v>
       </c>
-      <c r="D22" s="268" t="str">
+      <c r="D22" s="272" t="str">
         <v>净卖: -2220.75万</v>
       </c>
       <c r="E22">
@@ -10017,41 +10097,41 @@
       <c r="H22">
         <v>4.31</v>
       </c>
-      <c r="I22" s="266">
+      <c r="I22" s="270">
         <v>-1.31</v>
       </c>
-      <c r="J22" s="269">
+      <c r="J22" s="264">
         <v>0.76</v>
       </c>
-      <c r="K22" s="261">
+      <c r="K22" s="265">
         <v>-9.36</v>
       </c>
-      <c r="L22" s="262">
+      <c r="L22" s="266">
         <v>-13.71</v>
       </c>
-      <c r="M22" s="272">
+      <c r="M22" s="267">
         <v>-11.32</v>
       </c>
-      <c r="N22" s="263">
+      <c r="N22" s="262">
         <v>-12.08</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="273">
         <v>-7.51</v>
       </c>
-      <c r="P22" s="264">
+      <c r="P22" s="261">
         <v>-16.76</v>
       </c>
-      <c r="Q22" s="271">
+      <c r="Q22" s="268">
         <v>-15.13</v>
       </c>
-      <c r="R22" s="265">
+      <c r="R22" s="269">
         <v>-16.76</v>
       </c>
-      <c r="S22" s="267">
+      <c r="S22" s="271">
         <v>-15.67</v>
       </c>
-      <c r="T22" s="273">
-        <v>-13.71</v>
+      <c r="T22" s="263">
+        <v>-12.73</v>
       </c>
     </row>
     <row r="23">
@@ -10079,41 +10159,41 @@
       <c r="H23">
         <v>9.99</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="282">
         <v>0</v>
       </c>
-      <c r="J23" s="281">
+      <c r="J23" s="285">
         <v>-8.55</v>
       </c>
       <c r="K23" s="277">
         <v>-13.73</v>
       </c>
-      <c r="L23" s="278">
+      <c r="L23" s="283">
         <v>-17.5</v>
       </c>
-      <c r="M23" s="283">
+      <c r="M23" s="278">
         <v>-20.66</v>
       </c>
-      <c r="N23" s="274">
+      <c r="N23" s="279">
         <v>-28.6</v>
       </c>
-      <c r="O23" s="284">
+      <c r="O23" s="280">
         <v>-31.02</v>
       </c>
-      <c r="P23" s="279">
+      <c r="P23" s="274">
         <v>-31.09</v>
       </c>
-      <c r="Q23" s="285">
+      <c r="Q23" s="284">
         <v>-29.48</v>
       </c>
-      <c r="R23" s="280">
+      <c r="R23" s="275">
         <v>-28.33</v>
       </c>
-      <c r="S23" s="275">
+      <c r="S23" s="286">
         <v>-26.72</v>
       </c>
-      <c r="T23" s="282">
-        <v>-20.12</v>
+      <c r="T23" s="281">
+        <v>-19.31</v>
       </c>
     </row>
     <row r="24">
@@ -10141,41 +10221,41 @@
       <c r="H24">
         <v>-3.3</v>
       </c>
-      <c r="I24" s="291">
+      <c r="I24" s="293">
         <v>-6.9</v>
       </c>
-      <c r="J24" s="296">
+      <c r="J24" s="288">
         <v>-8.84</v>
       </c>
-      <c r="K24" s="299">
+      <c r="K24" s="294">
         <v>-7.5</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="289">
         <v>-7.64</v>
       </c>
-      <c r="M24" s="293">
+      <c r="M24" s="290">
         <v>-12.93</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="291">
         <v>-21.63</v>
       </c>
-      <c r="O24" s="297">
+      <c r="O24" s="295">
         <v>-20.23</v>
       </c>
-      <c r="P24" s="289">
+      <c r="P24" s="297">
         <v>-21.57</v>
       </c>
-      <c r="Q24" s="290">
+      <c r="Q24" s="296">
         <v>-20.09</v>
       </c>
-      <c r="R24" s="294">
+      <c r="R24" s="292">
         <v>-20.03</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="298">
         <v>-17.62</v>
       </c>
-      <c r="T24" s="298">
-        <v>8.91</v>
+      <c r="T24" s="299">
+        <v>10.58</v>
       </c>
     </row>
     <row r="25">
@@ -10188,7 +10268,7 @@
       <c r="C25" t="str">
         <v>001333</v>
       </c>
-      <c r="D25" s="303" t="str">
+      <c r="D25" s="304" t="str">
         <v>净买: 1650.82万</v>
       </c>
       <c r="E25">
@@ -10203,41 +10283,41 @@
       <c r="H25">
         <v>-1.88</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="302">
         <v>12.11</v>
       </c>
-      <c r="J25" s="306">
+      <c r="J25" s="305">
         <v>23.33</v>
       </c>
-      <c r="K25" s="304">
+      <c r="K25" s="303">
         <v>11.01</v>
       </c>
-      <c r="L25" s="309">
+      <c r="L25" s="306">
         <v>-0.08</v>
       </c>
-      <c r="M25" s="307">
+      <c r="M25" s="312">
         <v>-10.07</v>
       </c>
-      <c r="N25" s="300">
+      <c r="N25" s="307">
         <v>-18.1</v>
       </c>
-      <c r="O25" s="301">
+      <c r="O25" s="308">
         <v>-17.47</v>
       </c>
-      <c r="P25" s="310">
+      <c r="P25" s="300">
         <v>-15.81</v>
       </c>
-      <c r="Q25" s="305">
+      <c r="Q25" s="309">
         <v>-10.96</v>
       </c>
-      <c r="R25" s="311">
+      <c r="R25" s="301">
         <v>-8.75</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="310">
         <v>-10.28</v>
       </c>
-      <c r="T25" s="302">
-        <v>5.65</v>
+      <c r="T25" s="311">
+        <v>3.19</v>
       </c>
     </row>
     <row r="26">
@@ -10250,7 +10330,7 @@
       <c r="C26" t="str">
         <v>002365</v>
       </c>
-      <c r="D26" s="317" t="str">
+      <c r="D26" s="314" t="str">
         <v>净卖: -918.91万</v>
       </c>
       <c r="E26">
@@ -10265,41 +10345,41 @@
       <c r="H26">
         <v>-8.32</v>
       </c>
-      <c r="I26" s="321">
+      <c r="I26" s="318">
         <v>20.02</v>
       </c>
-      <c r="J26" s="314">
+      <c r="J26" s="323">
         <v>15.9</v>
       </c>
       <c r="K26" s="315">
         <v>22.97</v>
       </c>
-      <c r="L26" s="318">
+      <c r="L26" s="316">
         <v>19.43</v>
       </c>
-      <c r="M26" s="322">
+      <c r="M26" s="320">
         <v>16.02</v>
       </c>
-      <c r="N26" s="323">
+      <c r="N26" s="321">
         <v>10.37</v>
       </c>
       <c r="O26" s="319">
         <v>9.42</v>
       </c>
-      <c r="P26" s="320">
+      <c r="P26" s="317">
         <v>11.66</v>
       </c>
-      <c r="Q26" s="324">
+      <c r="Q26" s="322">
         <v>6.24</v>
       </c>
-      <c r="R26" s="325">
+      <c r="R26" s="324">
         <v>16.84</v>
       </c>
-      <c r="S26" s="313">
+      <c r="S26" s="325">
         <v>20.49</v>
       </c>
-      <c r="T26" s="316">
-        <v>58.54</v>
+      <c r="T26" s="313">
+        <v>52.18</v>
       </c>
     </row>
     <row r="27">
@@ -10312,7 +10392,7 @@
       <c r="C27" t="str">
         <v>600180</v>
       </c>
-      <c r="D27" s="327" t="str">
+      <c r="D27" s="330" t="str">
         <v>净卖: -1973.71万</v>
       </c>
       <c r="E27">
@@ -10327,41 +10407,41 @@
       <c r="H27">
         <v>-4.9</v>
       </c>
-      <c r="I27" s="336">
+      <c r="I27" s="327">
         <v>0.21</v>
       </c>
-      <c r="J27" s="337">
+      <c r="J27" s="328">
         <v>-1.93</v>
       </c>
       <c r="K27" s="331">
         <v>-3.86</v>
       </c>
-      <c r="L27" s="338">
+      <c r="L27" s="332">
         <v>-2.58</v>
       </c>
-      <c r="M27" s="326">
+      <c r="M27" s="336">
         <v>-1.5</v>
       </c>
-      <c r="N27" s="332">
+      <c r="N27" s="333">
         <v>-3.43</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="334">
         <v>-5.79</v>
       </c>
-      <c r="P27" s="328">
+      <c r="P27" s="337">
         <v>-4.94</v>
       </c>
       <c r="Q27" s="329">
         <v>-8.58</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="338">
         <v>-7.73</v>
       </c>
-      <c r="S27" s="334">
+      <c r="S27" s="335">
         <v>-8.37</v>
       </c>
-      <c r="T27" s="335">
-        <v>-31.12</v>
+      <c r="T27" s="326">
+        <v>-36.48</v>
       </c>
     </row>
     <row r="28">
@@ -10374,7 +10454,7 @@
       <c r="C28" t="str">
         <v>002743</v>
       </c>
-      <c r="D28" s="343" t="str">
+      <c r="D28" s="339" t="str">
         <v>净卖: -345.80万</v>
       </c>
       <c r="E28">
@@ -10389,41 +10469,41 @@
       <c r="H28">
         <v>-9.98</v>
       </c>
-      <c r="I28" s="346">
+      <c r="I28" s="347">
         <v>0</v>
       </c>
-      <c r="J28" s="349">
+      <c r="J28" s="340">
         <v>-5.83</v>
       </c>
-      <c r="K28" s="340">
+      <c r="K28" s="344">
         <v>-3.38</v>
       </c>
-      <c r="L28" s="350">
+      <c r="L28" s="348">
         <v>0.75</v>
       </c>
-      <c r="M28" s="344">
+      <c r="M28" s="342">
         <v>1.88</v>
       </c>
-      <c r="N28" s="347">
+      <c r="N28" s="345">
         <v>3.01</v>
       </c>
-      <c r="O28" s="341">
+      <c r="O28" s="349">
         <v>3.95</v>
       </c>
-      <c r="P28" s="348">
+      <c r="P28" s="350">
         <v>0.75</v>
       </c>
-      <c r="Q28" s="351">
+      <c r="Q28" s="341">
         <v>-0.19</v>
       </c>
-      <c r="R28" s="345">
+      <c r="R28" s="343">
         <v>1.5</v>
       </c>
-      <c r="S28" s="342">
+      <c r="S28" s="346">
         <v>5.83</v>
       </c>
-      <c r="T28" s="339">
-        <v>-0.56</v>
+      <c r="T28" s="351">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="29">
@@ -10451,41 +10531,41 @@
       <c r="H29">
         <v>-1.2</v>
       </c>
-      <c r="I29" s="363">
+      <c r="I29" s="354">
         <v>-8.91</v>
       </c>
-      <c r="J29" s="357">
+      <c r="J29" s="355">
         <v>0.2</v>
       </c>
-      <c r="K29" s="358">
+      <c r="K29" s="363">
         <v>4.45</v>
       </c>
-      <c r="L29" s="353">
+      <c r="L29" s="361">
         <v>-2.94</v>
       </c>
-      <c r="M29" s="359">
+      <c r="M29" s="358">
         <v>-7.89</v>
       </c>
-      <c r="N29" s="354">
+      <c r="N29" s="364">
         <v>-12.45</v>
       </c>
-      <c r="O29" s="360">
+      <c r="O29" s="356">
         <v>-11.84</v>
       </c>
-      <c r="P29" s="355">
+      <c r="P29" s="352">
         <v>-8.1</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="359">
         <v>-5.36</v>
       </c>
-      <c r="R29" s="361">
+      <c r="R29" s="357">
         <v>-2.53</v>
       </c>
-      <c r="S29" s="352">
+      <c r="S29" s="360">
         <v>-3.54</v>
       </c>
-      <c r="T29" s="356">
-        <v>-21.46</v>
+      <c r="T29" s="353">
+        <v>-24.8</v>
       </c>
     </row>
     <row r="30">
@@ -10498,7 +10578,7 @@
       <c r="C30" t="str">
         <v>000637</v>
       </c>
-      <c r="D30" s="375" t="str">
+      <c r="D30" s="372" t="str">
         <v>净卖: -692.69万</v>
       </c>
       <c r="E30">
@@ -10513,41 +10593,41 @@
       <c r="H30">
         <v>-4.62</v>
       </c>
-      <c r="I30" s="369">
+      <c r="I30" s="375">
         <v>-5.65</v>
       </c>
-      <c r="J30" s="372">
+      <c r="J30" s="367">
         <v>3.83</v>
       </c>
-      <c r="K30" s="370">
+      <c r="K30" s="376">
         <v>-0.81</v>
       </c>
-      <c r="L30" s="376">
+      <c r="L30" s="377">
         <v>0.6</v>
       </c>
-      <c r="M30" s="377">
+      <c r="M30" s="368">
         <v>-2.02</v>
       </c>
-      <c r="N30" s="365">
+      <c r="N30" s="369">
         <v>-6.25</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="365">
         <v>-4.84</v>
       </c>
-      <c r="P30" s="366">
+      <c r="P30" s="370">
         <v>-4.23</v>
       </c>
-      <c r="Q30" s="367">
+      <c r="Q30" s="366">
         <v>-3.43</v>
       </c>
-      <c r="R30" s="368">
+      <c r="R30" s="373">
         <v>-0.81</v>
       </c>
       <c r="S30" s="371">
         <v>-1.01</v>
       </c>
       <c r="T30" s="374">
-        <v>-10.89</v>
+        <v>-10.69</v>
       </c>
     </row>
     <row r="31">
@@ -10560,7 +10640,7 @@
       <c r="C31" t="str">
         <v>003038</v>
       </c>
-      <c r="D31" s="380" t="str">
+      <c r="D31" s="387" t="str">
         <v>净买: 1673.87万</v>
       </c>
       <c r="E31">
@@ -10578,38 +10658,38 @@
       <c r="I31" s="388">
         <v>-1.79</v>
       </c>
-      <c r="J31" s="383">
+      <c r="J31" s="389">
         <v>-1.79</v>
       </c>
-      <c r="K31" s="378">
+      <c r="K31" s="390">
         <v>-7.21</v>
       </c>
-      <c r="L31" s="389">
+      <c r="L31" s="378">
         <v>-9</v>
       </c>
-      <c r="M31" s="390">
+      <c r="M31" s="382">
         <v>-11.53</v>
       </c>
-      <c r="N31" s="384">
+      <c r="N31" s="383">
         <v>-10.42</v>
       </c>
-      <c r="O31" s="385">
+      <c r="O31" s="379">
         <v>-9.79</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="386">
         <v>-11.32</v>
       </c>
-      <c r="Q31" s="386">
+      <c r="Q31" s="380">
         <v>-11.26</v>
       </c>
-      <c r="R31" s="379">
+      <c r="R31" s="384">
         <v>-9.89</v>
       </c>
-      <c r="S31" s="387">
+      <c r="S31" s="381">
         <v>-11.89</v>
       </c>
-      <c r="T31" s="382">
-        <v>-20.63</v>
+      <c r="T31" s="385">
+        <v>-23.95</v>
       </c>
     </row>
     <row r="32">
@@ -10622,7 +10702,7 @@
       <c r="C32" t="str">
         <v>300390</v>
       </c>
-      <c r="D32" s="402" t="str">
+      <c r="D32" s="399" t="str">
         <v>净卖: -2712.20万</v>
       </c>
       <c r="E32">
@@ -10637,41 +10717,41 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="400">
         <v>15.32</v>
       </c>
-      <c r="J32" s="398">
+      <c r="J32" s="394">
         <v>19.24</v>
       </c>
-      <c r="K32" s="403">
+      <c r="K32" s="401">
         <v>21.18</v>
       </c>
-      <c r="L32" s="391">
+      <c r="L32" s="395">
         <v>17.01</v>
       </c>
-      <c r="M32" s="399">
+      <c r="M32" s="398">
         <v>39.41</v>
       </c>
-      <c r="N32" s="392">
+      <c r="N32" s="402">
         <v>44.54</v>
       </c>
-      <c r="O32" s="396">
+      <c r="O32" s="403">
         <v>73.45</v>
       </c>
-      <c r="P32" s="400">
+      <c r="P32" s="396">
         <v>64.28</v>
       </c>
-      <c r="Q32" s="393">
+      <c r="Q32" s="391">
         <v>66.69</v>
       </c>
-      <c r="R32" s="401">
+      <c r="R32" s="392">
         <v>76.84</v>
       </c>
-      <c r="S32" s="397">
+      <c r="S32" s="393">
         <v>41.99</v>
       </c>
-      <c r="T32" s="394">
-        <v>149.01</v>
+      <c r="T32" s="397">
+        <v>164.07</v>
       </c>
     </row>
     <row r="33">
@@ -10684,7 +10764,7 @@
       <c r="C33" t="str">
         <v>603829</v>
       </c>
-      <c r="D33" s="413" t="str">
+      <c r="D33" s="410" t="str">
         <v>净卖: -2484.77万</v>
       </c>
       <c r="E33">
@@ -10699,41 +10779,41 @@
       <c r="H33">
         <v>0.16</v>
       </c>
-      <c r="I33" s="404">
+      <c r="I33" s="411">
         <v>-10.16</v>
       </c>
-      <c r="J33" s="407">
+      <c r="J33" s="405">
         <v>-9.96</v>
       </c>
-      <c r="K33" s="405">
+      <c r="K33" s="406">
         <v>-18.94</v>
       </c>
       <c r="L33" s="412">
         <v>-22.65</v>
       </c>
-      <c r="M33" s="408">
+      <c r="M33" s="416">
         <v>-22.75</v>
       </c>
-      <c r="N33" s="409">
+      <c r="N33" s="407">
         <v>-25.3</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="404">
         <v>-26.94</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="413">
         <v>-27.14</v>
       </c>
-      <c r="Q33" s="410">
+      <c r="Q33" s="408">
         <v>-26.97</v>
       </c>
-      <c r="R33" s="411">
+      <c r="R33" s="414">
         <v>-27.01</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="409">
         <v>-25.4</v>
       </c>
-      <c r="T33" s="416">
-        <v>-8.55</v>
+      <c r="T33" s="415">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="34">
@@ -10746,7 +10826,7 @@
       <c r="C34" t="str">
         <v>603829</v>
       </c>
-      <c r="D34" s="426" t="str">
+      <c r="D34" s="424" t="str">
         <v>净卖: -2802.75万</v>
       </c>
       <c r="E34">
@@ -10761,41 +10841,41 @@
       <c r="H34">
         <v>0.15</v>
       </c>
-      <c r="I34" s="423">
+      <c r="I34" s="417">
         <v>-10.11</v>
       </c>
-      <c r="J34" s="427">
+      <c r="J34" s="418">
         <v>-14.21</v>
       </c>
-      <c r="K34" s="428">
+      <c r="K34" s="422">
         <v>-14.32</v>
       </c>
       <c r="L34" s="419">
         <v>-17.16</v>
       </c>
-      <c r="M34" s="421">
+      <c r="M34" s="420">
         <v>-18.97</v>
       </c>
-      <c r="N34" s="424">
+      <c r="N34" s="428">
         <v>-19.19</v>
       </c>
-      <c r="O34" s="422">
+      <c r="O34" s="429">
         <v>-19.01</v>
       </c>
-      <c r="P34" s="420">
+      <c r="P34" s="425">
         <v>-19.05</v>
       </c>
-      <c r="Q34" s="429">
+      <c r="Q34" s="426">
         <v>-17.27</v>
       </c>
-      <c r="R34" s="417">
+      <c r="R34" s="421">
         <v>-15.92</v>
       </c>
-      <c r="S34" s="418">
+      <c r="S34" s="427">
         <v>-14.76</v>
       </c>
-      <c r="T34" s="425">
-        <v>1.42</v>
+      <c r="T34" s="423">
+        <v>8.14</v>
       </c>
     </row>
     <row r="35">
@@ -10808,7 +10888,7 @@
       <c r="C35" t="str">
         <v>920427</v>
       </c>
-      <c r="D35" s="432" t="str">
+      <c r="D35" s="439" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E35">
@@ -10823,41 +10903,41 @@
       <c r="H35">
         <v>-8.89</v>
       </c>
-      <c r="I35" s="442">
+      <c r="I35" s="440">
         <v>-21.22</v>
       </c>
-      <c r="J35" s="439">
+      <c r="J35" s="430">
         <v>-19.61</v>
       </c>
-      <c r="K35" s="435">
+      <c r="K35" s="436">
         <v>-23.32</v>
       </c>
-      <c r="L35" s="436">
+      <c r="L35" s="434">
         <v>-23.12</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="431">
         <v>-27.46</v>
       </c>
-      <c r="N35" s="433">
+      <c r="N35" s="441">
         <v>-27.71</v>
       </c>
-      <c r="O35" s="440">
+      <c r="O35" s="432">
         <v>-26.34</v>
       </c>
-      <c r="P35" s="434">
+      <c r="P35" s="437">
         <v>-23.22</v>
       </c>
-      <c r="Q35" s="437">
+      <c r="Q35" s="433">
         <v>-26.44</v>
       </c>
-      <c r="R35" s="431">
+      <c r="R35" s="438">
         <v>-27.12</v>
       </c>
-      <c r="S35" s="441">
+      <c r="S35" s="442">
         <v>-26.68</v>
       </c>
-      <c r="T35" s="438">
-        <v>-39.32</v>
+      <c r="T35" s="435">
+        <v>-41.56</v>
       </c>
     </row>
     <row r="36">
@@ -10870,7 +10950,7 @@
       <c r="C36" t="str">
         <v>920427</v>
       </c>
-      <c r="D36" s="454" t="str">
+      <c r="D36" s="447" t="str">
         <v>净卖: -130.63万</v>
       </c>
       <c r="E36">
@@ -10885,41 +10965,41 @@
       <c r="H36">
         <v>-4.33</v>
       </c>
-      <c r="I36" s="455">
+      <c r="I36" s="448">
         <v>6.67</v>
       </c>
       <c r="J36" s="443">
         <v>1.75</v>
       </c>
-      <c r="K36" s="444">
+      <c r="K36" s="455">
         <v>2.01</v>
       </c>
-      <c r="L36" s="449">
+      <c r="L36" s="453">
         <v>-3.75</v>
       </c>
-      <c r="M36" s="445">
+      <c r="M36" s="449">
         <v>-4.08</v>
       </c>
-      <c r="N36" s="450">
+      <c r="N36" s="444">
         <v>-2.27</v>
       </c>
-      <c r="O36" s="451">
+      <c r="O36" s="445">
         <v>1.88</v>
       </c>
       <c r="P36" s="446">
         <v>-2.39</v>
       </c>
-      <c r="Q36" s="447">
+      <c r="Q36" s="450">
         <v>-3.3</v>
       </c>
-      <c r="R36" s="452">
+      <c r="R36" s="451">
         <v>-2.72</v>
       </c>
-      <c r="S36" s="453">
+      <c r="S36" s="452">
         <v>-6.54</v>
       </c>
-      <c r="T36" s="448">
-        <v>-19.48</v>
+      <c r="T36" s="454">
+        <v>-22.46</v>
       </c>
     </row>
     <row r="37">
@@ -10932,7 +11012,7 @@
       <c r="C37" t="str">
         <v>603798</v>
       </c>
-      <c r="D37" s="467" t="str">
+      <c r="D37" s="457" t="str">
         <v>净卖: -286.39万</v>
       </c>
       <c r="E37">
@@ -10950,38 +11030,38 @@
       <c r="I37" s="461">
         <v>0</v>
       </c>
-      <c r="J37" s="458">
+      <c r="J37" s="462">
         <v>-5.52</v>
       </c>
-      <c r="K37" s="468">
+      <c r="K37" s="464">
         <v>-0.12</v>
       </c>
-      <c r="L37" s="462">
+      <c r="L37" s="458">
         <v>-0.72</v>
       </c>
-      <c r="M37" s="466">
+      <c r="M37" s="465">
         <v>-6.3</v>
       </c>
       <c r="N37" s="463">
         <v>-2.82</v>
       </c>
-      <c r="O37" s="456">
+      <c r="O37" s="468">
         <v>-3.3</v>
       </c>
-      <c r="P37" s="459">
+      <c r="P37" s="456">
         <v>-5.34</v>
       </c>
-      <c r="Q37" s="457">
+      <c r="Q37" s="459">
         <v>-4.92</v>
       </c>
-      <c r="R37" s="464">
+      <c r="R37" s="466">
         <v>0.72</v>
       </c>
-      <c r="S37" s="465">
+      <c r="S37" s="460">
         <v>-4.08</v>
       </c>
-      <c r="T37" s="460">
-        <v>3.66</v>
+      <c r="T37" s="467">
+        <v>4.2</v>
       </c>
     </row>
     <row r="38">
@@ -10994,7 +11074,7 @@
       <c r="C38" t="str">
         <v>603291</v>
       </c>
-      <c r="D38" s="475" t="str">
+      <c r="D38" s="476" t="str">
         <v>净买: 465.04万</v>
       </c>
       <c r="E38">
@@ -11009,41 +11089,41 @@
       <c r="H38">
         <v>1.97</v>
       </c>
-      <c r="I38" s="481">
+      <c r="I38" s="477">
         <v>-11.73</v>
       </c>
-      <c r="J38" s="472">
+      <c r="J38" s="474">
         <v>-11.73</v>
       </c>
-      <c r="K38" s="473">
+      <c r="K38" s="478">
         <v>-15.59</v>
       </c>
-      <c r="L38" s="469">
+      <c r="L38" s="479">
         <v>-15.51</v>
       </c>
-      <c r="M38" s="470">
+      <c r="M38" s="469">
         <v>-14.97</v>
       </c>
-      <c r="N38" s="478">
+      <c r="N38" s="475">
         <v>-15.66</v>
       </c>
-      <c r="O38" s="479">
+      <c r="O38" s="471">
         <v>-15.82</v>
       </c>
-      <c r="P38" s="476">
+      <c r="P38" s="470">
         <v>-16.05</v>
       </c>
-      <c r="Q38" s="471">
+      <c r="Q38" s="480">
         <v>-15.97</v>
       </c>
-      <c r="R38" s="477">
+      <c r="R38" s="481">
         <v>-15.51</v>
       </c>
-      <c r="S38" s="480">
+      <c r="S38" s="472">
         <v>-15.59</v>
       </c>
-      <c r="T38" s="474">
-        <v>-6.56</v>
+      <c r="T38" s="473">
+        <v>-9.57</v>
       </c>
     </row>
     <row r="39">
@@ -11056,7 +11136,7 @@
       <c r="C39" t="str">
         <v>603284</v>
       </c>
-      <c r="D39" s="492" t="str">
+      <c r="D39" s="491" t="str">
         <v>净买: 1322.73万</v>
       </c>
       <c r="E39">
@@ -11071,37 +11151,41 @@
       <c r="H39">
         <v>-0.79</v>
       </c>
-      <c r="I39" s="487">
+      <c r="I39" s="484">
         <v>4.15</v>
       </c>
-      <c r="J39" s="484">
+      <c r="J39" s="485">
         <v>7.16</v>
       </c>
-      <c r="K39" s="488">
+      <c r="K39" s="489">
         <v>7.16</v>
       </c>
-      <c r="L39" s="491">
+      <c r="L39" s="492">
         <v>7.39</v>
       </c>
-      <c r="M39" s="489">
+      <c r="M39" s="486">
         <v>7.45</v>
       </c>
-      <c r="N39" s="490">
+      <c r="N39" s="482">
         <v>8.48</v>
       </c>
-      <c r="O39" s="482">
+      <c r="O39" s="493">
         <v>6.71</v>
       </c>
-      <c r="P39" s="483">
+      <c r="P39" s="487">
         <v>7.41</v>
       </c>
-      <c r="Q39" s="485">
+      <c r="Q39" s="490">
         <v>7.64</v>
       </c>
-      <c r="R39" t="str"/>
-      <c r="S39" t="str"/>
-      <c r="T39" s="486">
-        <v>7.64</v>
+      <c r="R39" s="494">
+        <v>6.33</v>
+      </c>
+      <c r="S39" s="488">
+        <v>3.28</v>
+      </c>
+      <c r="T39" s="483">
+        <v>2.69</v>
       </c>
     </row>
     <row r="40">
@@ -11114,7 +11198,7 @@
       <c r="C40" t="str">
         <v>600605</v>
       </c>
-      <c r="D40" s="498" t="str">
+      <c r="D40" s="497" t="str">
         <v>净卖: -789.04万</v>
       </c>
       <c r="E40">
@@ -11129,29 +11213,35 @@
       <c r="H40">
         <v>6.5</v>
       </c>
-      <c r="I40" s="499">
+      <c r="I40" s="498">
         <v>3.29</v>
       </c>
-      <c r="J40" s="493">
+      <c r="J40" s="499">
         <v>-0.16</v>
       </c>
-      <c r="K40" s="494">
+      <c r="K40" s="502">
         <v>-1.47</v>
       </c>
-      <c r="L40" s="495">
+      <c r="L40" s="500">
         <v>-3.1</v>
       </c>
-      <c r="M40" s="496">
+      <c r="M40" s="503">
         <v>-2.08</v>
       </c>
-      <c r="N40" t="str"/>
-      <c r="O40" t="str"/>
-      <c r="P40" t="str"/>
+      <c r="N40" s="504">
+        <v>-2.04</v>
+      </c>
+      <c r="O40" s="501">
+        <v>-4.31</v>
+      </c>
+      <c r="P40" s="495">
+        <v>1.66</v>
+      </c>
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="497">
-        <v>-2.08</v>
+      <c r="T40" s="496">
+        <v>1.66</v>
       </c>
     </row>
     <row r="41">
@@ -11181,22 +11271,22 @@
         <v>39</v>
       </c>
       <c r="N41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q41">
         <v>38</v>
       </c>
       <c r="R41">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S41">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T41">
         <v>39</v>
@@ -11213,41 +11303,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="502">
+      <c r="I42" s="512">
         <v>38.46</v>
       </c>
-      <c r="J42" s="500">
+      <c r="J42" s="508">
         <v>41.03</v>
       </c>
-      <c r="K42" s="510">
+      <c r="K42" s="509">
         <v>38.46</v>
       </c>
-      <c r="L42" s="503">
+      <c r="L42" s="513">
         <v>35.9</v>
       </c>
-      <c r="M42" s="511">
+      <c r="M42" s="505">
         <v>28.21</v>
       </c>
-      <c r="N42" s="504">
-        <v>26.32</v>
-      </c>
-      <c r="O42" s="505">
-        <v>31.58</v>
-      </c>
-      <c r="P42" s="506">
-        <v>34.21</v>
+      <c r="N42" s="506">
+        <v>25.64</v>
+      </c>
+      <c r="O42" s="515">
+        <v>30.77</v>
+      </c>
+      <c r="P42" s="510">
+        <v>35.9</v>
       </c>
       <c r="Q42" s="507">
         <v>26.32</v>
       </c>
-      <c r="R42" s="501">
-        <v>29.73</v>
-      </c>
-      <c r="S42" s="508">
-        <v>18.92</v>
-      </c>
-      <c r="T42" s="509">
-        <v>53.85</v>
+      <c r="R42" s="514">
+        <v>31.58</v>
+      </c>
+      <c r="S42" s="511">
+        <v>21.05</v>
+      </c>
+      <c r="T42" s="516">
+        <v>56.41</v>
       </c>
     </row>
     <row r="43">
@@ -11261,41 +11351,41 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="520">
+      <c r="I43" s="521">
         <v>-0.38</v>
       </c>
-      <c r="J43" s="515">
+      <c r="J43" s="522">
         <v>-0.74</v>
       </c>
-      <c r="K43" s="518">
+      <c r="K43" s="524">
         <v>-2.11</v>
       </c>
-      <c r="L43" s="521">
+      <c r="L43" s="525">
         <v>-4.11</v>
       </c>
-      <c r="M43" s="516">
+      <c r="M43" s="518">
         <v>-5.17</v>
       </c>
-      <c r="N43" s="522">
-        <v>-6.6</v>
-      </c>
-      <c r="O43" s="519">
-        <v>-5.4</v>
-      </c>
-      <c r="P43" s="512">
-        <v>-5.71</v>
-      </c>
-      <c r="Q43" s="523">
+      <c r="N43" s="526">
+        <v>-6.48</v>
+      </c>
+      <c r="O43" s="527">
+        <v>-5.38</v>
+      </c>
+      <c r="P43" s="520">
+        <v>-5.52</v>
+      </c>
+      <c r="Q43" s="528">
         <v>-6.11</v>
       </c>
-      <c r="R43" s="513">
-        <v>-5.55</v>
-      </c>
-      <c r="S43" s="514">
-        <v>-7.91</v>
-      </c>
-      <c r="T43" s="517">
-        <v>15.17</v>
+      <c r="R43" s="523">
+        <v>-5.24</v>
+      </c>
+      <c r="S43" s="517">
+        <v>-7.62</v>
+      </c>
+      <c r="T43" s="519">
+        <v>16.09</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/申港广东分/index.xlsx
+++ b/youzi/申港广东分/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="530">
+  <fills count="531">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -57,6 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -75,25 +81,415 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,12 +501,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -123,31 +513,241 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,31 +759,1843 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,7 +2607,559 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,2977 +3171,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87D87"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD6EEDB"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3206,7 +3212,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="529">
+  <borders count="530">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6914,7 +6927,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="529">
+  <cellXfs count="530">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8498,6 +8511,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="528" fillId="529" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="529" fillId="530" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8860,38 +8876,38 @@
       <c r="I2" s="9">
         <v>0</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="10">
         <v>9.98</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="4">
         <v>3.91</v>
       </c>
       <c r="L2" s="2">
         <v>1.47</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="3">
         <v>11.62</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="11">
         <v>22.79</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="12">
         <v>15.02</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="5">
         <v>26.53</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="13">
         <v>32.65</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="6">
         <v>28.74</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="7">
         <v>21.77</v>
       </c>
-      <c r="T2" s="12">
-        <v>1.3</v>
+      <c r="T2" s="1">
+        <v>11.45</v>
       </c>
     </row>
     <row r="3">
@@ -8904,7 +8920,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 486.49万</v>
       </c>
       <c r="E3">
@@ -8919,41 +8935,41 @@
       <c r="H3">
         <v>6.6</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="14">
         <v>-11.36</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="15">
         <v>-13.44</v>
       </c>
       <c r="K3" s="22">
         <v>-4.79</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="23">
         <v>4.74</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="16">
         <v>-1.89</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="24">
         <v>7.93</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="17">
         <v>13.15</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="18">
         <v>9.82</v>
       </c>
       <c r="Q3" s="25">
         <v>3.87</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="19">
         <v>6.53</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="20">
         <v>-4.11</v>
       </c>
-      <c r="T3" s="14">
-        <v>-13.59</v>
+      <c r="T3" s="21">
+        <v>-4.93</v>
       </c>
     </row>
     <row r="4">
@@ -8966,7 +8982,7 @@
       <c r="C4" t="str">
         <v>603881</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="30" t="str">
         <v>净买: 7242.53万</v>
       </c>
       <c r="E4">
@@ -8981,41 +8997,41 @@
       <c r="H4">
         <v>8.87</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="31">
         <v>1.04</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="32">
         <v>11.14</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="37">
         <v>0.03</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="38">
         <v>7.5</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="39">
         <v>8.74</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="28">
         <v>19.61</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="35">
         <v>25.9</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="27">
         <v>21.45</v>
       </c>
       <c r="Q4" s="33">
         <v>15.56</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="34">
         <v>9.81</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="29">
         <v>-0.74</v>
       </c>
-      <c r="T4" s="39">
-        <v>12.36</v>
+      <c r="T4" s="36">
+        <v>10.52</v>
       </c>
     </row>
     <row r="5">
@@ -9043,41 +9059,41 @@
       <c r="H5">
         <v>-4.56</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="52">
         <v>-5.7</v>
       </c>
       <c r="J5" s="45">
         <v>1.34</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="40">
         <v>2.51</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="46">
         <v>12.77</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="50">
         <v>18.69</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="47">
         <v>14.5</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="41">
         <v>8.94</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="48">
         <v>3.52</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="51">
         <v>-6.42</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="42">
         <v>-4.83</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="49">
         <v>-3.18</v>
       </c>
       <c r="T5" s="43">
-        <v>5.92</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="6">
@@ -9105,41 +9121,41 @@
       <c r="H6">
         <v>5.63</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="62">
         <v>4.13</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="53">
         <v>14.56</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="59">
         <v>7.97</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="63">
         <v>-2.83</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="60">
         <v>-12.53</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="56">
         <v>-15.63</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="54">
         <v>-12.8</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="57">
         <v>-16.13</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="58">
         <v>-19.84</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="61">
         <v>-20.37</v>
       </c>
       <c r="S6" s="55">
         <v>-19.6</v>
       </c>
-      <c r="T6" s="56">
-        <v>-61.17</v>
+      <c r="T6" s="64">
+        <v>-62.43</v>
       </c>
     </row>
     <row r="7">
@@ -9152,7 +9168,7 @@
       <c r="C7" t="str">
         <v>600590</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="74" t="str">
         <v>净买: 1013.84万</v>
       </c>
       <c r="E7">
@@ -9167,41 +9183,41 @@
       <c r="H7">
         <v>10.05</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="71">
         <v>0</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="75">
         <v>-2.39</v>
       </c>
       <c r="K7" s="67">
         <v>7.39</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="76">
         <v>1.85</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="72">
         <v>1.63</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="68">
         <v>-5.76</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="73">
         <v>-3.48</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="69">
         <v>6.2</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="70">
         <v>16.85</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="78">
         <v>26.41</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="77">
         <v>21.74</v>
       </c>
-      <c r="T7" s="70">
-        <v>85.43</v>
+      <c r="T7" s="66">
+        <v>78.04</v>
       </c>
     </row>
     <row r="8">
@@ -9214,7 +9230,7 @@
       <c r="C8" t="str">
         <v>000818</v>
       </c>
-      <c r="D8" s="88" t="str">
+      <c r="D8" s="89" t="str">
         <v>净卖: -5301.29万</v>
       </c>
       <c r="E8">
@@ -9229,41 +9245,41 @@
       <c r="H8">
         <v>-10</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="88">
         <v>0</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="90">
         <v>-9.99</v>
       </c>
       <c r="K8" s="80">
         <v>-13.17</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="81">
         <v>-10.26</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="86">
         <v>-13.69</v>
       </c>
-      <c r="N8" s="87">
+      <c r="N8" s="82">
         <v>-17.51</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="83">
         <v>-18.06</v>
       </c>
-      <c r="P8" s="90">
+      <c r="P8" s="91">
         <v>-17.26</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="84">
         <v>-14.79</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="85">
         <v>-16.85</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="87">
         <v>-14.02</v>
       </c>
-      <c r="T8" s="86">
-        <v>-60.04</v>
+      <c r="T8" s="79">
+        <v>-61.33</v>
       </c>
     </row>
     <row r="9">
@@ -9276,7 +9292,7 @@
       <c r="C9" t="str">
         <v>002290</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -2168.44万</v>
       </c>
       <c r="E9">
@@ -9291,41 +9307,41 @@
       <c r="H9">
         <v>-9.5</v>
       </c>
-      <c r="I9" s="98">
+      <c r="I9" s="92">
         <v>-0.54</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="102">
         <v>0</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="95">
         <v>0.33</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="93">
         <v>3.33</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="99">
         <v>-7</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="94">
         <v>-1.67</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="96">
         <v>6.04</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="103">
         <v>7.58</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="97">
         <v>12.71</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="100">
         <v>16.92</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="98">
         <v>12.79</v>
       </c>
-      <c r="T9" s="102">
-        <v>238.96</v>
+      <c r="T9" s="104">
+        <v>266.96</v>
       </c>
     </row>
     <row r="10">
@@ -9338,7 +9354,7 @@
       <c r="C10" t="str">
         <v>605300</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="116" t="str">
         <v>净买: 1145.88万</v>
       </c>
       <c r="E10">
@@ -9353,41 +9369,41 @@
       <c r="H10">
         <v>1.49</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="110">
         <v>8.41</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="117">
         <v>-2.41</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="105">
         <v>-12.18</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="107">
         <v>-15</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="108">
         <v>-12.88</v>
       </c>
-      <c r="N10" s="105">
+      <c r="N10" s="113">
         <v>-14.71</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="111">
         <v>-15.65</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="112">
         <v>-16.18</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="109">
         <v>-16.82</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="106">
         <v>-18.35</v>
       </c>
       <c r="S10" s="114">
         <v>-15.18</v>
       </c>
       <c r="T10" s="115">
-        <v>-35.76</v>
+        <v>-34.47</v>
       </c>
     </row>
     <row r="11">
@@ -9400,7 +9416,7 @@
       <c r="C11" t="str">
         <v>605100</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="125" t="str">
         <v>净买: 1795.46万</v>
       </c>
       <c r="E11">
@@ -9415,41 +9431,41 @@
       <c r="H11">
         <v>9.99</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="130">
         <v>0</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="126">
         <v>-9.16</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="127">
         <v>-0.08</v>
       </c>
-      <c r="L11" s="120">
+      <c r="L11" s="118">
         <v>0</v>
       </c>
-      <c r="M11" s="124">
+      <c r="M11" s="128">
         <v>9.99</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="119">
         <v>-0.99</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="129">
         <v>8.93</v>
       </c>
-      <c r="P11" s="122">
+      <c r="P11" s="121">
         <v>19.83</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="122">
         <v>12.16</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="123">
         <v>23.38</v>
       </c>
-      <c r="S11" s="125">
+      <c r="S11" s="124">
         <v>13.07</v>
       </c>
-      <c r="T11" s="130">
-        <v>92.54</v>
+      <c r="T11" s="120">
+        <v>91.15</v>
       </c>
     </row>
     <row r="12">
@@ -9462,7 +9478,7 @@
       <c r="C12" t="str">
         <v>605300</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="137" t="str">
         <v>净卖: -1034.72万</v>
       </c>
       <c r="E12">
@@ -9477,41 +9493,41 @@
       <c r="H12">
         <v>-5.36</v>
       </c>
-      <c r="I12" s="136">
+      <c r="I12" s="143">
         <v>2.26</v>
       </c>
-      <c r="J12" s="137">
+      <c r="J12" s="138">
         <v>4.81</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="133">
         <v>2.62</v>
       </c>
       <c r="L12" s="141">
         <v>1.49</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="131">
         <v>0.85</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="139">
         <v>0.07</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="134">
         <v>-1.77</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="142">
         <v>2.05</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="135">
         <v>0.85</v>
       </c>
       <c r="R12" s="132">
         <v>0.21</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="140">
         <v>-0.92</v>
       </c>
-      <c r="T12" s="139">
-        <v>-22.72</v>
+      <c r="T12" s="136">
+        <v>-21.16</v>
       </c>
     </row>
     <row r="13">
@@ -9524,7 +9540,7 @@
       <c r="C13" t="str">
         <v>002114</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="146" t="str">
         <v>净买: 1554.85万</v>
       </c>
       <c r="E13">
@@ -9539,41 +9555,41 @@
       <c r="H13">
         <v>9.83</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="154">
         <v>0.13</v>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="152">
         <v>-1.41</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="147">
         <v>-4.6</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="155">
         <v>-6.65</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="153">
         <v>-6.01</v>
       </c>
-      <c r="N13" s="152">
+      <c r="N13" s="148">
         <v>-6.52</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="149">
         <v>-5.5</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="150">
         <v>-10.1</v>
       </c>
-      <c r="Q13" s="154">
+      <c r="Q13" s="156">
         <v>-9.59</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="151">
         <v>-10.87</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="144">
         <v>-11.76</v>
       </c>
-      <c r="T13" s="155">
-        <v>15.6</v>
+      <c r="T13" s="145">
+        <v>16.11</v>
       </c>
     </row>
     <row r="14">
@@ -9604,38 +9620,38 @@
       <c r="I14" s="157">
         <v>0</v>
       </c>
-      <c r="J14" s="158">
+      <c r="J14" s="164">
         <v>-7.6</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="166">
         <v>-13.68</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="160">
         <v>-20.06</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="167">
         <v>-20.21</v>
       </c>
-      <c r="N14" s="159">
+      <c r="N14" s="165">
         <v>-21.58</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="158">
         <v>-22.87</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="161">
         <v>-23.86</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="162">
         <v>-24.62</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="159">
         <v>-27.13</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="168">
         <v>-26.6</v>
       </c>
-      <c r="T14" s="161">
-        <v>74.24</v>
+      <c r="T14" s="163">
+        <v>73.25</v>
       </c>
     </row>
     <row r="15">
@@ -9648,7 +9664,7 @@
       <c r="C15" t="str">
         <v>605303</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="170" t="str">
         <v>净卖: -1462.35万</v>
       </c>
       <c r="E15">
@@ -9663,41 +9679,41 @@
       <c r="H15">
         <v>-2.55</v>
       </c>
-      <c r="I15" s="174">
+      <c r="I15" s="175">
         <v>-4.97</v>
       </c>
-      <c r="J15" s="175">
+      <c r="J15" s="171">
         <v>-5.15</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="176">
         <v>-6.78</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="177">
         <v>-8.31</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="172">
         <v>-9.49</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="178">
         <v>-10.39</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="179">
         <v>-13.37</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="180">
         <v>-12.74</v>
       </c>
-      <c r="Q15" s="177">
+      <c r="Q15" s="181">
         <v>-14.27</v>
       </c>
-      <c r="R15" s="171">
+      <c r="R15" s="173">
         <v>-15.54</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="174">
         <v>-16.71</v>
       </c>
-      <c r="T15" s="172">
-        <v>107.14</v>
+      <c r="T15" s="182">
+        <v>105.96</v>
       </c>
     </row>
     <row r="16">
@@ -9710,7 +9726,7 @@
       <c r="C16" t="str">
         <v>600301</v>
       </c>
-      <c r="D16" s="188" t="str">
+      <c r="D16" s="191" t="str">
         <v>净卖: -3080.81万</v>
       </c>
       <c r="E16">
@@ -9725,41 +9741,41 @@
       <c r="H16">
         <v>-2.8</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="183">
         <v>-4.62</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="192">
         <v>-5.96</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="193">
         <v>-4.88</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="184">
         <v>-5.27</v>
       </c>
-      <c r="M16" s="190">
+      <c r="M16" s="185">
         <v>-3.31</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="194">
         <v>-7.19</v>
       </c>
-      <c r="O16" s="191">
+      <c r="O16" s="188">
         <v>-7.88</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="186">
         <v>-7.88</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="189">
         <v>-10.35</v>
       </c>
-      <c r="R16" s="195">
+      <c r="R16" s="190">
         <v>-11.15</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="187">
         <v>-14.38</v>
       </c>
-      <c r="T16" s="184">
-        <v>107.85</v>
+      <c r="T16" s="195">
+        <v>99.73</v>
       </c>
     </row>
     <row r="17">
@@ -9772,7 +9788,7 @@
       <c r="C17" t="str">
         <v>000815</v>
       </c>
-      <c r="D17" s="201" t="str">
+      <c r="D17" s="203" t="str">
         <v>净买: 5327.66万</v>
       </c>
       <c r="E17">
@@ -9787,41 +9803,41 @@
       <c r="H17">
         <v>2.39</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="204">
         <v>2.95</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="207">
         <v>-3.14</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="200">
         <v>-4.8</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="205">
         <v>-6.52</v>
       </c>
-      <c r="M17" s="198">
+      <c r="M17" s="208">
         <v>-12.98</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="196">
         <v>-17.22</v>
       </c>
-      <c r="O17" s="206">
+      <c r="O17" s="201">
         <v>-16.91</v>
       </c>
-      <c r="P17" s="200">
+      <c r="P17" s="197">
         <v>-20.79</v>
       </c>
-      <c r="Q17" s="204">
+      <c r="Q17" s="198">
         <v>-20.3</v>
       </c>
-      <c r="R17" s="196">
+      <c r="R17" s="199">
         <v>-19.74</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="206">
         <v>-20.85</v>
       </c>
-      <c r="T17" s="207">
-        <v>17.9</v>
+      <c r="T17" s="202">
+        <v>20.79</v>
       </c>
     </row>
     <row r="18">
@@ -9834,7 +9850,7 @@
       <c r="C18" t="str">
         <v>603315</v>
       </c>
-      <c r="D18" s="217" t="str">
+      <c r="D18" s="220" t="str">
         <v>净买: 2006.31万</v>
       </c>
       <c r="E18">
@@ -9849,41 +9865,41 @@
       <c r="H18">
         <v>10.03</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="216">
         <v>0</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="213">
         <v>9.99</v>
       </c>
-      <c r="K18" s="219">
+      <c r="K18" s="221">
         <v>20.99</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="209">
         <v>8.87</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="210">
         <v>-2</v>
       </c>
-      <c r="N18" s="220">
+      <c r="N18" s="219">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="215">
+      <c r="O18" s="217">
         <v>-12.8</v>
       </c>
-      <c r="P18" s="216">
+      <c r="P18" s="214">
         <v>-17.49</v>
       </c>
-      <c r="Q18" s="214">
+      <c r="Q18" s="211">
         <v>-18.11</v>
       </c>
-      <c r="R18" s="221">
+      <c r="R18" s="215">
         <v>-16.36</v>
       </c>
-      <c r="S18" s="213">
+      <c r="S18" s="212">
         <v>-16.55</v>
       </c>
-      <c r="T18" s="209">
-        <v>14.3</v>
+      <c r="T18" s="218">
+        <v>15.3</v>
       </c>
     </row>
     <row r="19">
@@ -9896,7 +9912,7 @@
       <c r="C19" t="str">
         <v>603315</v>
       </c>
-      <c r="D19" s="225" t="str">
+      <c r="D19" s="222" t="str">
         <v>净卖: -2227.67万</v>
       </c>
       <c r="E19">
@@ -9914,38 +9930,38 @@
       <c r="I19" s="226">
         <v>14.82</v>
       </c>
-      <c r="J19" s="227">
+      <c r="J19" s="232">
         <v>3.32</v>
       </c>
-      <c r="K19" s="228">
+      <c r="K19" s="223">
         <v>-6.99</v>
       </c>
-      <c r="L19" s="222">
+      <c r="L19" s="224">
         <v>-16.3</v>
       </c>
-      <c r="M19" s="231">
+      <c r="M19" s="227">
         <v>-17.25</v>
       </c>
-      <c r="N19" s="229">
+      <c r="N19" s="225">
         <v>-21.7</v>
       </c>
-      <c r="O19" s="223">
+      <c r="O19" s="233">
         <v>-22.29</v>
       </c>
-      <c r="P19" s="230">
+      <c r="P19" s="228">
         <v>-20.63</v>
       </c>
-      <c r="Q19" s="224">
+      <c r="Q19" s="229">
         <v>-20.81</v>
       </c>
-      <c r="R19" s="232">
+      <c r="R19" s="234">
         <v>-20.09</v>
       </c>
-      <c r="S19" s="233">
+      <c r="S19" s="230">
         <v>-22.05</v>
       </c>
-      <c r="T19" s="234">
-        <v>8.48</v>
+      <c r="T19" s="231">
+        <v>9.43</v>
       </c>
     </row>
     <row r="20">
@@ -9958,7 +9974,7 @@
       <c r="C20" t="str">
         <v>000737</v>
       </c>
-      <c r="D20" s="238" t="str">
+      <c r="D20" s="237" t="str">
         <v>净买: 2607.05万</v>
       </c>
       <c r="E20">
@@ -9973,41 +9989,41 @@
       <c r="H20">
         <v>0.79</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="240">
         <v>9.19</v>
       </c>
-      <c r="J20" s="246">
+      <c r="J20" s="245">
         <v>15.54</v>
       </c>
-      <c r="K20" s="239">
+      <c r="K20" s="241">
         <v>20.43</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="242">
         <v>11.93</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="246">
         <v>4.79</v>
       </c>
-      <c r="N20" s="240">
+      <c r="N20" s="243">
         <v>2.64</v>
       </c>
-      <c r="O20" s="242">
+      <c r="O20" s="244">
         <v>2.83</v>
       </c>
-      <c r="P20" s="243">
+      <c r="P20" s="238">
         <v>1.08</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="239">
         <v>-2.15</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="247">
         <v>-11.93</v>
       </c>
-      <c r="S20" s="241">
+      <c r="S20" s="235">
         <v>-19.65</v>
       </c>
-      <c r="T20" s="237">
-        <v>34.8</v>
+      <c r="T20" s="236">
+        <v>33.92</v>
       </c>
     </row>
     <row r="21">
@@ -10020,7 +10036,7 @@
       <c r="C21" t="str">
         <v>000779</v>
       </c>
-      <c r="D21" s="259" t="str">
+      <c r="D21" s="260" t="str">
         <v>净买: 1464.90万</v>
       </c>
       <c r="E21">
@@ -10035,41 +10051,41 @@
       <c r="H21">
         <v>9.36</v>
       </c>
-      <c r="I21" s="249">
+      <c r="I21" s="248">
         <v>-14.36</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="253">
         <v>-22.92</v>
       </c>
-      <c r="K21" s="250">
+      <c r="K21" s="254">
         <v>-25.67</v>
       </c>
-      <c r="L21" s="252">
+      <c r="L21" s="249">
         <v>-28.8</v>
       </c>
-      <c r="M21" s="248">
+      <c r="M21" s="255">
         <v>-29.11</v>
       </c>
-      <c r="N21" s="253">
+      <c r="N21" s="256">
         <v>-26.05</v>
       </c>
-      <c r="O21" s="251">
+      <c r="O21" s="259">
         <v>-28.27</v>
       </c>
-      <c r="P21" s="254">
+      <c r="P21" s="257">
         <v>-29.03</v>
       </c>
-      <c r="Q21" s="257">
+      <c r="Q21" s="250">
         <v>-29.95</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="258">
         <v>-36.97</v>
       </c>
-      <c r="S21" s="256">
+      <c r="S21" s="251">
         <v>-35.91</v>
       </c>
-      <c r="T21" s="258">
-        <v>-36.13</v>
+      <c r="T21" s="252">
+        <v>-33.61</v>
       </c>
     </row>
     <row r="22">
@@ -10082,7 +10098,7 @@
       <c r="C22" t="str">
         <v>600727</v>
       </c>
-      <c r="D22" s="272" t="str">
+      <c r="D22" s="261" t="str">
         <v>净卖: -2220.75万</v>
       </c>
       <c r="E22">
@@ -10097,41 +10113,41 @@
       <c r="H22">
         <v>4.31</v>
       </c>
-      <c r="I22" s="270">
+      <c r="I22" s="268">
         <v>-1.31</v>
       </c>
-      <c r="J22" s="264">
+      <c r="J22" s="262">
         <v>0.76</v>
       </c>
-      <c r="K22" s="265">
+      <c r="K22" s="266">
         <v>-9.36</v>
       </c>
-      <c r="L22" s="266">
+      <c r="L22" s="269">
         <v>-13.71</v>
       </c>
-      <c r="M22" s="267">
+      <c r="M22" s="263">
         <v>-11.32</v>
       </c>
-      <c r="N22" s="262">
+      <c r="N22" s="264">
         <v>-12.08</v>
       </c>
-      <c r="O22" s="273">
+      <c r="O22" s="270">
         <v>-7.51</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="265">
         <v>-16.76</v>
       </c>
-      <c r="Q22" s="268">
+      <c r="Q22" s="272">
         <v>-15.13</v>
       </c>
-      <c r="R22" s="269">
+      <c r="R22" s="273">
         <v>-16.76</v>
       </c>
       <c r="S22" s="271">
         <v>-15.67</v>
       </c>
-      <c r="T22" s="263">
-        <v>-12.73</v>
+      <c r="T22" s="267">
+        <v>-13.28</v>
       </c>
     </row>
     <row r="23">
@@ -10144,7 +10160,7 @@
       <c r="C23" t="str">
         <v>001217</v>
       </c>
-      <c r="D23" s="276" t="str">
+      <c r="D23" s="277" t="str">
         <v>净买: 3127.44万</v>
       </c>
       <c r="E23">
@@ -10159,41 +10175,41 @@
       <c r="H23">
         <v>9.99</v>
       </c>
-      <c r="I23" s="282">
+      <c r="I23" s="274">
         <v>0</v>
       </c>
-      <c r="J23" s="285">
+      <c r="J23" s="275">
         <v>-8.55</v>
       </c>
-      <c r="K23" s="277">
+      <c r="K23" s="278">
         <v>-13.73</v>
       </c>
-      <c r="L23" s="283">
+      <c r="L23" s="280">
         <v>-17.5</v>
       </c>
-      <c r="M23" s="278">
+      <c r="M23" s="276">
         <v>-20.66</v>
       </c>
       <c r="N23" s="279">
         <v>-28.6</v>
       </c>
-      <c r="O23" s="280">
+      <c r="O23" s="281">
         <v>-31.02</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="282">
         <v>-31.09</v>
       </c>
-      <c r="Q23" s="284">
+      <c r="Q23" s="283">
         <v>-29.48</v>
       </c>
-      <c r="R23" s="275">
+      <c r="R23" s="284">
         <v>-28.33</v>
       </c>
-      <c r="S23" s="286">
+      <c r="S23" s="285">
         <v>-26.72</v>
       </c>
-      <c r="T23" s="281">
-        <v>-19.31</v>
+      <c r="T23" s="286">
+        <v>-18.57</v>
       </c>
     </row>
     <row r="24">
@@ -10221,41 +10237,41 @@
       <c r="H24">
         <v>-3.3</v>
       </c>
-      <c r="I24" s="293">
+      <c r="I24" s="288">
         <v>-6.9</v>
       </c>
-      <c r="J24" s="288">
+      <c r="J24" s="293">
         <v>-8.84</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="289">
         <v>-7.5</v>
       </c>
-      <c r="L24" s="289">
+      <c r="L24" s="298">
         <v>-7.64</v>
       </c>
-      <c r="M24" s="290">
+      <c r="M24" s="299">
         <v>-12.93</v>
       </c>
-      <c r="N24" s="291">
+      <c r="N24" s="290">
         <v>-21.63</v>
       </c>
-      <c r="O24" s="295">
+      <c r="O24" s="294">
         <v>-20.23</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="291">
         <v>-21.57</v>
       </c>
-      <c r="Q24" s="296">
+      <c r="Q24" s="295">
         <v>-20.09</v>
       </c>
-      <c r="R24" s="292">
+      <c r="R24" s="296">
         <v>-20.03</v>
       </c>
-      <c r="S24" s="298">
+      <c r="S24" s="297">
         <v>-17.62</v>
       </c>
-      <c r="T24" s="299">
-        <v>10.58</v>
+      <c r="T24" s="292">
+        <v>7.77</v>
       </c>
     </row>
     <row r="25">
@@ -10268,7 +10284,7 @@
       <c r="C25" t="str">
         <v>001333</v>
       </c>
-      <c r="D25" s="304" t="str">
+      <c r="D25" s="308" t="str">
         <v>净买: 1650.82万</v>
       </c>
       <c r="E25">
@@ -10283,41 +10299,41 @@
       <c r="H25">
         <v>-1.88</v>
       </c>
-      <c r="I25" s="302">
+      <c r="I25" s="300">
         <v>12.11</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="301">
         <v>23.33</v>
       </c>
-      <c r="K25" s="303">
+      <c r="K25" s="302">
         <v>11.01</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="303">
         <v>-0.08</v>
       </c>
-      <c r="M25" s="312">
+      <c r="M25" s="310">
         <v>-10.07</v>
       </c>
-      <c r="N25" s="307">
+      <c r="N25" s="304">
         <v>-18.1</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="305">
         <v>-17.47</v>
       </c>
-      <c r="P25" s="300">
+      <c r="P25" s="306">
         <v>-15.81</v>
       </c>
       <c r="Q25" s="309">
         <v>-10.96</v>
       </c>
-      <c r="R25" s="301">
+      <c r="R25" s="307">
         <v>-8.75</v>
       </c>
-      <c r="S25" s="310">
+      <c r="S25" s="311">
         <v>-10.28</v>
       </c>
-      <c r="T25" s="311">
-        <v>3.19</v>
+      <c r="T25" s="312">
+        <v>2.46</v>
       </c>
     </row>
     <row r="26">
@@ -10330,7 +10346,7 @@
       <c r="C26" t="str">
         <v>002365</v>
       </c>
-      <c r="D26" s="314" t="str">
+      <c r="D26" s="316" t="str">
         <v>净卖: -918.91万</v>
       </c>
       <c r="E26">
@@ -10345,41 +10361,41 @@
       <c r="H26">
         <v>-8.32</v>
       </c>
-      <c r="I26" s="318">
+      <c r="I26" s="324">
         <v>20.02</v>
       </c>
-      <c r="J26" s="323">
+      <c r="J26" s="325">
         <v>15.9</v>
       </c>
-      <c r="K26" s="315">
+      <c r="K26" s="317">
         <v>22.97</v>
       </c>
-      <c r="L26" s="316">
+      <c r="L26" s="321">
         <v>19.43</v>
       </c>
-      <c r="M26" s="320">
+      <c r="M26" s="322">
         <v>16.02</v>
       </c>
-      <c r="N26" s="321">
+      <c r="N26" s="313">
         <v>10.37</v>
       </c>
-      <c r="O26" s="319">
+      <c r="O26" s="315">
         <v>9.42</v>
       </c>
-      <c r="P26" s="317">
+      <c r="P26" s="318">
         <v>11.66</v>
       </c>
-      <c r="Q26" s="322">
+      <c r="Q26" s="319">
         <v>6.24</v>
       </c>
-      <c r="R26" s="324">
+      <c r="R26" s="323">
         <v>16.84</v>
       </c>
-      <c r="S26" s="325">
+      <c r="S26" s="314">
         <v>20.49</v>
       </c>
-      <c r="T26" s="313">
-        <v>52.18</v>
+      <c r="T26" s="320">
+        <v>54.89</v>
       </c>
     </row>
     <row r="27">
@@ -10392,7 +10408,7 @@
       <c r="C27" t="str">
         <v>600180</v>
       </c>
-      <c r="D27" s="330" t="str">
+      <c r="D27" s="335" t="str">
         <v>净卖: -1973.71万</v>
       </c>
       <c r="E27">
@@ -10407,41 +10423,41 @@
       <c r="H27">
         <v>-4.9</v>
       </c>
-      <c r="I27" s="327">
+      <c r="I27" s="336">
         <v>0.21</v>
       </c>
-      <c r="J27" s="328">
+      <c r="J27" s="332">
         <v>-1.93</v>
       </c>
-      <c r="K27" s="331">
+      <c r="K27" s="337">
         <v>-3.86</v>
       </c>
-      <c r="L27" s="332">
+      <c r="L27" s="338">
         <v>-2.58</v>
       </c>
-      <c r="M27" s="336">
+      <c r="M27" s="327">
         <v>-1.5</v>
       </c>
       <c r="N27" s="333">
         <v>-3.43</v>
       </c>
-      <c r="O27" s="334">
+      <c r="O27" s="326">
         <v>-5.79</v>
       </c>
-      <c r="P27" s="337">
+      <c r="P27" s="329">
         <v>-4.94</v>
       </c>
-      <c r="Q27" s="329">
+      <c r="Q27" s="334">
         <v>-8.58</v>
       </c>
-      <c r="R27" s="338">
+      <c r="R27" s="330">
         <v>-7.73</v>
       </c>
-      <c r="S27" s="335">
+      <c r="S27" s="328">
         <v>-8.37</v>
       </c>
-      <c r="T27" s="326">
-        <v>-36.48</v>
+      <c r="T27" s="331">
+        <v>-37.34</v>
       </c>
     </row>
     <row r="28">
@@ -10454,7 +10470,7 @@
       <c r="C28" t="str">
         <v>002743</v>
       </c>
-      <c r="D28" s="339" t="str">
+      <c r="D28" s="348" t="str">
         <v>净卖: -345.80万</v>
       </c>
       <c r="E28">
@@ -10469,41 +10485,41 @@
       <c r="H28">
         <v>-9.98</v>
       </c>
-      <c r="I28" s="347">
+      <c r="I28" s="349">
         <v>0</v>
       </c>
-      <c r="J28" s="340">
+      <c r="J28" s="343">
         <v>-5.83</v>
       </c>
-      <c r="K28" s="344">
+      <c r="K28" s="350">
         <v>-3.38</v>
       </c>
-      <c r="L28" s="348">
+      <c r="L28" s="344">
         <v>0.75</v>
       </c>
-      <c r="M28" s="342">
+      <c r="M28" s="351">
         <v>1.88</v>
       </c>
       <c r="N28" s="345">
         <v>3.01</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="346">
         <v>3.95</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="347">
         <v>0.75</v>
       </c>
-      <c r="Q28" s="341">
+      <c r="Q28" s="339">
         <v>-0.19</v>
       </c>
-      <c r="R28" s="343">
+      <c r="R28" s="340">
         <v>1.5</v>
       </c>
-      <c r="S28" s="346">
+      <c r="S28" s="341">
         <v>5.83</v>
       </c>
-      <c r="T28" s="351">
-        <v>-2.44</v>
+      <c r="T28" s="342">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="29">
@@ -10516,7 +10532,7 @@
       <c r="C29" t="str">
         <v>600173</v>
       </c>
-      <c r="D29" s="362" t="str">
+      <c r="D29" s="353" t="str">
         <v>净卖: -1818.07万</v>
       </c>
       <c r="E29">
@@ -10531,41 +10547,41 @@
       <c r="H29">
         <v>-1.2</v>
       </c>
-      <c r="I29" s="354">
+      <c r="I29" s="364">
         <v>-8.91</v>
       </c>
-      <c r="J29" s="355">
+      <c r="J29" s="358">
         <v>0.2</v>
       </c>
-      <c r="K29" s="363">
+      <c r="K29" s="354">
         <v>4.45</v>
       </c>
-      <c r="L29" s="361">
+      <c r="L29" s="355">
         <v>-2.94</v>
       </c>
-      <c r="M29" s="358">
+      <c r="M29" s="359">
         <v>-7.89</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="361">
         <v>-12.45</v>
       </c>
-      <c r="O29" s="356">
+      <c r="O29" s="360">
         <v>-11.84</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="356">
         <v>-8.1</v>
       </c>
-      <c r="Q29" s="359">
+      <c r="Q29" s="352">
         <v>-5.36</v>
       </c>
       <c r="R29" s="357">
         <v>-2.53</v>
       </c>
-      <c r="S29" s="360">
+      <c r="S29" s="362">
         <v>-3.54</v>
       </c>
-      <c r="T29" s="353">
-        <v>-24.8</v>
+      <c r="T29" s="363">
+        <v>-24.19</v>
       </c>
     </row>
     <row r="30">
@@ -10578,7 +10594,7 @@
       <c r="C30" t="str">
         <v>000637</v>
       </c>
-      <c r="D30" s="372" t="str">
+      <c r="D30" s="367" t="str">
         <v>净卖: -692.69万</v>
       </c>
       <c r="E30">
@@ -10593,41 +10609,41 @@
       <c r="H30">
         <v>-4.62</v>
       </c>
-      <c r="I30" s="375">
+      <c r="I30" s="368">
         <v>-5.65</v>
       </c>
-      <c r="J30" s="367">
+      <c r="J30" s="369">
         <v>3.83</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="366">
         <v>-0.81</v>
       </c>
-      <c r="L30" s="377">
+      <c r="L30" s="371">
         <v>0.6</v>
       </c>
-      <c r="M30" s="368">
+      <c r="M30" s="372">
         <v>-2.02</v>
       </c>
-      <c r="N30" s="369">
+      <c r="N30" s="373">
         <v>-6.25</v>
       </c>
-      <c r="O30" s="365">
+      <c r="O30" s="375">
         <v>-4.84</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="374">
         <v>-4.23</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="376">
         <v>-3.43</v>
       </c>
-      <c r="R30" s="373">
+      <c r="R30" s="370">
         <v>-0.81</v>
       </c>
-      <c r="S30" s="371">
+      <c r="S30" s="377">
         <v>-1.01</v>
       </c>
-      <c r="T30" s="374">
-        <v>-10.69</v>
+      <c r="T30" s="365">
+        <v>-9.27</v>
       </c>
     </row>
     <row r="31">
@@ -10640,7 +10656,7 @@
       <c r="C31" t="str">
         <v>003038</v>
       </c>
-      <c r="D31" s="387" t="str">
+      <c r="D31" s="382" t="str">
         <v>净买: 1673.87万</v>
       </c>
       <c r="E31">
@@ -10655,41 +10671,41 @@
       <c r="H31">
         <v>-3.7</v>
       </c>
-      <c r="I31" s="388">
+      <c r="I31" s="383">
         <v>-1.79</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="379">
         <v>-1.79</v>
       </c>
-      <c r="K31" s="390">
+      <c r="K31" s="386">
         <v>-7.21</v>
       </c>
-      <c r="L31" s="378">
+      <c r="L31" s="384">
         <v>-9</v>
       </c>
-      <c r="M31" s="382">
+      <c r="M31" s="387">
         <v>-11.53</v>
       </c>
-      <c r="N31" s="383">
+      <c r="N31" s="388">
         <v>-10.42</v>
       </c>
-      <c r="O31" s="379">
+      <c r="O31" s="385">
         <v>-9.79</v>
       </c>
-      <c r="P31" s="386">
+      <c r="P31" s="389">
         <v>-11.32</v>
       </c>
-      <c r="Q31" s="380">
+      <c r="Q31" s="390">
         <v>-11.26</v>
       </c>
-      <c r="R31" s="384">
+      <c r="R31" s="380">
         <v>-9.89</v>
       </c>
-      <c r="S31" s="381">
+      <c r="S31" s="378">
         <v>-11.89</v>
       </c>
-      <c r="T31" s="385">
-        <v>-23.95</v>
+      <c r="T31" s="381">
+        <v>-23.26</v>
       </c>
     </row>
     <row r="32">
@@ -10702,7 +10718,7 @@
       <c r="C32" t="str">
         <v>300390</v>
       </c>
-      <c r="D32" s="399" t="str">
+      <c r="D32" s="393" t="str">
         <v>净卖: -2712.20万</v>
       </c>
       <c r="E32">
@@ -10717,41 +10733,41 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="400">
+      <c r="I32" s="402">
         <v>15.32</v>
       </c>
-      <c r="J32" s="394">
+      <c r="J32" s="396">
         <v>19.24</v>
       </c>
-      <c r="K32" s="401">
+      <c r="K32" s="399">
         <v>21.18</v>
       </c>
-      <c r="L32" s="395">
+      <c r="L32" s="403">
         <v>17.01</v>
       </c>
-      <c r="M32" s="398">
+      <c r="M32" s="400">
         <v>39.41</v>
       </c>
-      <c r="N32" s="402">
+      <c r="N32" s="397">
         <v>44.54</v>
       </c>
-      <c r="O32" s="403">
+      <c r="O32" s="398">
         <v>73.45</v>
       </c>
-      <c r="P32" s="396">
+      <c r="P32" s="391">
         <v>64.28</v>
       </c>
-      <c r="Q32" s="391">
+      <c r="Q32" s="401">
         <v>66.69</v>
       </c>
-      <c r="R32" s="392">
+      <c r="R32" s="394">
         <v>76.84</v>
       </c>
-      <c r="S32" s="393">
+      <c r="S32" s="392">
         <v>41.99</v>
       </c>
-      <c r="T32" s="397">
-        <v>164.07</v>
+      <c r="T32" s="395">
+        <v>173.45</v>
       </c>
     </row>
     <row r="33">
@@ -10764,7 +10780,7 @@
       <c r="C33" t="str">
         <v>603829</v>
       </c>
-      <c r="D33" s="410" t="str">
+      <c r="D33" s="414" t="str">
         <v>净卖: -2484.77万</v>
       </c>
       <c r="E33">
@@ -10779,41 +10795,41 @@
       <c r="H33">
         <v>0.16</v>
       </c>
-      <c r="I33" s="411">
+      <c r="I33" s="406">
         <v>-10.16</v>
       </c>
-      <c r="J33" s="405">
+      <c r="J33" s="412">
         <v>-9.96</v>
       </c>
-      <c r="K33" s="406">
+      <c r="K33" s="408">
         <v>-18.94</v>
       </c>
-      <c r="L33" s="412">
+      <c r="L33" s="415">
         <v>-22.65</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="409">
         <v>-22.75</v>
       </c>
-      <c r="N33" s="407">
+      <c r="N33" s="416">
         <v>-25.3</v>
       </c>
       <c r="O33" s="404">
         <v>-26.94</v>
       </c>
-      <c r="P33" s="413">
+      <c r="P33" s="405">
         <v>-27.14</v>
       </c>
-      <c r="Q33" s="408">
+      <c r="Q33" s="410">
         <v>-26.97</v>
       </c>
-      <c r="R33" s="414">
+      <c r="R33" s="411">
         <v>-27.01</v>
       </c>
-      <c r="S33" s="409">
+      <c r="S33" s="413">
         <v>-25.4</v>
       </c>
-      <c r="T33" s="415">
-        <v>-2.49</v>
+      <c r="T33" s="407">
+        <v>-3.97</v>
       </c>
     </row>
     <row r="34">
@@ -10826,7 +10842,7 @@
       <c r="C34" t="str">
         <v>603829</v>
       </c>
-      <c r="D34" s="424" t="str">
+      <c r="D34" s="421" t="str">
         <v>净卖: -2802.75万</v>
       </c>
       <c r="E34">
@@ -10841,41 +10857,41 @@
       <c r="H34">
         <v>0.15</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="422">
         <v>-10.11</v>
       </c>
-      <c r="J34" s="418">
+      <c r="J34" s="429">
         <v>-14.21</v>
       </c>
-      <c r="K34" s="422">
+      <c r="K34" s="417">
         <v>-14.32</v>
       </c>
-      <c r="L34" s="419">
+      <c r="L34" s="423">
         <v>-17.16</v>
       </c>
-      <c r="M34" s="420">
+      <c r="M34" s="425">
         <v>-18.97</v>
       </c>
-      <c r="N34" s="428">
+      <c r="N34" s="426">
         <v>-19.19</v>
       </c>
-      <c r="O34" s="429">
+      <c r="O34" s="424">
         <v>-19.01</v>
       </c>
-      <c r="P34" s="425">
+      <c r="P34" s="420">
         <v>-19.05</v>
       </c>
-      <c r="Q34" s="426">
+      <c r="Q34" s="418">
         <v>-17.27</v>
       </c>
-      <c r="R34" s="421">
+      <c r="R34" s="427">
         <v>-15.92</v>
       </c>
-      <c r="S34" s="427">
+      <c r="S34" s="419">
         <v>-14.76</v>
       </c>
-      <c r="T34" s="423">
-        <v>8.14</v>
+      <c r="T34" s="428">
+        <v>6.51</v>
       </c>
     </row>
     <row r="35">
@@ -10888,7 +10904,7 @@
       <c r="C35" t="str">
         <v>920427</v>
       </c>
-      <c r="D35" s="439" t="str">
+      <c r="D35" s="436" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E35">
@@ -10903,41 +10919,41 @@
       <c r="H35">
         <v>-8.89</v>
       </c>
-      <c r="I35" s="440">
+      <c r="I35" s="441">
         <v>-21.22</v>
       </c>
-      <c r="J35" s="430">
+      <c r="J35" s="437">
         <v>-19.61</v>
       </c>
-      <c r="K35" s="436">
+      <c r="K35" s="442">
         <v>-23.32</v>
       </c>
-      <c r="L35" s="434">
+      <c r="L35" s="432">
         <v>-23.12</v>
       </c>
-      <c r="M35" s="431">
+      <c r="M35" s="433">
         <v>-27.46</v>
       </c>
-      <c r="N35" s="441">
+      <c r="N35" s="438">
         <v>-27.71</v>
       </c>
-      <c r="O35" s="432">
+      <c r="O35" s="434">
         <v>-26.34</v>
       </c>
-      <c r="P35" s="437">
+      <c r="P35" s="439">
         <v>-23.22</v>
       </c>
-      <c r="Q35" s="433">
+      <c r="Q35" s="430">
         <v>-26.44</v>
       </c>
-      <c r="R35" s="438">
+      <c r="R35" s="435">
         <v>-27.12</v>
       </c>
-      <c r="S35" s="442">
+      <c r="S35" s="431">
         <v>-26.68</v>
       </c>
-      <c r="T35" s="435">
-        <v>-41.56</v>
+      <c r="T35" s="440">
+        <v>-43.41</v>
       </c>
     </row>
     <row r="36">
@@ -10950,7 +10966,7 @@
       <c r="C36" t="str">
         <v>920427</v>
       </c>
-      <c r="D36" s="447" t="str">
+      <c r="D36" s="445" t="str">
         <v>净卖: -130.63万</v>
       </c>
       <c r="E36">
@@ -10965,41 +10981,41 @@
       <c r="H36">
         <v>-4.33</v>
       </c>
-      <c r="I36" s="448">
+      <c r="I36" s="453">
         <v>6.67</v>
       </c>
-      <c r="J36" s="443">
+      <c r="J36" s="446">
         <v>1.75</v>
       </c>
-      <c r="K36" s="455">
+      <c r="K36" s="449">
         <v>2.01</v>
       </c>
-      <c r="L36" s="453">
+      <c r="L36" s="450">
         <v>-3.75</v>
       </c>
-      <c r="M36" s="449">
+      <c r="M36" s="443">
         <v>-4.08</v>
       </c>
-      <c r="N36" s="444">
+      <c r="N36" s="447">
         <v>-2.27</v>
       </c>
-      <c r="O36" s="445">
+      <c r="O36" s="454">
         <v>1.88</v>
       </c>
-      <c r="P36" s="446">
+      <c r="P36" s="448">
         <v>-2.39</v>
       </c>
-      <c r="Q36" s="450">
+      <c r="Q36" s="451">
         <v>-3.3</v>
       </c>
-      <c r="R36" s="451">
+      <c r="R36" s="455">
         <v>-2.72</v>
       </c>
-      <c r="S36" s="452">
+      <c r="S36" s="444">
         <v>-6.54</v>
       </c>
-      <c r="T36" s="454">
-        <v>-22.46</v>
+      <c r="T36" s="452">
+        <v>-24.92</v>
       </c>
     </row>
     <row r="37">
@@ -11012,7 +11028,7 @@
       <c r="C37" t="str">
         <v>603798</v>
       </c>
-      <c r="D37" s="457" t="str">
+      <c r="D37" s="461" t="str">
         <v>净卖: -286.39万</v>
       </c>
       <c r="E37">
@@ -11027,41 +11043,41 @@
       <c r="H37">
         <v>-9.99</v>
       </c>
-      <c r="I37" s="461">
+      <c r="I37" s="462">
         <v>0</v>
       </c>
-      <c r="J37" s="462">
+      <c r="J37" s="466">
         <v>-5.52</v>
       </c>
-      <c r="K37" s="464">
+      <c r="K37" s="463">
         <v>-0.12</v>
       </c>
-      <c r="L37" s="458">
+      <c r="L37" s="457">
         <v>-0.72</v>
       </c>
-      <c r="M37" s="465">
+      <c r="M37" s="458">
         <v>-6.3</v>
       </c>
-      <c r="N37" s="463">
+      <c r="N37" s="464">
         <v>-2.82</v>
       </c>
-      <c r="O37" s="468">
+      <c r="O37" s="467">
         <v>-3.3</v>
       </c>
-      <c r="P37" s="456">
+      <c r="P37" s="459">
         <v>-5.34</v>
       </c>
-      <c r="Q37" s="459">
+      <c r="Q37" s="460">
         <v>-4.92</v>
       </c>
-      <c r="R37" s="466">
+      <c r="R37" s="468">
         <v>0.72</v>
       </c>
-      <c r="S37" s="460">
+      <c r="S37" s="456">
         <v>-4.08</v>
       </c>
-      <c r="T37" s="467">
-        <v>4.2</v>
+      <c r="T37" s="465">
+        <v>9.36</v>
       </c>
     </row>
     <row r="38">
@@ -11074,7 +11090,7 @@
       <c r="C38" t="str">
         <v>603291</v>
       </c>
-      <c r="D38" s="476" t="str">
+      <c r="D38" s="469" t="str">
         <v>净买: 465.04万</v>
       </c>
       <c r="E38">
@@ -11089,41 +11105,41 @@
       <c r="H38">
         <v>1.97</v>
       </c>
-      <c r="I38" s="477">
+      <c r="I38" s="475">
         <v>-11.73</v>
       </c>
-      <c r="J38" s="474">
+      <c r="J38" s="476">
         <v>-11.73</v>
       </c>
       <c r="K38" s="478">
         <v>-15.59</v>
       </c>
-      <c r="L38" s="479">
+      <c r="L38" s="470">
         <v>-15.51</v>
       </c>
-      <c r="M38" s="469">
+      <c r="M38" s="479">
         <v>-14.97</v>
       </c>
-      <c r="N38" s="475">
+      <c r="N38" s="471">
         <v>-15.66</v>
       </c>
-      <c r="O38" s="471">
+      <c r="O38" s="472">
         <v>-15.82</v>
       </c>
-      <c r="P38" s="470">
+      <c r="P38" s="477">
         <v>-16.05</v>
       </c>
-      <c r="Q38" s="480">
+      <c r="Q38" s="473">
         <v>-15.97</v>
       </c>
-      <c r="R38" s="481">
+      <c r="R38" s="480">
         <v>-15.51</v>
       </c>
-      <c r="S38" s="472">
+      <c r="S38" s="474">
         <v>-15.59</v>
       </c>
-      <c r="T38" s="473">
-        <v>-9.57</v>
+      <c r="T38" s="481">
+        <v>-6.64</v>
       </c>
     </row>
     <row r="39">
@@ -11136,7 +11152,7 @@
       <c r="C39" t="str">
         <v>603284</v>
       </c>
-      <c r="D39" s="491" t="str">
+      <c r="D39" s="482" t="str">
         <v>净买: 1322.73万</v>
       </c>
       <c r="E39">
@@ -11151,41 +11167,41 @@
       <c r="H39">
         <v>-0.79</v>
       </c>
-      <c r="I39" s="484">
+      <c r="I39" s="492">
         <v>4.15</v>
       </c>
-      <c r="J39" s="485">
+      <c r="J39" s="493">
         <v>7.16</v>
       </c>
-      <c r="K39" s="489">
+      <c r="K39" s="488">
         <v>7.16</v>
       </c>
-      <c r="L39" s="492">
+      <c r="L39" s="483">
         <v>7.39</v>
       </c>
-      <c r="M39" s="486">
+      <c r="M39" s="484">
         <v>7.45</v>
       </c>
-      <c r="N39" s="482">
+      <c r="N39" s="485">
         <v>8.48</v>
       </c>
-      <c r="O39" s="493">
+      <c r="O39" s="494">
         <v>6.71</v>
       </c>
-      <c r="P39" s="487">
+      <c r="P39" s="486">
         <v>7.41</v>
       </c>
-      <c r="Q39" s="490">
+      <c r="Q39" s="487">
         <v>7.64</v>
       </c>
-      <c r="R39" s="494">
+      <c r="R39" s="489">
         <v>6.33</v>
       </c>
-      <c r="S39" s="488">
+      <c r="S39" s="490">
         <v>3.28</v>
       </c>
-      <c r="T39" s="483">
-        <v>2.69</v>
+      <c r="T39" s="491">
+        <v>-7.58</v>
       </c>
     </row>
     <row r="40">
@@ -11198,7 +11214,7 @@
       <c r="C40" t="str">
         <v>600605</v>
       </c>
-      <c r="D40" s="497" t="str">
+      <c r="D40" s="498" t="str">
         <v>净卖: -789.04万</v>
       </c>
       <c r="E40">
@@ -11213,35 +11229,37 @@
       <c r="H40">
         <v>6.5</v>
       </c>
-      <c r="I40" s="498">
+      <c r="I40" s="505">
         <v>3.29</v>
       </c>
-      <c r="J40" s="499">
+      <c r="J40" s="495">
         <v>-0.16</v>
       </c>
-      <c r="K40" s="502">
+      <c r="K40" s="501">
         <v>-1.47</v>
       </c>
-      <c r="L40" s="500">
+      <c r="L40" s="496">
         <v>-3.1</v>
       </c>
-      <c r="M40" s="503">
+      <c r="M40" s="499">
         <v>-2.08</v>
       </c>
-      <c r="N40" s="504">
+      <c r="N40" s="502">
         <v>-2.04</v>
       </c>
-      <c r="O40" s="501">
+      <c r="O40" s="504">
         <v>-4.31</v>
       </c>
-      <c r="P40" s="495">
+      <c r="P40" s="503">
         <v>1.66</v>
       </c>
-      <c r="Q40" t="str"/>
+      <c r="Q40" s="500">
+        <v>5.05</v>
+      </c>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="496">
-        <v>1.66</v>
+      <c r="T40" s="497">
+        <v>5.05</v>
       </c>
     </row>
     <row r="41">
@@ -11280,7 +11298,7 @@
         <v>39</v>
       </c>
       <c r="Q41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R41">
         <v>38</v>
@@ -11303,41 +11321,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="512">
+      <c r="I42" s="508">
         <v>38.46</v>
       </c>
-      <c r="J42" s="508">
+      <c r="J42" s="516">
         <v>41.03</v>
       </c>
-      <c r="K42" s="509">
+      <c r="K42" s="507">
         <v>38.46</v>
       </c>
-      <c r="L42" s="513">
+      <c r="L42" s="509">
         <v>35.9</v>
       </c>
-      <c r="M42" s="505">
+      <c r="M42" s="513">
         <v>28.21</v>
       </c>
-      <c r="N42" s="506">
+      <c r="N42" s="510">
         <v>25.64</v>
       </c>
-      <c r="O42" s="515">
+      <c r="O42" s="511">
         <v>30.77</v>
       </c>
-      <c r="P42" s="510">
+      <c r="P42" s="512">
         <v>35.9</v>
       </c>
-      <c r="Q42" s="507">
-        <v>26.32</v>
+      <c r="Q42" s="517">
+        <v>28.21</v>
       </c>
       <c r="R42" s="514">
         <v>31.58</v>
       </c>
-      <c r="S42" s="511">
+      <c r="S42" s="506">
         <v>21.05</v>
       </c>
-      <c r="T42" s="516">
-        <v>56.41</v>
+      <c r="T42" s="515">
+        <v>53.85</v>
       </c>
     </row>
     <row r="43">
@@ -11351,41 +11369,41 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="521">
+      <c r="I43" s="523">
         <v>-0.38</v>
       </c>
-      <c r="J43" s="522">
+      <c r="J43" s="519">
         <v>-0.74</v>
       </c>
-      <c r="K43" s="524">
+      <c r="K43" s="520">
         <v>-2.11</v>
       </c>
-      <c r="L43" s="525">
+      <c r="L43" s="524">
         <v>-4.11</v>
       </c>
-      <c r="M43" s="518">
+      <c r="M43" s="525">
         <v>-5.17</v>
       </c>
-      <c r="N43" s="526">
+      <c r="N43" s="529">
         <v>-6.48</v>
       </c>
-      <c r="O43" s="527">
+      <c r="O43" s="521">
         <v>-5.38</v>
       </c>
-      <c r="P43" s="520">
+      <c r="P43" s="526">
         <v>-5.52</v>
       </c>
-      <c r="Q43" s="528">
-        <v>-6.11</v>
-      </c>
-      <c r="R43" s="523">
+      <c r="Q43" s="527">
+        <v>-5.82</v>
+      </c>
+      <c r="R43" s="528">
         <v>-5.24</v>
       </c>
-      <c r="S43" s="517">
+      <c r="S43" s="518">
         <v>-7.62</v>
       </c>
-      <c r="T43" s="519">
-        <v>16.09</v>
+      <c r="T43" s="522">
+        <v>17.07</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/申港广东分/index.xlsx
+++ b/youzi/申港广东分/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="531">
+  <fills count="532">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -45,6 +45,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF4C3C8"/>
         <bgColor/>
       </patternFill>
@@ -57,12 +81,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -75,36 +93,552 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADDDB8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91D2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6707C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF69C17D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -117,19 +651,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,19 +747,2089 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA3AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3C4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF9FA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF59BB6F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF85CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,25 +2841,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,943 +2889,295 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87D87"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91D2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6707C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C788"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3C4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA3AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF9FA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
+        <fgColor rgb="FFD6EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1143,2046 +3189,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF59BB6F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF49B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -3212,7 +3218,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="530">
+  <borders count="531">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6927,7 +6940,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="530">
+  <cellXfs count="531">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8514,6 +8527,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="529" fillId="530" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="530" fillId="531" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8858,7 +8874,7 @@
       <c r="C2" t="str">
         <v>603110</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="13" t="str">
         <v>净买: 1763.82万</v>
       </c>
       <c r="E2">
@@ -8873,41 +8889,41 @@
       <c r="H2">
         <v>9.98</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="1">
         <v>9.98</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="5">
         <v>3.91</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="6">
         <v>1.47</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <v>11.62</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="7">
         <v>22.79</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="8">
         <v>15.02</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="3">
         <v>26.53</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="4">
         <v>32.65</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="9">
         <v>28.74</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="11">
         <v>21.77</v>
       </c>
-      <c r="T2" s="1">
-        <v>11.45</v>
+      <c r="T2" s="12">
+        <v>19.67</v>
       </c>
     </row>
     <row r="3">
@@ -8920,7 +8936,7 @@
       <c r="C3" t="str">
         <v>603110</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="19" t="str">
         <v>净买: 486.49万</v>
       </c>
       <c r="E3">
@@ -8935,10 +8951,10 @@
       <c r="H3">
         <v>6.6</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="25">
         <v>-11.36</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="20">
         <v>-13.44</v>
       </c>
       <c r="K3" s="22">
@@ -8947,29 +8963,29 @@
       <c r="L3" s="23">
         <v>4.74</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="26">
         <v>-1.89</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="14">
         <v>7.93</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="15">
         <v>13.15</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="16">
         <v>9.82</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="18">
         <v>3.87</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="21">
         <v>6.53</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="17">
         <v>-4.11</v>
       </c>
-      <c r="T3" s="21">
-        <v>-4.93</v>
+      <c r="T3" s="24">
+        <v>2.08</v>
       </c>
     </row>
     <row r="4">
@@ -8982,7 +8998,7 @@
       <c r="C4" t="str">
         <v>603881</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="36" t="str">
         <v>净买: 7242.53万</v>
       </c>
       <c r="E4">
@@ -8997,41 +9013,41 @@
       <c r="H4">
         <v>8.87</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="39">
         <v>1.04</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="27">
         <v>11.14</v>
       </c>
       <c r="K4" s="37">
         <v>0.03</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="28">
         <v>7.5</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="33">
         <v>8.74</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="29">
         <v>19.61</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="34">
         <v>25.9</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="35">
         <v>21.45</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="30">
         <v>15.56</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="31">
         <v>9.81</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="38">
         <v>-0.74</v>
       </c>
-      <c r="T4" s="36">
-        <v>10.52</v>
+      <c r="T4" s="32">
+        <v>8.47</v>
       </c>
     </row>
     <row r="5">
@@ -9044,7 +9060,7 @@
       <c r="C5" t="str">
         <v>603881</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="43" t="str">
         <v>净卖: -9194.30万</v>
       </c>
       <c r="E5">
@@ -9059,41 +9075,41 @@
       <c r="H5">
         <v>-4.56</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="44">
         <v>-5.7</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="49">
         <v>1.34</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="45">
         <v>2.51</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="42">
         <v>12.77</v>
       </c>
       <c r="M5" s="50">
         <v>18.69</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="46">
         <v>14.5</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="47">
         <v>8.94</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="51">
         <v>3.52</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="52">
         <v>-6.42</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="48">
         <v>-4.83</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="40">
         <v>-3.18</v>
       </c>
-      <c r="T5" s="43">
-        <v>4.19</v>
+      <c r="T5" s="41">
+        <v>2.26</v>
       </c>
     </row>
     <row r="6">
@@ -9106,7 +9122,7 @@
       <c r="C6" t="str">
         <v>000818</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 5099.54万</v>
       </c>
       <c r="E6">
@@ -9121,41 +9137,41 @@
       <c r="H6">
         <v>5.63</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="55">
         <v>4.13</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="59">
         <v>14.56</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="65">
         <v>7.97</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="53">
         <v>-2.83</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="64">
         <v>-12.53</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="60">
         <v>-15.63</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="56">
         <v>-12.8</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="61">
         <v>-16.13</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="57">
         <v>-19.84</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="54">
         <v>-20.37</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="58">
         <v>-19.6</v>
       </c>
-      <c r="T6" s="64">
-        <v>-62.43</v>
+      <c r="T6" s="62">
+        <v>-62.61</v>
       </c>
     </row>
     <row r="7">
@@ -9168,7 +9184,7 @@
       <c r="C7" t="str">
         <v>600590</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="75" t="str">
         <v>净买: 1013.84万</v>
       </c>
       <c r="E7">
@@ -9183,41 +9199,41 @@
       <c r="H7">
         <v>10.05</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="78">
         <v>0</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="69">
         <v>-2.39</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="73">
         <v>7.39</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="70">
         <v>1.85</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="71">
         <v>1.63</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="74">
         <v>-5.76</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="66">
         <v>-3.48</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="72">
         <v>6.2</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="67">
         <v>16.85</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="76">
         <v>26.41</v>
       </c>
       <c r="S7" s="77">
         <v>21.74</v>
       </c>
-      <c r="T7" s="66">
-        <v>78.04</v>
+      <c r="T7" s="68">
+        <v>72.07</v>
       </c>
     </row>
     <row r="8">
@@ -9230,7 +9246,7 @@
       <c r="C8" t="str">
         <v>000818</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="83" t="str">
         <v>净卖: -5301.29万</v>
       </c>
       <c r="E8">
@@ -9245,41 +9261,41 @@
       <c r="H8">
         <v>-10</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="81">
         <v>0</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="84">
         <v>-9.99</v>
       </c>
       <c r="K8" s="80">
         <v>-13.17</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="88">
         <v>-10.26</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="89">
         <v>-13.69</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="90">
         <v>-17.51</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="91">
         <v>-18.06</v>
       </c>
-      <c r="P8" s="91">
+      <c r="P8" s="85">
         <v>-17.26</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="79">
         <v>-14.79</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="86">
         <v>-16.85</v>
       </c>
       <c r="S8" s="87">
         <v>-14.02</v>
       </c>
-      <c r="T8" s="79">
-        <v>-61.33</v>
+      <c r="T8" s="82">
+        <v>-61.53</v>
       </c>
     </row>
     <row r="9">
@@ -9292,7 +9308,7 @@
       <c r="C9" t="str">
         <v>002290</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="97" t="str">
         <v>净卖: -2168.44万</v>
       </c>
       <c r="E9">
@@ -9307,41 +9323,41 @@
       <c r="H9">
         <v>-9.5</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="94">
         <v>-0.54</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="103">
         <v>0</v>
       </c>
-      <c r="K9" s="95">
+      <c r="K9" s="98">
         <v>0.33</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="95">
         <v>3.33</v>
       </c>
       <c r="M9" s="99">
         <v>-7</v>
       </c>
-      <c r="N9" s="94">
+      <c r="N9" s="100">
         <v>-1.67</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="104">
         <v>6.04</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="92">
         <v>7.58</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="101">
         <v>12.71</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="102">
         <v>16.92</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="93">
         <v>12.79</v>
       </c>
-      <c r="T9" s="104">
-        <v>266.96</v>
+      <c r="T9" s="96">
+        <v>230.25</v>
       </c>
     </row>
     <row r="10">
@@ -9354,7 +9370,7 @@
       <c r="C10" t="str">
         <v>605300</v>
       </c>
-      <c r="D10" s="116" t="str">
+      <c r="D10" s="107" t="str">
         <v>净买: 1145.88万</v>
       </c>
       <c r="E10">
@@ -9369,22 +9385,22 @@
       <c r="H10">
         <v>1.49</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="117">
         <v>8.41</v>
       </c>
-      <c r="J10" s="117">
+      <c r="J10" s="108">
         <v>-2.41</v>
       </c>
-      <c r="K10" s="105">
+      <c r="K10" s="113">
         <v>-12.18</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="109">
         <v>-15</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="110">
         <v>-12.88</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="114">
         <v>-14.71</v>
       </c>
       <c r="O10" s="111">
@@ -9393,17 +9409,17 @@
       <c r="P10" s="112">
         <v>-16.18</v>
       </c>
-      <c r="Q10" s="109">
+      <c r="Q10" s="105">
         <v>-16.82</v>
       </c>
-      <c r="R10" s="106">
+      <c r="R10" s="115">
         <v>-18.35</v>
       </c>
-      <c r="S10" s="114">
+      <c r="S10" s="106">
         <v>-15.18</v>
       </c>
-      <c r="T10" s="115">
-        <v>-34.47</v>
+      <c r="T10" s="116">
+        <v>-34.76</v>
       </c>
     </row>
     <row r="11">
@@ -9416,7 +9432,7 @@
       <c r="C11" t="str">
         <v>605100</v>
       </c>
-      <c r="D11" s="125" t="str">
+      <c r="D11" s="124" t="str">
         <v>净买: 1795.46万</v>
       </c>
       <c r="E11">
@@ -9431,22 +9447,22 @@
       <c r="H11">
         <v>9.99</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="123">
         <v>0</v>
       </c>
-      <c r="J11" s="126">
+      <c r="J11" s="125">
         <v>-9.16</v>
       </c>
-      <c r="K11" s="127">
+      <c r="K11" s="126">
         <v>-0.08</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="120">
         <v>0</v>
       </c>
-      <c r="M11" s="128">
+      <c r="M11" s="127">
         <v>9.99</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="128">
         <v>-0.99</v>
       </c>
       <c r="O11" s="129">
@@ -9455,17 +9471,17 @@
       <c r="P11" s="121">
         <v>19.83</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="130">
         <v>12.16</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="122">
         <v>23.38</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="118">
         <v>13.07</v>
       </c>
-      <c r="T11" s="120">
-        <v>91.15</v>
+      <c r="T11" s="119">
+        <v>91.82</v>
       </c>
     </row>
     <row r="12">
@@ -9478,7 +9494,7 @@
       <c r="C12" t="str">
         <v>605300</v>
       </c>
-      <c r="D12" s="137" t="str">
+      <c r="D12" s="142" t="str">
         <v>净卖: -1034.72万</v>
       </c>
       <c r="E12">
@@ -9493,41 +9509,41 @@
       <c r="H12">
         <v>-5.36</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="135">
         <v>2.26</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="136">
         <v>4.81</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="137">
         <v>2.62</v>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="134">
         <v>1.49</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="138">
         <v>0.85</v>
       </c>
-      <c r="N12" s="139">
+      <c r="N12" s="143">
         <v>0.07</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="139">
         <v>-1.77</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="131">
         <v>2.05</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="132">
         <v>0.85</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="140">
         <v>0.21</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="141">
         <v>-0.92</v>
       </c>
-      <c r="T12" s="136">
-        <v>-21.16</v>
+      <c r="T12" s="133">
+        <v>-21.51</v>
       </c>
     </row>
     <row r="13">
@@ -9540,7 +9556,7 @@
       <c r="C13" t="str">
         <v>002114</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="150" t="str">
         <v>净买: 1554.85万</v>
       </c>
       <c r="E13">
@@ -9555,41 +9571,41 @@
       <c r="H13">
         <v>9.83</v>
       </c>
-      <c r="I13" s="154">
+      <c r="I13" s="146">
         <v>0.13</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="155">
         <v>-1.41</v>
       </c>
-      <c r="K13" s="147">
+      <c r="K13" s="156">
         <v>-4.6</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="153">
         <v>-6.65</v>
       </c>
-      <c r="M13" s="153">
+      <c r="M13" s="154">
         <v>-6.01</v>
       </c>
-      <c r="N13" s="148">
+      <c r="N13" s="151">
         <v>-6.52</v>
       </c>
-      <c r="O13" s="149">
+      <c r="O13" s="144">
         <v>-5.5</v>
       </c>
-      <c r="P13" s="150">
+      <c r="P13" s="147">
         <v>-10.1</v>
       </c>
-      <c r="Q13" s="156">
+      <c r="Q13" s="148">
         <v>-9.59</v>
       </c>
-      <c r="R13" s="151">
+      <c r="R13" s="145">
         <v>-10.87</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="149">
         <v>-11.76</v>
       </c>
-      <c r="T13" s="145">
-        <v>16.11</v>
+      <c r="T13" s="152">
+        <v>13.3</v>
       </c>
     </row>
     <row r="14">
@@ -9623,35 +9639,35 @@
       <c r="J14" s="164">
         <v>-7.6</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="162">
         <v>-13.68</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="165">
         <v>-20.06</v>
       </c>
-      <c r="M14" s="167">
+      <c r="M14" s="158">
         <v>-20.21</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="159">
         <v>-21.58</v>
       </c>
-      <c r="O14" s="158">
+      <c r="O14" s="163">
         <v>-22.87</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="167">
         <v>-23.86</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="166">
         <v>-24.62</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="160">
         <v>-27.13</v>
       </c>
       <c r="S14" s="168">
         <v>-26.6</v>
       </c>
-      <c r="T14" s="163">
-        <v>73.25</v>
+      <c r="T14" s="161">
+        <v>75.15</v>
       </c>
     </row>
     <row r="15">
@@ -9664,7 +9680,7 @@
       <c r="C15" t="str">
         <v>605303</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="174" t="str">
         <v>净卖: -1462.35万</v>
       </c>
       <c r="E15">
@@ -9679,41 +9695,41 @@
       <c r="H15">
         <v>-2.55</v>
       </c>
-      <c r="I15" s="175">
+      <c r="I15" s="178">
         <v>-4.97</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="179">
         <v>-5.15</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="180">
         <v>-6.78</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="172">
         <v>-8.31</v>
       </c>
-      <c r="M15" s="172">
+      <c r="M15" s="181">
         <v>-9.49</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="175">
         <v>-10.39</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="182">
         <v>-13.37</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="170">
         <v>-12.74</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="171">
         <v>-14.27</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="176">
         <v>-15.54</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="177">
         <v>-16.71</v>
       </c>
-      <c r="T15" s="182">
-        <v>105.96</v>
+      <c r="T15" s="173">
+        <v>108.22</v>
       </c>
     </row>
     <row r="16">
@@ -9726,7 +9742,7 @@
       <c r="C16" t="str">
         <v>600301</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="192" t="str">
         <v>净卖: -3080.81万</v>
       </c>
       <c r="E16">
@@ -9741,41 +9757,41 @@
       <c r="H16">
         <v>-2.8</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="186">
         <v>-4.62</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="195">
         <v>-5.96</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="187">
         <v>-4.88</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="183">
         <v>-5.27</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="193">
         <v>-3.31</v>
       </c>
-      <c r="N16" s="194">
+      <c r="N16" s="188">
         <v>-7.19</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="189">
         <v>-7.88</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="194">
         <v>-7.88</v>
       </c>
-      <c r="Q16" s="189">
+      <c r="Q16" s="184">
         <v>-10.35</v>
       </c>
-      <c r="R16" s="190">
+      <c r="R16" s="185">
         <v>-11.15</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="190">
         <v>-14.38</v>
       </c>
-      <c r="T16" s="195">
-        <v>99.73</v>
+      <c r="T16" s="191">
+        <v>89.15</v>
       </c>
     </row>
     <row r="17">
@@ -9788,7 +9804,7 @@
       <c r="C17" t="str">
         <v>000815</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="199" t="str">
         <v>净买: 5327.66万</v>
       </c>
       <c r="E17">
@@ -9803,41 +9819,41 @@
       <c r="H17">
         <v>2.39</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="197">
         <v>2.95</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="203">
         <v>-3.14</v>
       </c>
-      <c r="K17" s="200">
+      <c r="K17" s="204">
         <v>-4.8</v>
       </c>
       <c r="L17" s="205">
         <v>-6.52</v>
       </c>
-      <c r="M17" s="208">
+      <c r="M17" s="206">
         <v>-12.98</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="208">
         <v>-17.22</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="200">
         <v>-16.91</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="198">
         <v>-20.79</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="201">
         <v>-20.3</v>
       </c>
-      <c r="R17" s="199">
+      <c r="R17" s="207">
         <v>-19.74</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="202">
         <v>-20.85</v>
       </c>
-      <c r="T17" s="202">
-        <v>20.79</v>
+      <c r="T17" s="196">
+        <v>23.55</v>
       </c>
     </row>
     <row r="18">
@@ -9850,7 +9866,7 @@
       <c r="C18" t="str">
         <v>603315</v>
       </c>
-      <c r="D18" s="220" t="str">
+      <c r="D18" s="217" t="str">
         <v>净买: 2006.31万</v>
       </c>
       <c r="E18">
@@ -9865,41 +9881,41 @@
       <c r="H18">
         <v>10.03</v>
       </c>
-      <c r="I18" s="216">
+      <c r="I18" s="218">
         <v>0</v>
       </c>
-      <c r="J18" s="213">
+      <c r="J18" s="219">
         <v>9.99</v>
       </c>
-      <c r="K18" s="221">
+      <c r="K18" s="209">
         <v>20.99</v>
       </c>
-      <c r="L18" s="209">
+      <c r="L18" s="213">
         <v>8.87</v>
       </c>
       <c r="M18" s="210">
         <v>-2</v>
       </c>
-      <c r="N18" s="219">
+      <c r="N18" s="211">
         <v>-11.81</v>
       </c>
-      <c r="O18" s="217">
+      <c r="O18" s="214">
         <v>-12.8</v>
       </c>
-      <c r="P18" s="214">
+      <c r="P18" s="215">
         <v>-17.49</v>
       </c>
-      <c r="Q18" s="211">
+      <c r="Q18" s="216">
         <v>-18.11</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="220">
         <v>-16.36</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="221">
         <v>-16.55</v>
       </c>
-      <c r="T18" s="218">
-        <v>15.3</v>
+      <c r="T18" s="212">
+        <v>8.12</v>
       </c>
     </row>
     <row r="19">
@@ -9912,7 +9928,7 @@
       <c r="C19" t="str">
         <v>603315</v>
       </c>
-      <c r="D19" s="222" t="str">
+      <c r="D19" s="228" t="str">
         <v>净卖: -2227.67万</v>
       </c>
       <c r="E19">
@@ -9927,41 +9943,41 @@
       <c r="H19">
         <v>-4.2</v>
       </c>
-      <c r="I19" s="226">
+      <c r="I19" s="222">
         <v>14.82</v>
       </c>
-      <c r="J19" s="232">
+      <c r="J19" s="223">
         <v>3.32</v>
       </c>
-      <c r="K19" s="223">
+      <c r="K19" s="232">
         <v>-6.99</v>
       </c>
-      <c r="L19" s="224">
+      <c r="L19" s="229">
         <v>-16.3</v>
       </c>
-      <c r="M19" s="227">
+      <c r="M19" s="230">
         <v>-17.25</v>
       </c>
-      <c r="N19" s="225">
+      <c r="N19" s="233">
         <v>-21.7</v>
       </c>
-      <c r="O19" s="233">
+      <c r="O19" s="231">
         <v>-22.29</v>
       </c>
-      <c r="P19" s="228">
+      <c r="P19" s="234">
         <v>-20.63</v>
       </c>
-      <c r="Q19" s="229">
+      <c r="Q19" s="226">
         <v>-20.81</v>
       </c>
-      <c r="R19" s="234">
+      <c r="R19" s="224">
         <v>-20.09</v>
       </c>
-      <c r="S19" s="230">
+      <c r="S19" s="225">
         <v>-22.05</v>
       </c>
-      <c r="T19" s="231">
-        <v>9.43</v>
+      <c r="T19" s="227">
+        <v>2.61</v>
       </c>
     </row>
     <row r="20">
@@ -9974,7 +9990,7 @@
       <c r="C20" t="str">
         <v>000737</v>
       </c>
-      <c r="D20" s="237" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 2607.05万</v>
       </c>
       <c r="E20">
@@ -9989,41 +10005,41 @@
       <c r="H20">
         <v>0.79</v>
       </c>
-      <c r="I20" s="240">
+      <c r="I20" s="237">
         <v>9.19</v>
       </c>
-      <c r="J20" s="245">
+      <c r="J20" s="244">
         <v>15.54</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="238">
         <v>20.43</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="239">
         <v>11.93</v>
       </c>
-      <c r="M20" s="246">
+      <c r="M20" s="245">
         <v>4.79</v>
       </c>
-      <c r="N20" s="243">
+      <c r="N20" s="240">
         <v>2.64</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="241">
         <v>2.83</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="235">
         <v>1.08</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="242">
         <v>-2.15</v>
       </c>
-      <c r="R20" s="247">
+      <c r="R20" s="243">
         <v>-11.93</v>
       </c>
-      <c r="S20" s="235">
+      <c r="S20" s="246">
         <v>-19.65</v>
       </c>
       <c r="T20" s="236">
-        <v>33.92</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="21">
@@ -10036,7 +10052,7 @@
       <c r="C21" t="str">
         <v>000779</v>
       </c>
-      <c r="D21" s="260" t="str">
+      <c r="D21" s="258" t="str">
         <v>净买: 1464.90万</v>
       </c>
       <c r="E21">
@@ -10051,40 +10067,40 @@
       <c r="H21">
         <v>9.36</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="256">
         <v>-14.36</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="259">
         <v>-22.92</v>
       </c>
-      <c r="K21" s="254">
+      <c r="K21" s="253">
         <v>-25.67</v>
       </c>
-      <c r="L21" s="249">
+      <c r="L21" s="260">
         <v>-28.8</v>
       </c>
-      <c r="M21" s="255">
+      <c r="M21" s="254">
         <v>-29.11</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="248">
         <v>-26.05</v>
       </c>
-      <c r="O21" s="259">
+      <c r="O21" s="251">
         <v>-28.27</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="252">
         <v>-29.03</v>
       </c>
-      <c r="Q21" s="250">
+      <c r="Q21" s="249">
         <v>-29.95</v>
       </c>
-      <c r="R21" s="258">
+      <c r="R21" s="255">
         <v>-36.97</v>
       </c>
-      <c r="S21" s="251">
+      <c r="S21" s="257">
         <v>-35.91</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="250">
         <v>-33.61</v>
       </c>
     </row>
@@ -10098,7 +10114,7 @@
       <c r="C22" t="str">
         <v>600727</v>
       </c>
-      <c r="D22" s="261" t="str">
+      <c r="D22" s="272" t="str">
         <v>净卖: -2220.75万</v>
       </c>
       <c r="E22">
@@ -10113,41 +10129,41 @@
       <c r="H22">
         <v>4.31</v>
       </c>
-      <c r="I22" s="268">
+      <c r="I22" s="265">
         <v>-1.31</v>
       </c>
-      <c r="J22" s="262">
+      <c r="J22" s="266">
         <v>0.76</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="267">
         <v>-9.36</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="273">
         <v>-13.71</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="270">
         <v>-11.32</v>
       </c>
-      <c r="N22" s="264">
+      <c r="N22" s="261">
         <v>-12.08</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="268">
         <v>-7.51</v>
       </c>
-      <c r="P22" s="265">
+      <c r="P22" s="269">
         <v>-16.76</v>
       </c>
-      <c r="Q22" s="272">
+      <c r="Q22" s="263">
         <v>-15.13</v>
       </c>
-      <c r="R22" s="273">
+      <c r="R22" s="262">
         <v>-16.76</v>
       </c>
       <c r="S22" s="271">
         <v>-15.67</v>
       </c>
-      <c r="T22" s="267">
-        <v>-13.28</v>
+      <c r="T22" s="264">
+        <v>-13.93</v>
       </c>
     </row>
     <row r="23">
@@ -10160,7 +10176,7 @@
       <c r="C23" t="str">
         <v>001217</v>
       </c>
-      <c r="D23" s="277" t="str">
+      <c r="D23" s="278" t="str">
         <v>净买: 3127.44万</v>
       </c>
       <c r="E23">
@@ -10175,41 +10191,41 @@
       <c r="H23">
         <v>9.99</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="283">
         <v>0</v>
       </c>
       <c r="J23" s="275">
         <v>-8.55</v>
       </c>
-      <c r="K23" s="278">
+      <c r="K23" s="279">
         <v>-13.73</v>
       </c>
-      <c r="L23" s="280">
+      <c r="L23" s="284">
         <v>-17.5</v>
       </c>
-      <c r="M23" s="276">
+      <c r="M23" s="280">
         <v>-20.66</v>
       </c>
-      <c r="N23" s="279">
+      <c r="N23" s="281">
         <v>-28.6</v>
       </c>
-      <c r="O23" s="281">
+      <c r="O23" s="285">
         <v>-31.02</v>
       </c>
-      <c r="P23" s="282">
+      <c r="P23" s="286">
         <v>-31.09</v>
       </c>
-      <c r="Q23" s="283">
+      <c r="Q23" s="274">
         <v>-29.48</v>
       </c>
-      <c r="R23" s="284">
+      <c r="R23" s="276">
         <v>-28.33</v>
       </c>
-      <c r="S23" s="285">
+      <c r="S23" s="277">
         <v>-26.72</v>
       </c>
-      <c r="T23" s="286">
-        <v>-18.57</v>
+      <c r="T23" s="282">
+        <v>-19.52</v>
       </c>
     </row>
     <row r="24">
@@ -10237,41 +10253,41 @@
       <c r="H24">
         <v>-3.3</v>
       </c>
-      <c r="I24" s="288">
+      <c r="I24" s="290">
         <v>-6.9</v>
       </c>
-      <c r="J24" s="293">
+      <c r="J24" s="288">
         <v>-8.84</v>
       </c>
-      <c r="K24" s="289">
+      <c r="K24" s="294">
         <v>-7.5</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="295">
         <v>-7.64</v>
       </c>
-      <c r="M24" s="299">
+      <c r="M24" s="297">
         <v>-12.93</v>
       </c>
-      <c r="N24" s="290">
+      <c r="N24" s="296">
         <v>-21.63</v>
       </c>
-      <c r="O24" s="294">
+      <c r="O24" s="298">
         <v>-20.23</v>
       </c>
       <c r="P24" s="291">
         <v>-21.57</v>
       </c>
-      <c r="Q24" s="295">
+      <c r="Q24" s="292">
         <v>-20.09</v>
       </c>
-      <c r="R24" s="296">
+      <c r="R24" s="299">
         <v>-20.03</v>
       </c>
-      <c r="S24" s="297">
+      <c r="S24" s="289">
         <v>-17.62</v>
       </c>
-      <c r="T24" s="292">
-        <v>7.77</v>
+      <c r="T24" s="293">
+        <v>13.19</v>
       </c>
     </row>
     <row r="25">
@@ -10284,7 +10300,7 @@
       <c r="C25" t="str">
         <v>001333</v>
       </c>
-      <c r="D25" s="308" t="str">
+      <c r="D25" s="309" t="str">
         <v>净买: 1650.82万</v>
       </c>
       <c r="E25">
@@ -10299,41 +10315,41 @@
       <c r="H25">
         <v>-1.88</v>
       </c>
-      <c r="I25" s="300">
+      <c r="I25" s="303">
         <v>12.11</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="310">
         <v>23.33</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="304">
         <v>11.01</v>
       </c>
-      <c r="L25" s="303">
+      <c r="L25" s="305">
         <v>-0.08</v>
       </c>
-      <c r="M25" s="310">
+      <c r="M25" s="311">
         <v>-10.07</v>
       </c>
-      <c r="N25" s="304">
+      <c r="N25" s="312">
         <v>-18.1</v>
       </c>
-      <c r="O25" s="305">
+      <c r="O25" s="306">
         <v>-17.47</v>
       </c>
-      <c r="P25" s="306">
+      <c r="P25" s="300">
         <v>-15.81</v>
       </c>
-      <c r="Q25" s="309">
+      <c r="Q25" s="301">
         <v>-10.96</v>
       </c>
-      <c r="R25" s="307">
+      <c r="R25" s="302">
         <v>-8.75</v>
       </c>
-      <c r="S25" s="311">
+      <c r="S25" s="307">
         <v>-10.28</v>
       </c>
-      <c r="T25" s="312">
-        <v>2.46</v>
+      <c r="T25" s="308">
+        <v>1.15</v>
       </c>
     </row>
     <row r="26">
@@ -10346,7 +10362,7 @@
       <c r="C26" t="str">
         <v>002365</v>
       </c>
-      <c r="D26" s="316" t="str">
+      <c r="D26" s="317" t="str">
         <v>净卖: -918.91万</v>
       </c>
       <c r="E26">
@@ -10361,41 +10377,41 @@
       <c r="H26">
         <v>-8.32</v>
       </c>
-      <c r="I26" s="324">
+      <c r="I26" s="318">
         <v>20.02</v>
       </c>
-      <c r="J26" s="325">
+      <c r="J26" s="319">
         <v>15.9</v>
       </c>
-      <c r="K26" s="317">
+      <c r="K26" s="320">
         <v>22.97</v>
       </c>
-      <c r="L26" s="321">
+      <c r="L26" s="325">
         <v>19.43</v>
       </c>
-      <c r="M26" s="322">
+      <c r="M26" s="313">
         <v>16.02</v>
       </c>
-      <c r="N26" s="313">
+      <c r="N26" s="322">
         <v>10.37</v>
       </c>
-      <c r="O26" s="315">
+      <c r="O26" s="314">
         <v>9.42</v>
       </c>
-      <c r="P26" s="318">
+      <c r="P26" s="315">
         <v>11.66</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="323">
         <v>6.24</v>
       </c>
-      <c r="R26" s="323">
+      <c r="R26" s="321">
         <v>16.84</v>
       </c>
-      <c r="S26" s="314">
+      <c r="S26" s="316">
         <v>20.49</v>
       </c>
-      <c r="T26" s="320">
-        <v>54.89</v>
+      <c r="T26" s="324">
+        <v>53.24</v>
       </c>
     </row>
     <row r="27">
@@ -10408,7 +10424,7 @@
       <c r="C27" t="str">
         <v>600180</v>
       </c>
-      <c r="D27" s="335" t="str">
+      <c r="D27" s="329" t="str">
         <v>净卖: -1973.71万</v>
       </c>
       <c r="E27">
@@ -10423,41 +10439,41 @@
       <c r="H27">
         <v>-4.9</v>
       </c>
-      <c r="I27" s="336">
+      <c r="I27" s="330">
         <v>0.21</v>
       </c>
-      <c r="J27" s="332">
+      <c r="J27" s="331">
         <v>-1.93</v>
       </c>
       <c r="K27" s="337">
         <v>-3.86</v>
       </c>
-      <c r="L27" s="338">
+      <c r="L27" s="332">
         <v>-2.58</v>
       </c>
-      <c r="M27" s="327">
+      <c r="M27" s="333">
         <v>-1.5</v>
       </c>
-      <c r="N27" s="333">
+      <c r="N27" s="326">
         <v>-3.43</v>
       </c>
-      <c r="O27" s="326">
+      <c r="O27" s="327">
         <v>-5.79</v>
       </c>
-      <c r="P27" s="329">
+      <c r="P27" s="334">
         <v>-4.94</v>
       </c>
-      <c r="Q27" s="334">
+      <c r="Q27" s="335">
         <v>-8.58</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="336">
         <v>-7.73</v>
       </c>
-      <c r="S27" s="328">
+      <c r="S27" s="338">
         <v>-8.37</v>
       </c>
-      <c r="T27" s="331">
-        <v>-37.34</v>
+      <c r="T27" s="328">
+        <v>-34.33</v>
       </c>
     </row>
     <row r="28">
@@ -10470,7 +10486,7 @@
       <c r="C28" t="str">
         <v>002743</v>
       </c>
-      <c r="D28" s="348" t="str">
+      <c r="D28" s="343" t="str">
         <v>净卖: -345.80万</v>
       </c>
       <c r="E28">
@@ -10485,41 +10501,41 @@
       <c r="H28">
         <v>-9.98</v>
       </c>
-      <c r="I28" s="349">
+      <c r="I28" s="346">
         <v>0</v>
       </c>
-      <c r="J28" s="343">
+      <c r="J28" s="339">
         <v>-5.83</v>
       </c>
-      <c r="K28" s="350">
+      <c r="K28" s="347">
         <v>-3.38</v>
       </c>
-      <c r="L28" s="344">
+      <c r="L28" s="340">
         <v>0.75</v>
       </c>
-      <c r="M28" s="351">
+      <c r="M28" s="348">
         <v>1.88</v>
       </c>
-      <c r="N28" s="345">
+      <c r="N28" s="349">
         <v>3.01</v>
       </c>
-      <c r="O28" s="346">
+      <c r="O28" s="350">
         <v>3.95</v>
       </c>
-      <c r="P28" s="347">
+      <c r="P28" s="344">
         <v>0.75</v>
       </c>
-      <c r="Q28" s="339">
+      <c r="Q28" s="341">
         <v>-0.19</v>
       </c>
-      <c r="R28" s="340">
+      <c r="R28" s="345">
         <v>1.5</v>
       </c>
-      <c r="S28" s="341">
+      <c r="S28" s="351">
         <v>5.83</v>
       </c>
       <c r="T28" s="342">
-        <v>-0.38</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="29">
@@ -10547,41 +10563,41 @@
       <c r="H29">
         <v>-1.2</v>
       </c>
-      <c r="I29" s="364">
+      <c r="I29" s="360">
         <v>-8.91</v>
       </c>
-      <c r="J29" s="358">
+      <c r="J29" s="361">
         <v>0.2</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="362">
         <v>4.45</v>
       </c>
-      <c r="L29" s="355">
+      <c r="L29" s="359">
         <v>-2.94</v>
       </c>
-      <c r="M29" s="359">
+      <c r="M29" s="363">
         <v>-7.89</v>
       </c>
-      <c r="N29" s="361">
+      <c r="N29" s="354">
         <v>-12.45</v>
       </c>
-      <c r="O29" s="360">
+      <c r="O29" s="355">
         <v>-11.84</v>
       </c>
-      <c r="P29" s="356">
+      <c r="P29" s="364">
         <v>-8.1</v>
       </c>
       <c r="Q29" s="352">
         <v>-5.36</v>
       </c>
-      <c r="R29" s="357">
+      <c r="R29" s="356">
         <v>-2.53</v>
       </c>
-      <c r="S29" s="362">
+      <c r="S29" s="357">
         <v>-3.54</v>
       </c>
-      <c r="T29" s="363">
-        <v>-24.19</v>
+      <c r="T29" s="358">
+        <v>-26.11</v>
       </c>
     </row>
     <row r="30">
@@ -10594,7 +10610,7 @@
       <c r="C30" t="str">
         <v>000637</v>
       </c>
-      <c r="D30" s="367" t="str">
+      <c r="D30" s="375" t="str">
         <v>净卖: -692.69万</v>
       </c>
       <c r="E30">
@@ -10609,41 +10625,41 @@
       <c r="H30">
         <v>-4.62</v>
       </c>
-      <c r="I30" s="368">
+      <c r="I30" s="376">
         <v>-5.65</v>
       </c>
-      <c r="J30" s="369">
+      <c r="J30" s="377">
         <v>3.83</v>
       </c>
-      <c r="K30" s="366">
+      <c r="K30" s="365">
         <v>-0.81</v>
       </c>
-      <c r="L30" s="371">
+      <c r="L30" s="368">
         <v>0.6</v>
       </c>
-      <c r="M30" s="372">
+      <c r="M30" s="366">
         <v>-2.02</v>
       </c>
       <c r="N30" s="373">
         <v>-6.25</v>
       </c>
-      <c r="O30" s="375">
+      <c r="O30" s="369">
         <v>-4.84</v>
       </c>
       <c r="P30" s="374">
         <v>-4.23</v>
       </c>
-      <c r="Q30" s="376">
+      <c r="Q30" s="370">
         <v>-3.43</v>
       </c>
-      <c r="R30" s="370">
+      <c r="R30" s="367">
         <v>-0.81</v>
       </c>
-      <c r="S30" s="377">
+      <c r="S30" s="371">
         <v>-1.01</v>
       </c>
-      <c r="T30" s="365">
-        <v>-9.27</v>
+      <c r="T30" s="372">
+        <v>-8.06</v>
       </c>
     </row>
     <row r="31">
@@ -10656,7 +10672,7 @@
       <c r="C31" t="str">
         <v>003038</v>
       </c>
-      <c r="D31" s="382" t="str">
+      <c r="D31" s="388" t="str">
         <v>净买: 1673.87万</v>
       </c>
       <c r="E31">
@@ -10671,41 +10687,41 @@
       <c r="H31">
         <v>-3.7</v>
       </c>
-      <c r="I31" s="383">
+      <c r="I31" s="381">
         <v>-1.79</v>
       </c>
-      <c r="J31" s="379">
+      <c r="J31" s="382">
         <v>-1.79</v>
       </c>
-      <c r="K31" s="386">
+      <c r="K31" s="384">
         <v>-7.21</v>
       </c>
-      <c r="L31" s="384">
+      <c r="L31" s="389">
         <v>-9</v>
       </c>
-      <c r="M31" s="387">
+      <c r="M31" s="390">
         <v>-11.53</v>
       </c>
-      <c r="N31" s="388">
+      <c r="N31" s="385">
         <v>-10.42</v>
       </c>
-      <c r="O31" s="385">
+      <c r="O31" s="378">
         <v>-9.79</v>
       </c>
-      <c r="P31" s="389">
+      <c r="P31" s="379">
         <v>-11.32</v>
       </c>
-      <c r="Q31" s="390">
+      <c r="Q31" s="380">
         <v>-11.26</v>
       </c>
-      <c r="R31" s="380">
+      <c r="R31" s="386">
         <v>-9.89</v>
       </c>
-      <c r="S31" s="378">
+      <c r="S31" s="383">
         <v>-11.89</v>
       </c>
-      <c r="T31" s="381">
-        <v>-23.26</v>
+      <c r="T31" s="387">
+        <v>-25</v>
       </c>
     </row>
     <row r="32">
@@ -10718,7 +10734,7 @@
       <c r="C32" t="str">
         <v>300390</v>
       </c>
-      <c r="D32" s="393" t="str">
+      <c r="D32" s="402" t="str">
         <v>净卖: -2712.20万</v>
       </c>
       <c r="E32">
@@ -10733,41 +10749,41 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" s="402">
+      <c r="I32" s="396">
         <v>15.32</v>
       </c>
-      <c r="J32" s="396">
+      <c r="J32" s="397">
         <v>19.24</v>
       </c>
-      <c r="K32" s="399">
+      <c r="K32" s="403">
         <v>21.18</v>
       </c>
-      <c r="L32" s="403">
+      <c r="L32" s="398">
         <v>17.01</v>
       </c>
-      <c r="M32" s="400">
+      <c r="M32" s="391">
         <v>39.41</v>
       </c>
-      <c r="N32" s="397">
+      <c r="N32" s="399">
         <v>44.54</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="392">
         <v>73.45</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="395">
         <v>64.28</v>
       </c>
-      <c r="Q32" s="401">
+      <c r="Q32" s="393">
         <v>66.69</v>
       </c>
-      <c r="R32" s="394">
+      <c r="R32" s="400">
         <v>76.84</v>
       </c>
-      <c r="S32" s="392">
+      <c r="S32" s="394">
         <v>41.99</v>
       </c>
-      <c r="T32" s="395">
-        <v>173.45</v>
+      <c r="T32" s="401">
+        <v>169.85</v>
       </c>
     </row>
     <row r="33">
@@ -10780,7 +10796,7 @@
       <c r="C33" t="str">
         <v>603829</v>
       </c>
-      <c r="D33" s="414" t="str">
+      <c r="D33" s="406" t="str">
         <v>净卖: -2484.77万</v>
       </c>
       <c r="E33">
@@ -10795,13 +10811,13 @@
       <c r="H33">
         <v>0.16</v>
       </c>
-      <c r="I33" s="406">
+      <c r="I33" s="411">
         <v>-10.16</v>
       </c>
-      <c r="J33" s="412">
+      <c r="J33" s="414">
         <v>-9.96</v>
       </c>
-      <c r="K33" s="408">
+      <c r="K33" s="407">
         <v>-18.94</v>
       </c>
       <c r="L33" s="415">
@@ -10810,26 +10826,26 @@
       <c r="M33" s="409">
         <v>-22.75</v>
       </c>
-      <c r="N33" s="416">
+      <c r="N33" s="412">
         <v>-25.3</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="408">
         <v>-26.94</v>
       </c>
-      <c r="P33" s="405">
+      <c r="P33" s="410">
         <v>-27.14</v>
       </c>
-      <c r="Q33" s="410">
+      <c r="Q33" s="416">
         <v>-26.97</v>
       </c>
-      <c r="R33" s="411">
+      <c r="R33" s="404">
         <v>-27.01</v>
       </c>
       <c r="S33" s="413">
         <v>-25.4</v>
       </c>
-      <c r="T33" s="407">
-        <v>-3.97</v>
+      <c r="T33" s="405">
+        <v>-10.19</v>
       </c>
     </row>
     <row r="34">
@@ -10842,7 +10858,7 @@
       <c r="C34" t="str">
         <v>603829</v>
       </c>
-      <c r="D34" s="421" t="str">
+      <c r="D34" s="419" t="str">
         <v>净卖: -2802.75万</v>
       </c>
       <c r="E34">
@@ -10857,41 +10873,41 @@
       <c r="H34">
         <v>0.15</v>
       </c>
-      <c r="I34" s="422">
+      <c r="I34" s="426">
         <v>-10.11</v>
       </c>
-      <c r="J34" s="429">
+      <c r="J34" s="427">
         <v>-14.21</v>
       </c>
-      <c r="K34" s="417">
+      <c r="K34" s="423">
         <v>-14.32</v>
       </c>
-      <c r="L34" s="423">
+      <c r="L34" s="420">
         <v>-17.16</v>
       </c>
-      <c r="M34" s="425">
+      <c r="M34" s="428">
         <v>-18.97</v>
       </c>
-      <c r="N34" s="426">
+      <c r="N34" s="429">
         <v>-19.19</v>
       </c>
-      <c r="O34" s="424">
+      <c r="O34" s="417">
         <v>-19.01</v>
       </c>
-      <c r="P34" s="420">
+      <c r="P34" s="421">
         <v>-19.05</v>
       </c>
-      <c r="Q34" s="418">
+      <c r="Q34" s="424">
         <v>-17.27</v>
       </c>
-      <c r="R34" s="427">
+      <c r="R34" s="418">
         <v>-15.92</v>
       </c>
-      <c r="S34" s="419">
+      <c r="S34" s="425">
         <v>-14.76</v>
       </c>
-      <c r="T34" s="428">
-        <v>6.51</v>
+      <c r="T34" s="422">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="35">
@@ -10904,7 +10920,7 @@
       <c r="C35" t="str">
         <v>920427</v>
       </c>
-      <c r="D35" s="436" t="str">
+      <c r="D35" s="431" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E35">
@@ -10919,41 +10935,41 @@
       <c r="H35">
         <v>-8.89</v>
       </c>
-      <c r="I35" s="441">
+      <c r="I35" s="439">
         <v>-21.22</v>
       </c>
-      <c r="J35" s="437">
+      <c r="J35" s="432">
         <v>-19.61</v>
       </c>
       <c r="K35" s="442">
         <v>-23.32</v>
       </c>
-      <c r="L35" s="432">
+      <c r="L35" s="440">
         <v>-23.12</v>
       </c>
       <c r="M35" s="433">
         <v>-27.46</v>
       </c>
-      <c r="N35" s="438">
+      <c r="N35" s="437">
         <v>-27.71</v>
       </c>
       <c r="O35" s="434">
         <v>-26.34</v>
       </c>
-      <c r="P35" s="439">
+      <c r="P35" s="438">
         <v>-23.22</v>
       </c>
-      <c r="Q35" s="430">
+      <c r="Q35" s="441">
         <v>-26.44</v>
       </c>
       <c r="R35" s="435">
         <v>-27.12</v>
       </c>
-      <c r="S35" s="431">
+      <c r="S35" s="430">
         <v>-26.68</v>
       </c>
-      <c r="T35" s="440">
-        <v>-43.41</v>
+      <c r="T35" s="436">
+        <v>-44.44</v>
       </c>
     </row>
     <row r="36">
@@ -10966,7 +10982,7 @@
       <c r="C36" t="str">
         <v>920427</v>
       </c>
-      <c r="D36" s="445" t="str">
+      <c r="D36" s="455" t="str">
         <v>净卖: -130.63万</v>
       </c>
       <c r="E36">
@@ -10981,41 +10997,41 @@
       <c r="H36">
         <v>-4.33</v>
       </c>
-      <c r="I36" s="453">
+      <c r="I36" s="447">
         <v>6.67</v>
       </c>
-      <c r="J36" s="446">
+      <c r="J36" s="443">
         <v>1.75</v>
       </c>
-      <c r="K36" s="449">
+      <c r="K36" s="448">
         <v>2.01</v>
       </c>
-      <c r="L36" s="450">
+      <c r="L36" s="444">
         <v>-3.75</v>
       </c>
-      <c r="M36" s="443">
+      <c r="M36" s="451">
         <v>-4.08</v>
       </c>
-      <c r="N36" s="447">
+      <c r="N36" s="452">
         <v>-2.27</v>
       </c>
-      <c r="O36" s="454">
+      <c r="O36" s="453">
         <v>1.88</v>
       </c>
-      <c r="P36" s="448">
+      <c r="P36" s="449">
         <v>-2.39</v>
       </c>
-      <c r="Q36" s="451">
+      <c r="Q36" s="445">
         <v>-3.3</v>
       </c>
-      <c r="R36" s="455">
+      <c r="R36" s="450">
         <v>-2.72</v>
       </c>
-      <c r="S36" s="444">
+      <c r="S36" s="446">
         <v>-6.54</v>
       </c>
-      <c r="T36" s="452">
-        <v>-24.92</v>
+      <c r="T36" s="454">
+        <v>-26.28</v>
       </c>
     </row>
     <row r="37">
@@ -11028,7 +11044,7 @@
       <c r="C37" t="str">
         <v>603798</v>
       </c>
-      <c r="D37" s="461" t="str">
+      <c r="D37" s="463" t="str">
         <v>净卖: -286.39万</v>
       </c>
       <c r="E37">
@@ -11043,41 +11059,41 @@
       <c r="H37">
         <v>-9.99</v>
       </c>
-      <c r="I37" s="462">
+      <c r="I37" s="464">
         <v>0</v>
       </c>
-      <c r="J37" s="466">
+      <c r="J37" s="465">
         <v>-5.52</v>
       </c>
-      <c r="K37" s="463">
+      <c r="K37" s="466">
         <v>-0.12</v>
       </c>
-      <c r="L37" s="457">
+      <c r="L37" s="456">
         <v>-0.72</v>
       </c>
-      <c r="M37" s="458">
+      <c r="M37" s="460">
         <v>-6.3</v>
       </c>
-      <c r="N37" s="464">
+      <c r="N37" s="461">
         <v>-2.82</v>
       </c>
-      <c r="O37" s="467">
+      <c r="O37" s="457">
         <v>-3.3</v>
       </c>
-      <c r="P37" s="459">
+      <c r="P37" s="468">
         <v>-5.34</v>
       </c>
-      <c r="Q37" s="460">
+      <c r="Q37" s="467">
         <v>-4.92</v>
       </c>
-      <c r="R37" s="468">
+      <c r="R37" s="458">
         <v>0.72</v>
       </c>
-      <c r="S37" s="456">
+      <c r="S37" s="462">
         <v>-4.08</v>
       </c>
-      <c r="T37" s="465">
-        <v>9.36</v>
+      <c r="T37" s="459">
+        <v>12.18</v>
       </c>
     </row>
     <row r="38">
@@ -11090,7 +11106,7 @@
       <c r="C38" t="str">
         <v>603291</v>
       </c>
-      <c r="D38" s="469" t="str">
+      <c r="D38" s="475" t="str">
         <v>净买: 465.04万</v>
       </c>
       <c r="E38">
@@ -11105,41 +11121,41 @@
       <c r="H38">
         <v>1.97</v>
       </c>
-      <c r="I38" s="475">
+      <c r="I38" s="476">
         <v>-11.73</v>
       </c>
-      <c r="J38" s="476">
+      <c r="J38" s="480">
         <v>-11.73</v>
       </c>
-      <c r="K38" s="478">
+      <c r="K38" s="481">
         <v>-15.59</v>
       </c>
-      <c r="L38" s="470">
+      <c r="L38" s="469">
         <v>-15.51</v>
       </c>
-      <c r="M38" s="479">
+      <c r="M38" s="478">
         <v>-14.97</v>
       </c>
-      <c r="N38" s="471">
+      <c r="N38" s="470">
         <v>-15.66</v>
       </c>
-      <c r="O38" s="472">
+      <c r="O38" s="477">
         <v>-15.82</v>
       </c>
-      <c r="P38" s="477">
+      <c r="P38" s="473">
         <v>-16.05</v>
       </c>
-      <c r="Q38" s="473">
+      <c r="Q38" s="471">
         <v>-15.97</v>
       </c>
-      <c r="R38" s="480">
+      <c r="R38" s="479">
         <v>-15.51</v>
       </c>
-      <c r="S38" s="474">
+      <c r="S38" s="472">
         <v>-15.59</v>
       </c>
-      <c r="T38" s="481">
-        <v>-6.64</v>
+      <c r="T38" s="474">
+        <v>-12.73</v>
       </c>
     </row>
     <row r="39">
@@ -11152,7 +11168,7 @@
       <c r="C39" t="str">
         <v>603284</v>
       </c>
-      <c r="D39" s="482" t="str">
+      <c r="D39" s="494" t="str">
         <v>净买: 1322.73万</v>
       </c>
       <c r="E39">
@@ -11167,41 +11183,41 @@
       <c r="H39">
         <v>-0.79</v>
       </c>
-      <c r="I39" s="492">
+      <c r="I39" s="487">
         <v>4.15</v>
       </c>
-      <c r="J39" s="493">
+      <c r="J39" s="482">
         <v>7.16</v>
       </c>
-      <c r="K39" s="488">
+      <c r="K39" s="483">
         <v>7.16</v>
       </c>
-      <c r="L39" s="483">
+      <c r="L39" s="488">
         <v>7.39</v>
       </c>
-      <c r="M39" s="484">
+      <c r="M39" s="490">
         <v>7.45</v>
       </c>
-      <c r="N39" s="485">
+      <c r="N39" s="491">
         <v>8.48</v>
       </c>
-      <c r="O39" s="494">
+      <c r="O39" s="484">
         <v>6.71</v>
       </c>
-      <c r="P39" s="486">
+      <c r="P39" s="489">
         <v>7.41</v>
       </c>
-      <c r="Q39" s="487">
+      <c r="Q39" s="493">
         <v>7.64</v>
       </c>
-      <c r="R39" s="489">
+      <c r="R39" s="485">
         <v>6.33</v>
       </c>
-      <c r="S39" s="490">
+      <c r="S39" s="486">
         <v>3.28</v>
       </c>
-      <c r="T39" s="491">
-        <v>-7.58</v>
+      <c r="T39" s="492">
+        <v>-10.5</v>
       </c>
     </row>
     <row r="40">
@@ -11214,7 +11230,7 @@
       <c r="C40" t="str">
         <v>600605</v>
       </c>
-      <c r="D40" s="498" t="str">
+      <c r="D40" s="502" t="str">
         <v>净卖: -789.04万</v>
       </c>
       <c r="E40">
@@ -11229,37 +11245,39 @@
       <c r="H40">
         <v>6.5</v>
       </c>
-      <c r="I40" s="505">
+      <c r="I40" s="500">
         <v>3.29</v>
       </c>
-      <c r="J40" s="495">
+      <c r="J40" s="503">
         <v>-0.16</v>
       </c>
-      <c r="K40" s="501">
+      <c r="K40" s="499">
         <v>-1.47</v>
       </c>
-      <c r="L40" s="496">
+      <c r="L40" s="504">
         <v>-3.1</v>
       </c>
-      <c r="M40" s="499">
+      <c r="M40" s="498">
         <v>-2.08</v>
       </c>
-      <c r="N40" s="502">
+      <c r="N40" s="505">
         <v>-2.04</v>
       </c>
-      <c r="O40" s="504">
+      <c r="O40" s="501">
         <v>-4.31</v>
       </c>
-      <c r="P40" s="503">
+      <c r="P40" s="506">
         <v>1.66</v>
       </c>
-      <c r="Q40" s="500">
+      <c r="Q40" s="495">
         <v>5.05</v>
       </c>
-      <c r="R40" t="str"/>
+      <c r="R40" s="496">
+        <v>0.73</v>
+      </c>
       <c r="S40" t="str"/>
       <c r="T40" s="497">
-        <v>5.05</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="41">
@@ -11301,7 +11319,7 @@
         <v>39</v>
       </c>
       <c r="R41">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S41">
         <v>38</v>
@@ -11321,41 +11339,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="508">
+      <c r="I42" s="507">
         <v>38.46</v>
       </c>
-      <c r="J42" s="516">
+      <c r="J42" s="508">
         <v>41.03</v>
       </c>
-      <c r="K42" s="507">
+      <c r="K42" s="512">
         <v>38.46</v>
       </c>
-      <c r="L42" s="509">
+      <c r="L42" s="517">
         <v>35.9</v>
       </c>
-      <c r="M42" s="513">
+      <c r="M42" s="514">
         <v>28.21</v>
       </c>
-      <c r="N42" s="510">
+      <c r="N42" s="515">
         <v>25.64</v>
       </c>
-      <c r="O42" s="511">
+      <c r="O42" s="516">
         <v>30.77</v>
       </c>
-      <c r="P42" s="512">
+      <c r="P42" s="509">
         <v>35.9</v>
       </c>
-      <c r="Q42" s="517">
+      <c r="Q42" s="513">
         <v>28.21</v>
       </c>
-      <c r="R42" s="514">
-        <v>31.58</v>
-      </c>
-      <c r="S42" s="506">
+      <c r="R42" s="510">
+        <v>33.33</v>
+      </c>
+      <c r="S42" s="511">
         <v>21.05</v>
       </c>
-      <c r="T42" s="515">
-        <v>53.85</v>
+      <c r="T42" s="518">
+        <v>56.41</v>
       </c>
     </row>
     <row r="43">
@@ -11369,41 +11387,41 @@
       <c r="F43" t="str"/>
       <c r="G43" t="str"/>
       <c r="H43" t="str"/>
-      <c r="I43" s="523">
+      <c r="I43" s="521">
         <v>-0.38</v>
       </c>
-      <c r="J43" s="519">
+      <c r="J43" s="524">
         <v>-0.74</v>
       </c>
-      <c r="K43" s="520">
+      <c r="K43" s="525">
         <v>-2.11</v>
       </c>
-      <c r="L43" s="524">
+      <c r="L43" s="526">
         <v>-4.11</v>
       </c>
-      <c r="M43" s="525">
+      <c r="M43" s="527">
         <v>-5.17</v>
       </c>
-      <c r="N43" s="529">
+      <c r="N43" s="522">
         <v>-6.48</v>
       </c>
-      <c r="O43" s="521">
+      <c r="O43" s="528">
         <v>-5.38</v>
       </c>
-      <c r="P43" s="526">
+      <c r="P43" s="529">
         <v>-5.52</v>
       </c>
-      <c r="Q43" s="527">
+      <c r="Q43" s="530">
         <v>-5.82</v>
       </c>
-      <c r="R43" s="528">
-        <v>-5.24</v>
-      </c>
-      <c r="S43" s="518">
+      <c r="R43" s="519">
+        <v>-5.09</v>
+      </c>
+      <c r="S43" s="523">
         <v>-7.62</v>
       </c>
-      <c r="T43" s="522">
-        <v>17.07</v>
+      <c r="T43" s="520">
+        <v>14.96</v>
       </c>
     </row>
   </sheetData>
